--- a/UConnBleedBlue/wwwroot/Data/Players.xlsx
+++ b/UConnBleedBlue/wwwroot/Data/Players.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\UConnBleedBlue\UConnBleedBlue\wwwroot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE495F1-6AF8-49BC-81EA-E3FAB0B1872B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269C181E-D1DC-4C8F-9047-0B9692242ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2670" yWindow="1800" windowWidth="21600" windowHeight="13680" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
+    <workbookView xWindow="-21465" yWindow="1800" windowWidth="21600" windowHeight="13680" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="213">
   <si>
     <t>Demers, Kenny</t>
   </si>
@@ -630,6 +630,51 @@
   </si>
   <si>
     <t>Timko, Ryan</t>
+  </si>
+  <si>
+    <t>Chanterelle, Jerry</t>
+  </si>
+  <si>
+    <t>jerry.chanterelle@gmail.com</t>
+  </si>
+  <si>
+    <t>Faison, Hezekiah</t>
+  </si>
+  <si>
+    <t>hfaison33@yahoo.com</t>
+  </si>
+  <si>
+    <t>Ferraro, Dave</t>
+  </si>
+  <si>
+    <t>davef@rollinglawns.com</t>
+  </si>
+  <si>
+    <t>Jones, Daniel</t>
+  </si>
+  <si>
+    <t>yankee39@gmail.com</t>
+  </si>
+  <si>
+    <t>Sudora, Scott</t>
+  </si>
+  <si>
+    <t>gssudsy@yahoo.com</t>
+  </si>
+  <si>
+    <t>Wardlow, Doug</t>
+  </si>
+  <si>
+    <t>wardlawdoug51@gmail.com</t>
+  </si>
+  <si>
+    <t>Williams, Brandon</t>
+  </si>
+  <si>
+    <t>cwilli6161@gmail.com</t>
+  </si>
+  <si>
+    <t>Robert Ingalls</t>
   </si>
 </sst>
 </file>
@@ -1014,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F97E2D-D2EE-4E19-AA28-ED70E4256082}">
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" customWidth="1"/>
@@ -1411,16 +1456,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>198</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
@@ -1428,33 +1467,33 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>113</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C24" s="1">
         <v>1974</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="E23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1982</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="E24" t="b">
         <v>1</v>
@@ -1462,13 +1501,13 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>194</v>
+        <v>26</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="C25" s="1">
-        <v>1977</v>
+        <v>1982</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>140</v>
@@ -1479,10 +1518,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>117</v>
+        <v>193</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>118</v>
+        <v>194</v>
       </c>
       <c r="C26" s="1">
         <v>1977</v>
@@ -1493,39 +1532,39 @@
       <c r="E26" t="b">
         <v>1</v>
       </c>
-      <c r="G26" t="s">
-        <v>150</v>
-      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" t="s">
-        <v>93</v>
+      <c r="A27" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="C27" s="1">
-        <v>1964</v>
+        <v>1977</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
+      </c>
+      <c r="G27" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>94</v>
+        <v>16</v>
+      </c>
+      <c r="B28" t="s">
+        <v>93</v>
       </c>
       <c r="C28" s="1">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
@@ -1533,53 +1572,53 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="C29" s="1">
-        <v>1993</v>
+        <v>1969</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
-      </c>
-      <c r="G29" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>115</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>165</v>
+        <v>116</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1993</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E30" t="b">
         <v>1</v>
+      </c>
+      <c r="G30" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" s="1">
-        <v>1979</v>
+        <v>42</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
@@ -1587,16 +1626,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C32" s="1">
-        <v>2005</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>145</v>
+        <v>201</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
@@ -1604,36 +1637,27 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>161</v>
+        <v>202</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
-      </c>
-      <c r="G33" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C34" s="1">
-        <v>1971</v>
+        <v>1979</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
@@ -1641,41 +1665,35 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>71</v>
+        <v>183</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="C35" s="1">
-        <v>1993</v>
+        <v>2005</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E35" t="b">
         <v>1</v>
-      </c>
-      <c r="G35" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C36" s="1">
-        <v>1970</v>
+        <v>162</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="E36" t="b">
-        <v>1</v>
-      </c>
-      <c r="F36" t="b">
         <v>1</v>
       </c>
       <c r="G36" t="s">
@@ -1684,13 +1702,13 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C37" s="1">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>142</v>
@@ -1701,53 +1719,59 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>175</v>
+        <v>71</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>176</v>
+        <v>72</v>
       </c>
       <c r="C38" s="1">
-        <v>2004</v>
+        <v>1993</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
       </c>
-      <c r="F38" t="b">
-        <v>1</v>
+      <c r="G38" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="C39" s="1">
-        <v>1995</v>
+        <v>1970</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E39" t="b">
         <v>1</v>
+      </c>
+      <c r="F39" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>63</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>64</v>
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>97</v>
       </c>
       <c r="C40" s="1">
-        <v>1979</v>
+        <v>1972</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E40" t="b">
         <v>1</v>
@@ -1755,33 +1779,30 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>20</v>
-      </c>
-      <c r="B41" t="s">
-        <v>98</v>
+        <v>175</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="C41" s="1">
-        <v>1979</v>
+        <v>2004</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E41" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C42" s="1">
-        <v>1986</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
       <c r="E42" t="b">
         <v>1</v>
@@ -1789,36 +1810,33 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C43" s="1">
-        <v>1982</v>
+        <v>1995</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E43" t="b">
         <v>1</v>
-      </c>
-      <c r="G43" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>137</v>
+        <v>63</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>138</v>
+        <v>64</v>
       </c>
       <c r="C44" s="1">
-        <v>1994</v>
+        <v>1979</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E44" t="b">
         <v>1</v>
@@ -1826,13 +1844,13 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>27</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>99</v>
+        <v>20</v>
+      </c>
+      <c r="B45" t="s">
+        <v>98</v>
       </c>
       <c r="C45" s="1">
-        <v>1982</v>
+        <v>1979</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>140</v>
@@ -1840,22 +1858,19 @@
       <c r="E45" t="b">
         <v>1</v>
       </c>
-      <c r="G45" t="s">
-        <v>150</v>
-      </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="C46" s="1">
-        <v>2008</v>
+        <v>1986</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
@@ -1863,33 +1878,36 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>165</v>
+        <v>120</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1982</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
+      </c>
+      <c r="G47" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" t="s">
-        <v>100</v>
+        <v>137</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="C48" s="1">
-        <v>1987</v>
+        <v>1994</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E48" t="b">
         <v>1</v>
@@ -1897,13 +1915,13 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C49" s="1">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>140</v>
@@ -1917,53 +1935,47 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="C50" s="1">
-        <v>1973</v>
+        <v>2008</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E50" t="b">
         <v>1</v>
-      </c>
-      <c r="G50" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>166</v>
+        <v>75</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="C51" s="1">
-        <v>1978</v>
+        <v>76</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="E51" t="b">
         <v>1</v>
-      </c>
-      <c r="G51" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>131</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>132</v>
+        <v>2</v>
+      </c>
+      <c r="B52" t="s">
+        <v>100</v>
       </c>
       <c r="C52" s="1">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>144</v>
@@ -1971,16 +1983,13 @@
       <c r="E52" t="b">
         <v>1</v>
       </c>
-      <c r="G52" t="s">
-        <v>150</v>
-      </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="C53" s="1">
         <v>1981</v>
@@ -1997,33 +2006,36 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>25</v>
-      </c>
-      <c r="B54" t="s">
-        <v>101</v>
+        <v>163</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="C54" s="1">
-        <v>1986</v>
+        <v>1973</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E54" t="b">
         <v>1</v>
+      </c>
+      <c r="G54" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>166</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>48</v>
+        <v>167</v>
       </c>
       <c r="C55" s="1">
-        <v>1966</v>
+        <v>1978</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E55" t="b">
         <v>1</v>
@@ -2034,13 +2046,13 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="C56" s="1">
-        <v>1992</v>
+        <v>1989</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>144</v>
@@ -2054,33 +2066,36 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C57" s="1">
-        <v>1984</v>
+        <v>1981</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E57" t="b">
         <v>1</v>
+      </c>
+      <c r="G57" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>67</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>68</v>
+        <v>25</v>
+      </c>
+      <c r="B58" t="s">
+        <v>101</v>
       </c>
       <c r="C58" s="1">
-        <v>1979</v>
+        <v>1986</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E58" t="b">
         <v>1</v>
@@ -2088,27 +2103,36 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>24</v>
-      </c>
-      <c r="B59" t="s">
-        <v>102</v>
+        <v>47</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="C59" s="1">
-        <v>1979</v>
+        <v>1966</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E59" t="b">
         <v>1</v>
+      </c>
+      <c r="G59" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>169</v>
+        <v>112</v>
+      </c>
+      <c r="C60" s="1">
+        <v>1992</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="E60" t="b">
         <v>1</v>
@@ -2119,53 +2143,47 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1</v>
-      </c>
-      <c r="B61" t="s">
-        <v>105</v>
+        <v>88</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="C61" s="1">
-        <v>1970</v>
+        <v>1984</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E61" t="b">
         <v>1</v>
-      </c>
-      <c r="G61" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>3</v>
-      </c>
-      <c r="B62" t="s">
-        <v>106</v>
+        <v>67</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="C62" s="1">
-        <v>2015</v>
+        <v>1979</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="E62" t="b">
         <v>1</v>
-      </c>
-      <c r="G62" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>65</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>66</v>
+        <v>24</v>
+      </c>
+      <c r="B63" t="s">
+        <v>102</v>
       </c>
       <c r="C63" s="1">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>140</v>
@@ -2176,67 +2194,70 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>69</v>
+        <v>168</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C64" s="1">
-        <v>1974</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="E64" t="b">
         <v>1</v>
+      </c>
+      <c r="G64" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>181</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>182</v>
+        <v>1</v>
+      </c>
+      <c r="B65" t="s">
+        <v>105</v>
       </c>
       <c r="C65" s="1">
-        <v>1976</v>
+        <v>1970</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E65" t="b">
         <v>1</v>
+      </c>
+      <c r="G65" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>127</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>128</v>
+        <v>3</v>
+      </c>
+      <c r="B66" t="s">
+        <v>106</v>
       </c>
       <c r="C66" s="1">
-        <v>1980</v>
+        <v>2015</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E66" t="b">
         <v>1</v>
+      </c>
+      <c r="G66" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>7</v>
-      </c>
-      <c r="B67" t="s">
-        <v>107</v>
+        <v>65</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="C67" s="1">
-        <v>1969</v>
+        <v>1978</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E67" t="b">
         <v>1</v>
@@ -2244,36 +2265,33 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
+      </c>
+      <c r="C68" s="1">
+        <v>1974</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="E68" t="b">
         <v>1</v>
-      </c>
-      <c r="G68" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C69" s="1">
-        <v>2004</v>
+        <v>1976</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E69" t="b">
         <v>1</v>
@@ -2281,16 +2299,16 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="C70" s="1">
-        <v>1968</v>
+        <v>1980</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E70" t="b">
         <v>1</v>
@@ -2298,16 +2316,16 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>49</v>
+        <v>7</v>
+      </c>
+      <c r="B71" t="s">
+        <v>107</v>
       </c>
       <c r="C71" s="1">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E71" t="b">
         <v>1</v>
@@ -2315,16 +2333,16 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C72" s="1">
-        <v>1985</v>
+        <v>37</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="E72" t="b">
         <v>1</v>
@@ -2335,33 +2353,30 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>38</v>
+        <v>179</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="C73" s="1">
-        <v>1975</v>
+        <v>2004</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E73" t="b">
         <v>1</v>
-      </c>
-      <c r="G73" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>13</v>
-      </c>
-      <c r="B74" t="s">
-        <v>109</v>
+        <v>81</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="C74" s="1">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>143</v>
@@ -2372,16 +2387,16 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>195</v>
+        <v>15</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>196</v>
+        <v>49</v>
       </c>
       <c r="C75" s="1">
-        <v>1995</v>
+        <v>1971</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E75" t="b">
         <v>1</v>
@@ -2389,16 +2404,16 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="C76" s="1">
-        <v>1975</v>
+        <v>1985</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E76" t="b">
         <v>1</v>
@@ -2409,67 +2424,70 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>187</v>
+        <v>38</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>188</v>
+        <v>39</v>
       </c>
       <c r="C77" s="1">
-        <v>1964</v>
+        <v>1975</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E77" t="b">
         <v>1</v>
+      </c>
+      <c r="G77" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>40</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>165</v>
+        <v>13</v>
+      </c>
+      <c r="B78" t="s">
+        <v>109</v>
+      </c>
+      <c r="C78" s="1">
+        <v>1970</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="E78" t="b">
         <v>1</v>
-      </c>
-      <c r="G78" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>123</v>
+        <v>195</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>124</v>
+        <v>196</v>
       </c>
       <c r="C79" s="1">
-        <v>1976</v>
+        <v>1995</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E79" t="b">
         <v>1</v>
-      </c>
-      <c r="G79" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>171</v>
+        <v>62</v>
+      </c>
+      <c r="C80" s="1">
+        <v>1975</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="E80" t="b">
         <v>1</v>
@@ -2480,36 +2498,33 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>129</v>
+        <v>187</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="C81" s="1">
-        <v>1993</v>
+        <v>1963</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="E81" t="b">
         <v>1</v>
-      </c>
-      <c r="G81" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C82" s="1">
-        <v>2004</v>
+        <v>41</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="E82" t="b">
         <v>1</v>
@@ -2520,10 +2535,10 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="C83" s="1">
         <v>1976</v>
@@ -2540,33 +2555,30 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>44</v>
+        <v>170</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C84" s="1">
-        <v>1970</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="E84" t="b">
         <v>1</v>
+      </c>
+      <c r="G84" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C85" s="1">
-        <v>2016</v>
+        <v>1993</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E85" t="b">
         <v>1</v>
@@ -2577,13 +2589,13 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>197</v>
+        <v>135</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="C86" s="1">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>145</v>
@@ -2591,19 +2603,22 @@
       <c r="E86" t="b">
         <v>1</v>
       </c>
+      <c r="G86" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>17</v>
-      </c>
-      <c r="B87" t="s">
-        <v>110</v>
+        <v>172</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>173</v>
       </c>
       <c r="C87" s="1">
-        <v>1969</v>
+        <v>1976</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E87" t="b">
         <v>1</v>
@@ -2614,16 +2629,16 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="C88" s="1">
-        <v>1975</v>
+        <v>1970</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E88" t="b">
         <v>1</v>
@@ -2631,16 +2646,10 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>9</v>
+        <v>206</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C89" s="1">
-        <v>1989</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>144</v>
+        <v>207</v>
       </c>
       <c r="E89" t="b">
         <v>1</v>
@@ -2648,27 +2657,33 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>22</v>
+        <v>121</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="C90" s="1">
-        <v>1979</v>
+        <v>2016</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E90" t="b">
         <v>1</v>
+      </c>
+      <c r="G90" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>56</v>
+        <v>197</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>57</v>
+        <v>174</v>
       </c>
       <c r="C91" s="1">
-        <v>2006</v>
+        <v>2000</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>145</v>
@@ -2676,27 +2691,134 @@
       <c r="E91" t="b">
         <v>1</v>
       </c>
-      <c r="G91" t="s">
-        <v>150</v>
-      </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>17</v>
+      </c>
+      <c r="B92" t="s">
+        <v>110</v>
+      </c>
+      <c r="C92" s="1">
+        <v>1969</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E92" t="b">
+        <v>1</v>
+      </c>
+      <c r="G92" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>73</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C93" s="1">
+        <v>1975</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>9</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C94" s="1">
+        <v>1989</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>22</v>
+      </c>
+      <c r="C95" s="1">
+        <v>1979</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>56</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C96" s="1">
+        <v>2006</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E96" t="b">
+        <v>1</v>
+      </c>
+      <c r="G96" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>208</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E97" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>210</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>52</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B99" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C92" s="1">
+      <c r="C99" s="1">
         <v>1975</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="D99" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E92" t="b">
-        <v>1</v>
-      </c>
-      <c r="G92" t="s">
+      <c r="E99" t="b">
+        <v>1</v>
+      </c>
+      <c r="G99" t="s">
         <v>150</v>
       </c>
     </row>
@@ -2704,75 +2826,76 @@
   <hyperlinks>
     <hyperlink ref="B5" r:id="rId1" xr:uid="{8227A597-9225-4357-B8B6-9F19CC6D2D47}"/>
     <hyperlink ref="B16" r:id="rId2" xr:uid="{C440EE30-529A-4080-AE83-A4A978C3E02B}"/>
-    <hyperlink ref="B68" r:id="rId3" xr:uid="{C5FAAB38-5F1C-4A08-8709-401E7E23E0D1}"/>
-    <hyperlink ref="B73" r:id="rId4" xr:uid="{109EA93A-660A-4099-B212-FD77BC4B5297}"/>
-    <hyperlink ref="B78" r:id="rId5" xr:uid="{4FC29F3F-346D-4C86-81DD-BA31CA08B134}"/>
-    <hyperlink ref="B30" r:id="rId6" xr:uid="{98703E9F-F4A5-4829-8BBF-B9F807C63E68}"/>
-    <hyperlink ref="B84" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
-    <hyperlink ref="B22" r:id="rId8" xr:uid="{804D2DB9-BDF1-463B-9BD3-ACBFC15F041A}"/>
-    <hyperlink ref="B55" r:id="rId9" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
-    <hyperlink ref="B71" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
+    <hyperlink ref="B72" r:id="rId3" xr:uid="{C5FAAB38-5F1C-4A08-8709-401E7E23E0D1}"/>
+    <hyperlink ref="B77" r:id="rId4" xr:uid="{109EA93A-660A-4099-B212-FD77BC4B5297}"/>
+    <hyperlink ref="B82" r:id="rId5" xr:uid="{4FC29F3F-346D-4C86-81DD-BA31CA08B134}"/>
+    <hyperlink ref="B31" r:id="rId6" xr:uid="{98703E9F-F4A5-4829-8BBF-B9F807C63E68}"/>
+    <hyperlink ref="B88" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
+    <hyperlink ref="B23" r:id="rId8" xr:uid="{804D2DB9-BDF1-463B-9BD3-ACBFC15F041A}"/>
+    <hyperlink ref="B59" r:id="rId9" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
+    <hyperlink ref="B75" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
     <hyperlink ref="B19" r:id="rId11" xr:uid="{DF6F8079-E647-4079-9719-72DC2FF3791C}"/>
-    <hyperlink ref="B92" r:id="rId12" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
-    <hyperlink ref="B91" r:id="rId13" xr:uid="{ECCFE763-5E69-4122-B27B-DA1C21FADA86}"/>
+    <hyperlink ref="B99" r:id="rId12" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
+    <hyperlink ref="B96" r:id="rId13" xr:uid="{ECCFE763-5E69-4122-B27B-DA1C21FADA86}"/>
     <hyperlink ref="B2" r:id="rId14" xr:uid="{8869974B-11E2-4A99-8438-9F9B8ABEB9F6}"/>
     <hyperlink ref="B20" r:id="rId15" display="mailto:elizabeth.casarella@gmail.com" xr:uid="{C150E814-8C96-4E50-8A55-5EB3344749B1}"/>
-    <hyperlink ref="B76" r:id="rId16" display="mailto:paul@levelbreaker.com" xr:uid="{9746CC3F-863E-4E18-931A-FADD4ED10BF2}"/>
-    <hyperlink ref="B40" r:id="rId17" xr:uid="{316BCF75-05DF-4572-9F46-9F76127C0677}"/>
-    <hyperlink ref="B63" r:id="rId18" display="mailto:dennis.p.oconnell@gmail.com" xr:uid="{57197F8F-1C51-4977-936A-74B15D239DF7}"/>
-    <hyperlink ref="B58" r:id="rId19" display="mailto:hef714@aol.com" xr:uid="{A4825BC7-F2DD-43E9-A39B-48544C54E403}"/>
-    <hyperlink ref="B64" r:id="rId20" xr:uid="{53A4A1D2-46D5-45C1-BB62-DA92169DD070}"/>
-    <hyperlink ref="B35" r:id="rId21" xr:uid="{A871275A-577B-4F01-A590-B30FBADA40A1}"/>
-    <hyperlink ref="B88" r:id="rId22" xr:uid="{7E7AC9EC-4484-43DC-8B81-7AA0BCCFA407}"/>
-    <hyperlink ref="B49" r:id="rId23" display="mailto:Gjhusky52@yahoo.com" xr:uid="{1F5D9E16-5BA9-4F8F-B8CF-14485F325E5D}"/>
-    <hyperlink ref="B89" r:id="rId24" display="mailto:s.vibberts@yahoo.com" xr:uid="{CD95CA65-C8C5-44B3-8AFC-2E088AEC194C}"/>
-    <hyperlink ref="B70" r:id="rId25" display="mailto:oldparsonage3@gmail.com" xr:uid="{DC8DA8C9-CCEA-4FC3-AA05-1EF34B65B0C1}"/>
-    <hyperlink ref="B42" r:id="rId26" xr:uid="{C2395B48-B35E-4045-A136-C8B31BE4A5FC}"/>
+    <hyperlink ref="B80" r:id="rId16" display="mailto:paul@levelbreaker.com" xr:uid="{9746CC3F-863E-4E18-931A-FADD4ED10BF2}"/>
+    <hyperlink ref="B44" r:id="rId17" xr:uid="{316BCF75-05DF-4572-9F46-9F76127C0677}"/>
+    <hyperlink ref="B67" r:id="rId18" display="mailto:dennis.p.oconnell@gmail.com" xr:uid="{57197F8F-1C51-4977-936A-74B15D239DF7}"/>
+    <hyperlink ref="B62" r:id="rId19" display="mailto:hef714@aol.com" xr:uid="{A4825BC7-F2DD-43E9-A39B-48544C54E403}"/>
+    <hyperlink ref="B68" r:id="rId20" xr:uid="{53A4A1D2-46D5-45C1-BB62-DA92169DD070}"/>
+    <hyperlink ref="B38" r:id="rId21" xr:uid="{A871275A-577B-4F01-A590-B30FBADA40A1}"/>
+    <hyperlink ref="B93" r:id="rId22" xr:uid="{7E7AC9EC-4484-43DC-8B81-7AA0BCCFA407}"/>
+    <hyperlink ref="B53" r:id="rId23" display="mailto:Gjhusky52@yahoo.com" xr:uid="{1F5D9E16-5BA9-4F8F-B8CF-14485F325E5D}"/>
+    <hyperlink ref="B94" r:id="rId24" display="mailto:s.vibberts@yahoo.com" xr:uid="{CD95CA65-C8C5-44B3-8AFC-2E088AEC194C}"/>
+    <hyperlink ref="B74" r:id="rId25" display="mailto:oldparsonage3@gmail.com" xr:uid="{DC8DA8C9-CCEA-4FC3-AA05-1EF34B65B0C1}"/>
+    <hyperlink ref="B46" r:id="rId26" xr:uid="{C2395B48-B35E-4045-A136-C8B31BE4A5FC}"/>
     <hyperlink ref="B6" r:id="rId27" xr:uid="{37F7977A-EC68-4733-8738-6C53C959B816}"/>
     <hyperlink ref="B12" r:id="rId28" display="mailto:cwb84122@gmail.com" xr:uid="{A209B655-7CEF-4F8D-BFEE-DFB49C33870B}"/>
-    <hyperlink ref="B57" r:id="rId29" display="mailto:Npmyers@sbcglobal.net" xr:uid="{46F1EE8C-941D-4D6B-A27A-3BDDA65A15CE}"/>
+    <hyperlink ref="B61" r:id="rId29" display="mailto:Npmyers@sbcglobal.net" xr:uid="{46F1EE8C-941D-4D6B-A27A-3BDDA65A15CE}"/>
     <hyperlink ref="B8" r:id="rId30" xr:uid="{647703FF-1796-4612-923D-2A3CF89F5A46}"/>
-    <hyperlink ref="B28" r:id="rId31" xr:uid="{D4F421DD-A322-4F00-A209-B464A28664A6}"/>
-    <hyperlink ref="B45" r:id="rId32" xr:uid="{5FF15619-CFAB-48CB-8BF0-78013919701C}"/>
-    <hyperlink ref="B53" r:id="rId33" display="mailto:Kmills8080@gmail.com" xr:uid="{6653A4F2-00C8-4ACF-A9B2-950ABB23037C}"/>
-    <hyperlink ref="B47" r:id="rId34" xr:uid="{0F8932AA-3F92-4F04-A82F-C839649C3558}"/>
-    <hyperlink ref="B72" r:id="rId35" xr:uid="{74573551-A238-45F0-95FA-078470676D33}"/>
-    <hyperlink ref="B56" r:id="rId36" xr:uid="{F093A50A-9255-43F2-873A-E61FB97B7B6E}"/>
-    <hyperlink ref="B23" r:id="rId37" display="mailto:joecorbo@icloud.com" xr:uid="{9664FD56-34AE-4697-8A23-BBA8942C6ABA}"/>
-    <hyperlink ref="B29" r:id="rId38" display="mailto:lostdogs@charter.net" xr:uid="{95D046AE-D83E-4029-8E4D-F457CDD3F23E}"/>
-    <hyperlink ref="B26" r:id="rId39" xr:uid="{93D1D532-1D29-4735-B6C3-7B9B46F15302}"/>
-    <hyperlink ref="B43" r:id="rId40" display="mailto:langer0125@gmail.com" xr:uid="{EF3BA7C4-32BE-431A-9979-8B42711B0D73}"/>
-    <hyperlink ref="B85" r:id="rId41" display="mailto:Ntjr05@gmail.com" xr:uid="{38DDEC56-F2AD-4C66-8377-3BFC9B7BDDB9}"/>
-    <hyperlink ref="B79" r:id="rId42" display="mailto:gregsinay3@gmail.com" xr:uid="{004C878C-63EB-40FC-B549-87CFABDE66E1}"/>
-    <hyperlink ref="B39" r:id="rId43" display="mailto:Suj9283@yahoo.com" xr:uid="{E8FF833B-A9E0-4AED-A7DB-065ED67E2244}"/>
-    <hyperlink ref="B66" r:id="rId44" display="mailto:djpal@zoominternet.net" xr:uid="{FAF882CB-F959-4D5E-B4E0-3608ADC9DA13}"/>
-    <hyperlink ref="B81" r:id="rId45" display="mailto:sosikiii@msn.com" xr:uid="{218E6BB5-6D46-4A2B-BD2C-6CF05A021B3C}"/>
-    <hyperlink ref="B46" r:id="rId46" display="mailto:Robertmlunn@gmail.com" xr:uid="{33551D8E-478C-410F-9E21-46488F70F42D}"/>
-    <hyperlink ref="B82" r:id="rId47" display="mailto:brisparks@gmail.com" xr:uid="{E8A49946-13F1-4C59-AD3D-A3E5B9D77EFF}"/>
-    <hyperlink ref="B44" r:id="rId48" display="mailto:Dlew44@gmail.com" xr:uid="{25AC56D9-918C-4162-BE04-DAA69217239F}"/>
+    <hyperlink ref="B29" r:id="rId31" xr:uid="{D4F421DD-A322-4F00-A209-B464A28664A6}"/>
+    <hyperlink ref="B49" r:id="rId32" xr:uid="{5FF15619-CFAB-48CB-8BF0-78013919701C}"/>
+    <hyperlink ref="B57" r:id="rId33" display="mailto:Kmills8080@gmail.com" xr:uid="{6653A4F2-00C8-4ACF-A9B2-950ABB23037C}"/>
+    <hyperlink ref="B51" r:id="rId34" xr:uid="{0F8932AA-3F92-4F04-A82F-C839649C3558}"/>
+    <hyperlink ref="B76" r:id="rId35" xr:uid="{74573551-A238-45F0-95FA-078470676D33}"/>
+    <hyperlink ref="B60" r:id="rId36" xr:uid="{F093A50A-9255-43F2-873A-E61FB97B7B6E}"/>
+    <hyperlink ref="B24" r:id="rId37" display="mailto:joecorbo@icloud.com" xr:uid="{9664FD56-34AE-4697-8A23-BBA8942C6ABA}"/>
+    <hyperlink ref="B30" r:id="rId38" display="mailto:lostdogs@charter.net" xr:uid="{95D046AE-D83E-4029-8E4D-F457CDD3F23E}"/>
+    <hyperlink ref="B27" r:id="rId39" xr:uid="{93D1D532-1D29-4735-B6C3-7B9B46F15302}"/>
+    <hyperlink ref="B47" r:id="rId40" display="mailto:langer0125@gmail.com" xr:uid="{EF3BA7C4-32BE-431A-9979-8B42711B0D73}"/>
+    <hyperlink ref="B90" r:id="rId41" display="mailto:Ntjr05@gmail.com" xr:uid="{38DDEC56-F2AD-4C66-8377-3BFC9B7BDDB9}"/>
+    <hyperlink ref="B83" r:id="rId42" display="mailto:gregsinay3@gmail.com" xr:uid="{004C878C-63EB-40FC-B549-87CFABDE66E1}"/>
+    <hyperlink ref="B43" r:id="rId43" display="mailto:Suj9283@yahoo.com" xr:uid="{E8FF833B-A9E0-4AED-A7DB-065ED67E2244}"/>
+    <hyperlink ref="B70" r:id="rId44" display="mailto:djpal@zoominternet.net" xr:uid="{FAF882CB-F959-4D5E-B4E0-3608ADC9DA13}"/>
+    <hyperlink ref="B85" r:id="rId45" display="mailto:sosikiii@msn.com" xr:uid="{218E6BB5-6D46-4A2B-BD2C-6CF05A021B3C}"/>
+    <hyperlink ref="B50" r:id="rId46" display="mailto:Robertmlunn@gmail.com" xr:uid="{33551D8E-478C-410F-9E21-46488F70F42D}"/>
+    <hyperlink ref="B86" r:id="rId47" display="mailto:brisparks@gmail.com" xr:uid="{E8A49946-13F1-4C59-AD3D-A3E5B9D77EFF}"/>
+    <hyperlink ref="B48" r:id="rId48" display="mailto:Dlew44@gmail.com" xr:uid="{25AC56D9-918C-4162-BE04-DAA69217239F}"/>
     <hyperlink ref="B7" r:id="rId49" xr:uid="{02619D1B-E12D-411C-8267-1EA72D337FA4}"/>
     <hyperlink ref="B14" r:id="rId50" xr:uid="{297F912D-F1B3-4511-B9FB-7F6A5151679A}"/>
     <hyperlink ref="B17" r:id="rId51" xr:uid="{23A72ED8-42A8-4AD2-AED4-16447BAE4A08}"/>
     <hyperlink ref="B18" r:id="rId52" xr:uid="{5484D007-8240-489C-A613-B2C0F0F2AC56}"/>
     <hyperlink ref="B21" r:id="rId53" xr:uid="{D01BE816-0B5A-4446-924C-46E6BAD18108}"/>
-    <hyperlink ref="B33" r:id="rId54" xr:uid="{276C5002-FCF1-4B64-9438-E4287F3F2787}"/>
-    <hyperlink ref="B50" r:id="rId55" xr:uid="{05B37D53-659E-462F-9D42-00105B550079}"/>
-    <hyperlink ref="B51" r:id="rId56" xr:uid="{F7EC428E-8409-4830-9429-9C5E7ABB09A4}"/>
-    <hyperlink ref="B60" r:id="rId57" xr:uid="{EE1C2C4D-03AE-46ED-A073-46B29C8D3689}"/>
-    <hyperlink ref="B80" r:id="rId58" xr:uid="{4C733EB2-A8CB-4A19-80B4-31601DA15BF2}"/>
-    <hyperlink ref="B83" r:id="rId59" xr:uid="{77C5CEA7-AAB7-4C0E-8FED-A2F21F462250}"/>
-    <hyperlink ref="B86" r:id="rId60" display="mailto:ryantimko@hotmail.com" xr:uid="{D3F25966-9FE3-42C3-94BB-54469D722B9E}"/>
-    <hyperlink ref="B38" r:id="rId61" display="mailto:bill.irwin58@gmail.com" xr:uid="{21398664-274B-466E-AEF3-003790919F40}"/>
-    <hyperlink ref="B36" r:id="rId62" display="mailto:Hogan6523@Yahoo.com" xr:uid="{8F033920-5D36-4035-9970-BF7A906D9337}"/>
-    <hyperlink ref="B69" r:id="rId63" display="mailto:justperk2@gmail.com" xr:uid="{3915D652-1507-4F3C-AEB3-935E95D07A08}"/>
-    <hyperlink ref="B65" r:id="rId64" display="mailto:bernard.e.palmer@gmail.com" xr:uid="{4E7DEDEB-BA72-4331-A716-378C6A511DCC}"/>
-    <hyperlink ref="B32" r:id="rId65" display="mailto:fogs14@yahoo.com" xr:uid="{E734B4DB-161E-4386-9BE4-4D2A768C19C0}"/>
+    <hyperlink ref="B36" r:id="rId54" xr:uid="{276C5002-FCF1-4B64-9438-E4287F3F2787}"/>
+    <hyperlink ref="B54" r:id="rId55" xr:uid="{05B37D53-659E-462F-9D42-00105B550079}"/>
+    <hyperlink ref="B55" r:id="rId56" xr:uid="{F7EC428E-8409-4830-9429-9C5E7ABB09A4}"/>
+    <hyperlink ref="B64" r:id="rId57" xr:uid="{EE1C2C4D-03AE-46ED-A073-46B29C8D3689}"/>
+    <hyperlink ref="B84" r:id="rId58" xr:uid="{4C733EB2-A8CB-4A19-80B4-31601DA15BF2}"/>
+    <hyperlink ref="B87" r:id="rId59" xr:uid="{77C5CEA7-AAB7-4C0E-8FED-A2F21F462250}"/>
+    <hyperlink ref="B91" r:id="rId60" display="mailto:ryantimko@hotmail.com" xr:uid="{D3F25966-9FE3-42C3-94BB-54469D722B9E}"/>
+    <hyperlink ref="B41" r:id="rId61" display="mailto:bill.irwin58@gmail.com" xr:uid="{21398664-274B-466E-AEF3-003790919F40}"/>
+    <hyperlink ref="B39" r:id="rId62" display="mailto:Hogan6523@Yahoo.com" xr:uid="{8F033920-5D36-4035-9970-BF7A906D9337}"/>
+    <hyperlink ref="B73" r:id="rId63" display="mailto:justperk2@gmail.com" xr:uid="{3915D652-1507-4F3C-AEB3-935E95D07A08}"/>
+    <hyperlink ref="B69" r:id="rId64" display="mailto:bernard.e.palmer@gmail.com" xr:uid="{4E7DEDEB-BA72-4331-A716-378C6A511DCC}"/>
+    <hyperlink ref="B35" r:id="rId65" display="mailto:fogs14@yahoo.com" xr:uid="{E734B4DB-161E-4386-9BE4-4D2A768C19C0}"/>
     <hyperlink ref="B4" r:id="rId66" display="mailto:Robertalfaro@outlook.com" xr:uid="{94ECE3FB-34A8-40D2-A511-C6F49E1F79C8}"/>
-    <hyperlink ref="B77" r:id="rId67" xr:uid="{8042AEE0-2132-486D-AFC6-008B86CDABF9}"/>
-    <hyperlink ref="B25" r:id="rId68" display="mailto:rmdecambre@gmail.com" xr:uid="{61906EF9-7178-4E37-9EF5-F697B7AF8714}"/>
-    <hyperlink ref="B75" r:id="rId69" xr:uid="{C73311BF-B167-4642-BFA3-507299A38EFE}"/>
+    <hyperlink ref="B81" r:id="rId67" xr:uid="{8042AEE0-2132-486D-AFC6-008B86CDABF9}"/>
+    <hyperlink ref="B26" r:id="rId68" display="mailto:rmdecambre@gmail.com" xr:uid="{61906EF9-7178-4E37-9EF5-F697B7AF8714}"/>
+    <hyperlink ref="B79" r:id="rId69" xr:uid="{C73311BF-B167-4642-BFA3-507299A38EFE}"/>
+    <hyperlink ref="B22" r:id="rId70" xr:uid="{A7D0DDDF-0E1D-4EAA-BC8A-6B20E1097E98}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId70"/>
+  <pageSetup orientation="portrait" r:id="rId71"/>
 </worksheet>
 </file>
--- a/UConnBleedBlue/wwwroot/Data/Players.xlsx
+++ b/UConnBleedBlue/wwwroot/Data/Players.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\UConnBleedBlue\UConnBleedBlue\wwwroot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269C181E-D1DC-4C8F-9047-0B9692242ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48161018-3720-4590-90B4-6C024265ED69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21465" yWindow="1800" windowWidth="21600" windowHeight="13680" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
+    <workbookView xWindow="5910" yWindow="1365" windowWidth="21600" windowHeight="13680" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="219">
   <si>
     <t>Demers, Kenny</t>
   </si>
@@ -164,9 +164,6 @@
     <t>adam@odysseyteencamp.com</t>
   </si>
   <si>
-    <t>Estep, EJ</t>
-  </si>
-  <si>
     <t>michael.estep@acps.k12.va.us</t>
   </si>
   <si>
@@ -668,13 +665,34 @@
     <t>wardlawdoug51@gmail.com</t>
   </si>
   <si>
-    <t>Williams, Brandon</t>
-  </si>
-  <si>
     <t>cwilli6161@gmail.com</t>
   </si>
   <si>
     <t>Robert Ingalls</t>
+  </si>
+  <si>
+    <t>Finkeldey, Drew</t>
+  </si>
+  <si>
+    <t>tfink9@juno.com</t>
+  </si>
+  <si>
+    <t>Estep, Michael`</t>
+  </si>
+  <si>
+    <t>Williams, Courtney</t>
+  </si>
+  <si>
+    <t>Zito, Mike</t>
+  </si>
+  <si>
+    <t>zitomichele128@gmail.com</t>
+  </si>
+  <si>
+    <t>Sullivan, Danny</t>
+  </si>
+  <si>
+    <t>danielle.sullivan@briancenter.org</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F97E2D-D2EE-4E19-AA28-ED70E4256082}">
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" customWidth="1"/>
@@ -1081,7 +1099,7 @@
         <v>33</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>34</v>
@@ -1090,21 +1108,21 @@
         <v>35</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="C2" s="1">
         <v>1977</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -1115,13 +1133,13 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3" s="1">
         <v>1971</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -1129,16 +1147,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="C4" s="1">
         <v>1998</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -1155,7 +1173,7 @@
         <v>1967</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -1163,39 +1181,42 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="C6" s="1">
         <v>1987</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>165</v>
+      <c r="C7" s="1">
+        <v>1988</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1203,13 +1224,13 @@
         <v>11</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C8" s="1">
         <v>1970</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -1217,16 +1238,16 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>190</v>
       </c>
       <c r="C9" s="1">
         <v>1972</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
@@ -1234,16 +1255,16 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>190</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="C10" s="1">
         <v>1972</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -1257,7 +1278,7 @@
         <v>1981</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -1265,16 +1286,16 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="C12" s="1">
         <v>2005</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -1285,39 +1306,39 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C13" s="1">
         <v>1970</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>165</v>
+      <c r="C14" s="1">
+        <v>2015</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1325,13 +1346,13 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
@@ -1348,7 +1369,7 @@
         <v>1998</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
@@ -1359,76 +1380,73 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>154</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="C17" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>156</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>165</v>
+      <c r="C18" s="1">
+        <v>1996</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="C19" s="1">
         <v>1989</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="C20" s="1">
         <v>1969</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
@@ -1436,30 +1454,30 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>158</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>165</v>
+      <c r="C21" s="1">
+        <v>1978</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="E21" t="b">
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>197</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
@@ -1470,13 +1488,13 @@
         <v>6</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
@@ -1484,16 +1502,16 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="C24" s="1">
         <v>1974</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E24" t="b">
         <v>1</v>
@@ -1504,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C25" s="1">
         <v>1982</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
@@ -1518,16 +1536,16 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="C26" s="1">
         <v>1977</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E26" t="b">
         <v>1</v>
@@ -1535,22 +1553,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="C27" s="1">
         <v>1977</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1558,13 +1576,13 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C28" s="1">
         <v>1964</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
@@ -1575,13 +1593,13 @@
         <v>0</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C29" s="1">
         <v>1969</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
@@ -1589,36 +1607,36 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="C30" s="1">
         <v>1993</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E30" t="b">
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>213</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="C31" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
@@ -1626,10 +1644,16 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>199</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>201</v>
+      <c r="C32" s="1">
+        <v>1997</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
@@ -1637,10 +1661,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>201</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>203</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
@@ -1648,16 +1672,16 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" t="s">
-        <v>95</v>
+        <v>211</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="C34" s="1">
-        <v>1979</v>
+        <v>1982</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
@@ -1665,16 +1689,16 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>183</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>184</v>
+        <v>23</v>
+      </c>
+      <c r="B35" t="s">
+        <v>94</v>
       </c>
       <c r="C35" s="1">
-        <v>2005</v>
+        <v>1979</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E35" t="b">
         <v>1</v>
@@ -1682,70 +1706,67 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>165</v>
+        <v>183</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2005</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
-      </c>
-      <c r="G36" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" s="1">
-        <v>1971</v>
+        <v>160</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
+      </c>
+      <c r="G37" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>71</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>72</v>
+        <v>4</v>
+      </c>
+      <c r="B38" t="s">
+        <v>95</v>
       </c>
       <c r="C38" s="1">
-        <v>1993</v>
+        <v>1971</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
-      </c>
-      <c r="G38" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>177</v>
+        <v>70</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>178</v>
+        <v>71</v>
       </c>
       <c r="C39" s="1">
-        <v>1970</v>
+        <v>1993</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>143</v>
@@ -1753,22 +1774,19 @@
       <c r="E39" t="b">
         <v>1</v>
       </c>
-      <c r="F39" t="b">
-        <v>1</v>
-      </c>
       <c r="G39" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" t="s">
-        <v>97</v>
+        <v>176</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="C40" s="1">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>142</v>
@@ -1776,50 +1794,62 @@
       <c r="E40" t="b">
         <v>1</v>
       </c>
+      <c r="F40" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>175</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>176</v>
+        <v>19</v>
+      </c>
+      <c r="B41" t="s">
+        <v>96</v>
       </c>
       <c r="C41" s="1">
-        <v>2004</v>
+        <v>1972</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E41" t="b">
-        <v>1</v>
-      </c>
-      <c r="F41" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>205</v>
+        <v>175</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2004</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="E42" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>125</v>
+        <v>203</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>126</v>
+        <v>204</v>
       </c>
       <c r="C43" s="1">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E43" t="b">
         <v>1</v>
@@ -1827,16 +1857,16 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="C44" s="1">
-        <v>1979</v>
+        <v>1995</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E44" t="b">
         <v>1</v>
@@ -1844,16 +1874,16 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>20</v>
-      </c>
-      <c r="B45" t="s">
-        <v>98</v>
+        <v>62</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="C45" s="1">
         <v>1979</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E45" t="b">
         <v>1</v>
@@ -1861,16 +1891,16 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>82</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>83</v>
+        <v>20</v>
+      </c>
+      <c r="B46" t="s">
+        <v>97</v>
       </c>
       <c r="C46" s="1">
-        <v>1986</v>
+        <v>1979</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
@@ -1878,90 +1908,90 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="C47" s="1">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
-      </c>
-      <c r="G47" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="C48" s="1">
-        <v>1994</v>
+        <v>1982</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E48" t="b">
         <v>1</v>
+      </c>
+      <c r="G48" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="C49" s="1">
-        <v>1982</v>
+        <v>1994</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E49" t="b">
         <v>1</v>
-      </c>
-      <c r="G49" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="C50" s="1">
-        <v>2008</v>
+        <v>1982</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E50" t="b">
         <v>1</v>
+      </c>
+      <c r="G50" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>165</v>
+        <v>133</v>
+      </c>
+      <c r="C51" s="1">
+        <v>2008</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E51" t="b">
         <v>1</v>
@@ -1969,16 +1999,16 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>2</v>
-      </c>
-      <c r="B52" t="s">
-        <v>100</v>
-      </c>
-      <c r="C52" s="1">
-        <v>1987</v>
+        <v>74</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="E52" t="b">
         <v>1</v>
@@ -1986,53 +2016,50 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>77</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>78</v>
+        <v>2</v>
+      </c>
+      <c r="B53" t="s">
+        <v>99</v>
       </c>
       <c r="C53" s="1">
-        <v>1981</v>
+        <v>1987</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E53" t="b">
         <v>1</v>
-      </c>
-      <c r="G53" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="C54" s="1">
-        <v>1973</v>
+        <v>1981</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E54" t="b">
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C55" s="1">
-        <v>1978</v>
+        <v>1973</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>140</v>
@@ -2041,75 +2068,78 @@
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="C56" s="1">
-        <v>1989</v>
+        <v>1978</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E56" t="b">
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="C57" s="1">
-        <v>1981</v>
+        <v>1989</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E57" t="b">
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>25</v>
-      </c>
-      <c r="B58" t="s">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="C58" s="1">
-        <v>1986</v>
+        <v>1981</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E58" t="b">
         <v>1</v>
+      </c>
+      <c r="G58" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>47</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>48</v>
+        <v>25</v>
+      </c>
+      <c r="B59" t="s">
+        <v>100</v>
       </c>
       <c r="C59" s="1">
-        <v>1966</v>
+        <v>1986</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>143</v>
@@ -2117,59 +2147,59 @@
       <c r="E59" t="b">
         <v>1</v>
       </c>
-      <c r="G59" t="s">
-        <v>150</v>
-      </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>112</v>
+        <v>47</v>
       </c>
       <c r="C60" s="1">
-        <v>1992</v>
+        <v>1966</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E60" t="b">
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="C61" s="1">
-        <v>1984</v>
+        <v>1992</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E61" t="b">
         <v>1</v>
+      </c>
+      <c r="G61" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="C62" s="1">
-        <v>1979</v>
+        <v>1984</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E62" t="b">
         <v>1</v>
@@ -2177,16 +2207,16 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>24</v>
-      </c>
-      <c r="B63" t="s">
-        <v>102</v>
+        <v>66</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="C63" s="1">
         <v>1979</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E63" t="b">
         <v>1</v>
@@ -2194,87 +2224,87 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>168</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>169</v>
+        <v>24</v>
+      </c>
+      <c r="B64" t="s">
+        <v>101</v>
+      </c>
+      <c r="C64" s="1">
+        <v>1979</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="E64" t="b">
         <v>1</v>
-      </c>
-      <c r="G64" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1</v>
-      </c>
-      <c r="B65" t="s">
-        <v>105</v>
-      </c>
-      <c r="C65" s="1">
-        <v>1970</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>143</v>
+        <v>167</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="E65" t="b">
         <v>1</v>
       </c>
       <c r="G65" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B66" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C66" s="1">
-        <v>2015</v>
+        <v>1970</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E66" t="b">
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>65</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>66</v>
+        <v>3</v>
+      </c>
+      <c r="B67" t="s">
+        <v>105</v>
       </c>
       <c r="C67" s="1">
-        <v>1978</v>
+        <v>2015</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E67" t="b">
         <v>1</v>
+      </c>
+      <c r="G67" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C68" s="1">
-        <v>1974</v>
+        <v>1978</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E68" t="b">
         <v>1</v>
@@ -2282,16 +2312,16 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>181</v>
+        <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>182</v>
+        <v>69</v>
       </c>
       <c r="C69" s="1">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E69" t="b">
         <v>1</v>
@@ -2299,13 +2329,13 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>127</v>
+        <v>180</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>128</v>
+        <v>181</v>
       </c>
       <c r="C70" s="1">
-        <v>1980</v>
+        <v>1976</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>140</v>
@@ -2316,16 +2346,16 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>7</v>
-      </c>
-      <c r="B71" t="s">
-        <v>107</v>
+        <v>126</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>127</v>
       </c>
       <c r="C71" s="1">
-        <v>1969</v>
+        <v>1980</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E71" t="b">
         <v>1</v>
@@ -2333,53 +2363,53 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>36</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>165</v>
+        <v>7</v>
+      </c>
+      <c r="B72" t="s">
+        <v>106</v>
+      </c>
+      <c r="C72" s="1">
+        <v>1969</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="E72" t="b">
         <v>1</v>
-      </c>
-      <c r="G72" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>179</v>
+        <v>36</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C73" s="1">
-        <v>2004</v>
+        <v>37</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="E73" t="b">
         <v>1</v>
+      </c>
+      <c r="G73" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>81</v>
+        <v>178</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="C74" s="1">
-        <v>1968</v>
+        <v>2004</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E74" t="b">
         <v>1</v>
@@ -2387,13 +2417,13 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="C75" s="1">
-        <v>1971</v>
+        <v>1968</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>142</v>
@@ -2404,73 +2434,73 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="C76" s="1">
-        <v>1985</v>
+        <v>1971</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E76" t="b">
         <v>1</v>
-      </c>
-      <c r="G76" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="C77" s="1">
-        <v>1975</v>
+        <v>1985</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E77" t="b">
         <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>13</v>
-      </c>
-      <c r="B78" t="s">
-        <v>109</v>
+        <v>38</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="C78" s="1">
-        <v>1970</v>
+        <v>1975</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E78" t="b">
         <v>1</v>
+      </c>
+      <c r="G78" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>195</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>196</v>
+        <v>13</v>
+      </c>
+      <c r="B79" t="s">
+        <v>108</v>
       </c>
       <c r="C79" s="1">
-        <v>1995</v>
+        <v>1970</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E79" t="b">
         <v>1</v>
@@ -2478,178 +2508,190 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>62</v>
+        <v>195</v>
       </c>
       <c r="C80" s="1">
-        <v>1975</v>
+        <v>1995</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E80" t="b">
         <v>1</v>
-      </c>
-      <c r="G80" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>188</v>
+        <v>61</v>
       </c>
       <c r="C81" s="1">
-        <v>1963</v>
+        <v>1975</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>212</v>
+        <v>140</v>
       </c>
       <c r="E81" t="b">
         <v>1</v>
+      </c>
+      <c r="G81" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>40</v>
+        <v>186</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>165</v>
+        <v>187</v>
+      </c>
+      <c r="C82" s="1">
+        <v>1963</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>165</v>
+        <v>210</v>
       </c>
       <c r="E82" t="b">
         <v>1</v>
-      </c>
-      <c r="G82" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>123</v>
+        <v>40</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C83" s="1">
-        <v>1976</v>
+        <v>41</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="E83" t="b">
         <v>1</v>
       </c>
       <c r="G83" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>170</v>
+        <v>122</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>171</v>
+        <v>123</v>
+      </c>
+      <c r="C84" s="1">
+        <v>1976</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="E84" t="b">
         <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="C85" s="1">
-        <v>1993</v>
+        <v>1967</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E85" t="b">
         <v>1</v>
       </c>
       <c r="G85" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C86" s="1">
-        <v>2004</v>
+        <v>1993</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E86" t="b">
         <v>1</v>
       </c>
       <c r="G86" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="C87" s="1">
-        <v>1976</v>
+        <v>2004</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E87" t="b">
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>44</v>
+        <v>171</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>45</v>
+        <v>172</v>
       </c>
       <c r="C88" s="1">
-        <v>1970</v>
+        <v>1976</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E88" t="b">
         <v>1</v>
+      </c>
+      <c r="G88" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>206</v>
+        <v>43</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>207</v>
+        <v>44</v>
+      </c>
+      <c r="C89" s="1">
+        <v>1970</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="E89" t="b">
         <v>1</v>
@@ -2657,36 +2699,27 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>121</v>
+        <v>205</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C90" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>148</v>
+        <v>206</v>
       </c>
       <c r="E90" t="b">
         <v>1</v>
-      </c>
-      <c r="G90" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="C91" s="1">
-        <v>2000</v>
+        <v>1970</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E91" t="b">
         <v>1</v>
@@ -2694,36 +2727,36 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>17</v>
-      </c>
-      <c r="B92" t="s">
-        <v>110</v>
+        <v>120</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="C92" s="1">
-        <v>1969</v>
+        <v>2016</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E92" t="b">
         <v>1</v>
       </c>
       <c r="G92" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>73</v>
+        <v>196</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>74</v>
+        <v>173</v>
       </c>
       <c r="C93" s="1">
-        <v>1975</v>
+        <v>2000</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E93" t="b">
         <v>1</v>
@@ -2731,27 +2764,33 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>9</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>79</v>
+        <v>17</v>
+      </c>
+      <c r="B94" t="s">
+        <v>109</v>
       </c>
       <c r="C94" s="1">
-        <v>1989</v>
+        <v>1969</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E94" t="b">
         <v>1</v>
+      </c>
+      <c r="G94" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>22</v>
+        <v>72</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="C95" s="1">
-        <v>1979</v>
+        <v>1975</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>140</v>
@@ -2762,30 +2801,30 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="C96" s="1">
-        <v>2006</v>
+        <v>1989</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E96" t="b">
         <v>1</v>
-      </c>
-      <c r="G96" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>208</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>209</v>
+        <v>22</v>
+      </c>
+      <c r="C97" s="1">
+        <v>1979</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="E97" t="b">
         <v>1</v>
@@ -2793,109 +2832,175 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>210</v>
+        <v>55</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>211</v>
+        <v>56</v>
+      </c>
+      <c r="C98" s="1">
+        <v>2006</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="E98" t="b">
         <v>1</v>
+      </c>
+      <c r="G98" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>207</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C99" s="1">
+        <v>2019</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E99" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>214</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C100" s="1">
+        <v>1998</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>51</v>
+      </c>
+      <c r="B101" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C99" s="1">
+      <c r="C101" s="1">
         <v>1975</v>
       </c>
-      <c r="D99" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E99" t="b">
-        <v>1</v>
-      </c>
-      <c r="G99" t="s">
-        <v>150</v>
+      <c r="D101" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E101" t="b">
+        <v>1</v>
+      </c>
+      <c r="G101" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>215</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C102" s="1">
+        <v>1970</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E102" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B5" r:id="rId1" xr:uid="{8227A597-9225-4357-B8B6-9F19CC6D2D47}"/>
     <hyperlink ref="B16" r:id="rId2" xr:uid="{C440EE30-529A-4080-AE83-A4A978C3E02B}"/>
-    <hyperlink ref="B72" r:id="rId3" xr:uid="{C5FAAB38-5F1C-4A08-8709-401E7E23E0D1}"/>
-    <hyperlink ref="B77" r:id="rId4" xr:uid="{109EA93A-660A-4099-B212-FD77BC4B5297}"/>
-    <hyperlink ref="B82" r:id="rId5" xr:uid="{4FC29F3F-346D-4C86-81DD-BA31CA08B134}"/>
+    <hyperlink ref="B73" r:id="rId3" xr:uid="{C5FAAB38-5F1C-4A08-8709-401E7E23E0D1}"/>
+    <hyperlink ref="B78" r:id="rId4" xr:uid="{109EA93A-660A-4099-B212-FD77BC4B5297}"/>
+    <hyperlink ref="B83" r:id="rId5" xr:uid="{4FC29F3F-346D-4C86-81DD-BA31CA08B134}"/>
     <hyperlink ref="B31" r:id="rId6" xr:uid="{98703E9F-F4A5-4829-8BBF-B9F807C63E68}"/>
-    <hyperlink ref="B88" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
+    <hyperlink ref="B89" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
     <hyperlink ref="B23" r:id="rId8" xr:uid="{804D2DB9-BDF1-463B-9BD3-ACBFC15F041A}"/>
-    <hyperlink ref="B59" r:id="rId9" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
-    <hyperlink ref="B75" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
+    <hyperlink ref="B60" r:id="rId9" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
+    <hyperlink ref="B76" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
     <hyperlink ref="B19" r:id="rId11" xr:uid="{DF6F8079-E647-4079-9719-72DC2FF3791C}"/>
-    <hyperlink ref="B99" r:id="rId12" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
-    <hyperlink ref="B96" r:id="rId13" xr:uid="{ECCFE763-5E69-4122-B27B-DA1C21FADA86}"/>
+    <hyperlink ref="B101" r:id="rId12" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
+    <hyperlink ref="B98" r:id="rId13" xr:uid="{ECCFE763-5E69-4122-B27B-DA1C21FADA86}"/>
     <hyperlink ref="B2" r:id="rId14" xr:uid="{8869974B-11E2-4A99-8438-9F9B8ABEB9F6}"/>
     <hyperlink ref="B20" r:id="rId15" display="mailto:elizabeth.casarella@gmail.com" xr:uid="{C150E814-8C96-4E50-8A55-5EB3344749B1}"/>
-    <hyperlink ref="B80" r:id="rId16" display="mailto:paul@levelbreaker.com" xr:uid="{9746CC3F-863E-4E18-931A-FADD4ED10BF2}"/>
-    <hyperlink ref="B44" r:id="rId17" xr:uid="{316BCF75-05DF-4572-9F46-9F76127C0677}"/>
-    <hyperlink ref="B67" r:id="rId18" display="mailto:dennis.p.oconnell@gmail.com" xr:uid="{57197F8F-1C51-4977-936A-74B15D239DF7}"/>
-    <hyperlink ref="B62" r:id="rId19" display="mailto:hef714@aol.com" xr:uid="{A4825BC7-F2DD-43E9-A39B-48544C54E403}"/>
-    <hyperlink ref="B68" r:id="rId20" xr:uid="{53A4A1D2-46D5-45C1-BB62-DA92169DD070}"/>
-    <hyperlink ref="B38" r:id="rId21" xr:uid="{A871275A-577B-4F01-A590-B30FBADA40A1}"/>
-    <hyperlink ref="B93" r:id="rId22" xr:uid="{7E7AC9EC-4484-43DC-8B81-7AA0BCCFA407}"/>
-    <hyperlink ref="B53" r:id="rId23" display="mailto:Gjhusky52@yahoo.com" xr:uid="{1F5D9E16-5BA9-4F8F-B8CF-14485F325E5D}"/>
-    <hyperlink ref="B94" r:id="rId24" display="mailto:s.vibberts@yahoo.com" xr:uid="{CD95CA65-C8C5-44B3-8AFC-2E088AEC194C}"/>
-    <hyperlink ref="B74" r:id="rId25" display="mailto:oldparsonage3@gmail.com" xr:uid="{DC8DA8C9-CCEA-4FC3-AA05-1EF34B65B0C1}"/>
-    <hyperlink ref="B46" r:id="rId26" xr:uid="{C2395B48-B35E-4045-A136-C8B31BE4A5FC}"/>
+    <hyperlink ref="B81" r:id="rId16" display="mailto:paul@levelbreaker.com" xr:uid="{9746CC3F-863E-4E18-931A-FADD4ED10BF2}"/>
+    <hyperlink ref="B45" r:id="rId17" xr:uid="{316BCF75-05DF-4572-9F46-9F76127C0677}"/>
+    <hyperlink ref="B68" r:id="rId18" display="mailto:dennis.p.oconnell@gmail.com" xr:uid="{57197F8F-1C51-4977-936A-74B15D239DF7}"/>
+    <hyperlink ref="B63" r:id="rId19" display="mailto:hef714@aol.com" xr:uid="{A4825BC7-F2DD-43E9-A39B-48544C54E403}"/>
+    <hyperlink ref="B69" r:id="rId20" xr:uid="{53A4A1D2-46D5-45C1-BB62-DA92169DD070}"/>
+    <hyperlink ref="B39" r:id="rId21" xr:uid="{A871275A-577B-4F01-A590-B30FBADA40A1}"/>
+    <hyperlink ref="B95" r:id="rId22" xr:uid="{7E7AC9EC-4484-43DC-8B81-7AA0BCCFA407}"/>
+    <hyperlink ref="B54" r:id="rId23" display="mailto:Gjhusky52@yahoo.com" xr:uid="{1F5D9E16-5BA9-4F8F-B8CF-14485F325E5D}"/>
+    <hyperlink ref="B96" r:id="rId24" display="mailto:s.vibberts@yahoo.com" xr:uid="{CD95CA65-C8C5-44B3-8AFC-2E088AEC194C}"/>
+    <hyperlink ref="B75" r:id="rId25" display="mailto:oldparsonage3@gmail.com" xr:uid="{DC8DA8C9-CCEA-4FC3-AA05-1EF34B65B0C1}"/>
+    <hyperlink ref="B47" r:id="rId26" xr:uid="{C2395B48-B35E-4045-A136-C8B31BE4A5FC}"/>
     <hyperlink ref="B6" r:id="rId27" xr:uid="{37F7977A-EC68-4733-8738-6C53C959B816}"/>
     <hyperlink ref="B12" r:id="rId28" display="mailto:cwb84122@gmail.com" xr:uid="{A209B655-7CEF-4F8D-BFEE-DFB49C33870B}"/>
-    <hyperlink ref="B61" r:id="rId29" display="mailto:Npmyers@sbcglobal.net" xr:uid="{46F1EE8C-941D-4D6B-A27A-3BDDA65A15CE}"/>
+    <hyperlink ref="B62" r:id="rId29" display="mailto:Npmyers@sbcglobal.net" xr:uid="{46F1EE8C-941D-4D6B-A27A-3BDDA65A15CE}"/>
     <hyperlink ref="B8" r:id="rId30" xr:uid="{647703FF-1796-4612-923D-2A3CF89F5A46}"/>
     <hyperlink ref="B29" r:id="rId31" xr:uid="{D4F421DD-A322-4F00-A209-B464A28664A6}"/>
-    <hyperlink ref="B49" r:id="rId32" xr:uid="{5FF15619-CFAB-48CB-8BF0-78013919701C}"/>
-    <hyperlink ref="B57" r:id="rId33" display="mailto:Kmills8080@gmail.com" xr:uid="{6653A4F2-00C8-4ACF-A9B2-950ABB23037C}"/>
-    <hyperlink ref="B51" r:id="rId34" xr:uid="{0F8932AA-3F92-4F04-A82F-C839649C3558}"/>
-    <hyperlink ref="B76" r:id="rId35" xr:uid="{74573551-A238-45F0-95FA-078470676D33}"/>
-    <hyperlink ref="B60" r:id="rId36" xr:uid="{F093A50A-9255-43F2-873A-E61FB97B7B6E}"/>
+    <hyperlink ref="B50" r:id="rId32" xr:uid="{5FF15619-CFAB-48CB-8BF0-78013919701C}"/>
+    <hyperlink ref="B58" r:id="rId33" display="mailto:Kmills8080@gmail.com" xr:uid="{6653A4F2-00C8-4ACF-A9B2-950ABB23037C}"/>
+    <hyperlink ref="B52" r:id="rId34" xr:uid="{0F8932AA-3F92-4F04-A82F-C839649C3558}"/>
+    <hyperlink ref="B77" r:id="rId35" xr:uid="{74573551-A238-45F0-95FA-078470676D33}"/>
+    <hyperlink ref="B61" r:id="rId36" xr:uid="{F093A50A-9255-43F2-873A-E61FB97B7B6E}"/>
     <hyperlink ref="B24" r:id="rId37" display="mailto:joecorbo@icloud.com" xr:uid="{9664FD56-34AE-4697-8A23-BBA8942C6ABA}"/>
     <hyperlink ref="B30" r:id="rId38" display="mailto:lostdogs@charter.net" xr:uid="{95D046AE-D83E-4029-8E4D-F457CDD3F23E}"/>
     <hyperlink ref="B27" r:id="rId39" xr:uid="{93D1D532-1D29-4735-B6C3-7B9B46F15302}"/>
-    <hyperlink ref="B47" r:id="rId40" display="mailto:langer0125@gmail.com" xr:uid="{EF3BA7C4-32BE-431A-9979-8B42711B0D73}"/>
-    <hyperlink ref="B90" r:id="rId41" display="mailto:Ntjr05@gmail.com" xr:uid="{38DDEC56-F2AD-4C66-8377-3BFC9B7BDDB9}"/>
-    <hyperlink ref="B83" r:id="rId42" display="mailto:gregsinay3@gmail.com" xr:uid="{004C878C-63EB-40FC-B549-87CFABDE66E1}"/>
-    <hyperlink ref="B43" r:id="rId43" display="mailto:Suj9283@yahoo.com" xr:uid="{E8FF833B-A9E0-4AED-A7DB-065ED67E2244}"/>
-    <hyperlink ref="B70" r:id="rId44" display="mailto:djpal@zoominternet.net" xr:uid="{FAF882CB-F959-4D5E-B4E0-3608ADC9DA13}"/>
-    <hyperlink ref="B85" r:id="rId45" display="mailto:sosikiii@msn.com" xr:uid="{218E6BB5-6D46-4A2B-BD2C-6CF05A021B3C}"/>
-    <hyperlink ref="B50" r:id="rId46" display="mailto:Robertmlunn@gmail.com" xr:uid="{33551D8E-478C-410F-9E21-46488F70F42D}"/>
-    <hyperlink ref="B86" r:id="rId47" display="mailto:brisparks@gmail.com" xr:uid="{E8A49946-13F1-4C59-AD3D-A3E5B9D77EFF}"/>
-    <hyperlink ref="B48" r:id="rId48" display="mailto:Dlew44@gmail.com" xr:uid="{25AC56D9-918C-4162-BE04-DAA69217239F}"/>
+    <hyperlink ref="B48" r:id="rId40" display="mailto:langer0125@gmail.com" xr:uid="{EF3BA7C4-32BE-431A-9979-8B42711B0D73}"/>
+    <hyperlink ref="B92" r:id="rId41" display="mailto:Ntjr05@gmail.com" xr:uid="{38DDEC56-F2AD-4C66-8377-3BFC9B7BDDB9}"/>
+    <hyperlink ref="B84" r:id="rId42" display="mailto:gregsinay3@gmail.com" xr:uid="{004C878C-63EB-40FC-B549-87CFABDE66E1}"/>
+    <hyperlink ref="B44" r:id="rId43" display="mailto:Suj9283@yahoo.com" xr:uid="{E8FF833B-A9E0-4AED-A7DB-065ED67E2244}"/>
+    <hyperlink ref="B71" r:id="rId44" display="mailto:djpal@zoominternet.net" xr:uid="{FAF882CB-F959-4D5E-B4E0-3608ADC9DA13}"/>
+    <hyperlink ref="B86" r:id="rId45" display="mailto:sosikiii@msn.com" xr:uid="{218E6BB5-6D46-4A2B-BD2C-6CF05A021B3C}"/>
+    <hyperlink ref="B51" r:id="rId46" display="mailto:Robertmlunn@gmail.com" xr:uid="{33551D8E-478C-410F-9E21-46488F70F42D}"/>
+    <hyperlink ref="B87" r:id="rId47" display="mailto:brisparks@gmail.com" xr:uid="{E8A49946-13F1-4C59-AD3D-A3E5B9D77EFF}"/>
+    <hyperlink ref="B49" r:id="rId48" display="mailto:Dlew44@gmail.com" xr:uid="{25AC56D9-918C-4162-BE04-DAA69217239F}"/>
     <hyperlink ref="B7" r:id="rId49" xr:uid="{02619D1B-E12D-411C-8267-1EA72D337FA4}"/>
     <hyperlink ref="B14" r:id="rId50" xr:uid="{297F912D-F1B3-4511-B9FB-7F6A5151679A}"/>
     <hyperlink ref="B17" r:id="rId51" xr:uid="{23A72ED8-42A8-4AD2-AED4-16447BAE4A08}"/>
     <hyperlink ref="B18" r:id="rId52" xr:uid="{5484D007-8240-489C-A613-B2C0F0F2AC56}"/>
     <hyperlink ref="B21" r:id="rId53" xr:uid="{D01BE816-0B5A-4446-924C-46E6BAD18108}"/>
-    <hyperlink ref="B36" r:id="rId54" xr:uid="{276C5002-FCF1-4B64-9438-E4287F3F2787}"/>
-    <hyperlink ref="B54" r:id="rId55" xr:uid="{05B37D53-659E-462F-9D42-00105B550079}"/>
-    <hyperlink ref="B55" r:id="rId56" xr:uid="{F7EC428E-8409-4830-9429-9C5E7ABB09A4}"/>
-    <hyperlink ref="B64" r:id="rId57" xr:uid="{EE1C2C4D-03AE-46ED-A073-46B29C8D3689}"/>
-    <hyperlink ref="B84" r:id="rId58" xr:uid="{4C733EB2-A8CB-4A19-80B4-31601DA15BF2}"/>
-    <hyperlink ref="B87" r:id="rId59" xr:uid="{77C5CEA7-AAB7-4C0E-8FED-A2F21F462250}"/>
-    <hyperlink ref="B91" r:id="rId60" display="mailto:ryantimko@hotmail.com" xr:uid="{D3F25966-9FE3-42C3-94BB-54469D722B9E}"/>
-    <hyperlink ref="B41" r:id="rId61" display="mailto:bill.irwin58@gmail.com" xr:uid="{21398664-274B-466E-AEF3-003790919F40}"/>
-    <hyperlink ref="B39" r:id="rId62" display="mailto:Hogan6523@Yahoo.com" xr:uid="{8F033920-5D36-4035-9970-BF7A906D9337}"/>
-    <hyperlink ref="B73" r:id="rId63" display="mailto:justperk2@gmail.com" xr:uid="{3915D652-1507-4F3C-AEB3-935E95D07A08}"/>
-    <hyperlink ref="B69" r:id="rId64" display="mailto:bernard.e.palmer@gmail.com" xr:uid="{4E7DEDEB-BA72-4331-A716-378C6A511DCC}"/>
-    <hyperlink ref="B35" r:id="rId65" display="mailto:fogs14@yahoo.com" xr:uid="{E734B4DB-161E-4386-9BE4-4D2A768C19C0}"/>
+    <hyperlink ref="B37" r:id="rId54" xr:uid="{276C5002-FCF1-4B64-9438-E4287F3F2787}"/>
+    <hyperlink ref="B55" r:id="rId55" xr:uid="{05B37D53-659E-462F-9D42-00105B550079}"/>
+    <hyperlink ref="B56" r:id="rId56" xr:uid="{F7EC428E-8409-4830-9429-9C5E7ABB09A4}"/>
+    <hyperlink ref="B65" r:id="rId57" xr:uid="{EE1C2C4D-03AE-46ED-A073-46B29C8D3689}"/>
+    <hyperlink ref="B85" r:id="rId58" xr:uid="{4C733EB2-A8CB-4A19-80B4-31601DA15BF2}"/>
+    <hyperlink ref="B88" r:id="rId59" xr:uid="{77C5CEA7-AAB7-4C0E-8FED-A2F21F462250}"/>
+    <hyperlink ref="B93" r:id="rId60" display="mailto:ryantimko@hotmail.com" xr:uid="{D3F25966-9FE3-42C3-94BB-54469D722B9E}"/>
+    <hyperlink ref="B42" r:id="rId61" display="mailto:bill.irwin58@gmail.com" xr:uid="{21398664-274B-466E-AEF3-003790919F40}"/>
+    <hyperlink ref="B40" r:id="rId62" display="mailto:Hogan6523@Yahoo.com" xr:uid="{8F033920-5D36-4035-9970-BF7A906D9337}"/>
+    <hyperlink ref="B74" r:id="rId63" display="mailto:justperk2@gmail.com" xr:uid="{3915D652-1507-4F3C-AEB3-935E95D07A08}"/>
+    <hyperlink ref="B70" r:id="rId64" display="mailto:bernard.e.palmer@gmail.com" xr:uid="{4E7DEDEB-BA72-4331-A716-378C6A511DCC}"/>
+    <hyperlink ref="B36" r:id="rId65" display="mailto:fogs14@yahoo.com" xr:uid="{E734B4DB-161E-4386-9BE4-4D2A768C19C0}"/>
     <hyperlink ref="B4" r:id="rId66" display="mailto:Robertalfaro@outlook.com" xr:uid="{94ECE3FB-34A8-40D2-A511-C6F49E1F79C8}"/>
-    <hyperlink ref="B81" r:id="rId67" xr:uid="{8042AEE0-2132-486D-AFC6-008B86CDABF9}"/>
+    <hyperlink ref="B82" r:id="rId67" xr:uid="{8042AEE0-2132-486D-AFC6-008B86CDABF9}"/>
     <hyperlink ref="B26" r:id="rId68" display="mailto:rmdecambre@gmail.com" xr:uid="{61906EF9-7178-4E37-9EF5-F697B7AF8714}"/>
-    <hyperlink ref="B79" r:id="rId69" xr:uid="{C73311BF-B167-4642-BFA3-507299A38EFE}"/>
+    <hyperlink ref="B80" r:id="rId69" xr:uid="{C73311BF-B167-4642-BFA3-507299A38EFE}"/>
     <hyperlink ref="B22" r:id="rId70" xr:uid="{A7D0DDDF-0E1D-4EAA-BC8A-6B20E1097E98}"/>
+    <hyperlink ref="B34" r:id="rId71" display="mailto:tfink9@juno.com" xr:uid="{34A73A04-8440-48B2-9348-0E4A6602D420}"/>
+    <hyperlink ref="B33" r:id="rId72" xr:uid="{0BB6B871-9927-4DD2-B508-224D22FD6229}"/>
+    <hyperlink ref="B90" r:id="rId73" xr:uid="{6DBAAB43-CE57-45EC-BCA9-CB408BBC84B6}"/>
+    <hyperlink ref="B99" r:id="rId74" xr:uid="{DB8385C7-8934-4CD0-B87E-4D74991BD43E}"/>
+    <hyperlink ref="B102" r:id="rId75" xr:uid="{CEB5326F-2589-4355-9CCD-6A3D6FC84E4A}"/>
+    <hyperlink ref="B91" r:id="rId76" xr:uid="{4A20E15A-8219-4697-83CE-53E329D1A594}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId71"/>
+  <pageSetup orientation="portrait" r:id="rId77"/>
 </worksheet>
 </file>
--- a/UConnBleedBlue/wwwroot/Data/Players.xlsx
+++ b/UConnBleedBlue/wwwroot/Data/Players.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\UConnBleedBlue\UConnBleedBlue\wwwroot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48161018-3720-4590-90B4-6C024265ED69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5621FBBB-6759-4E49-A8C1-1C1714F16EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5910" yWindow="1365" windowWidth="21600" windowHeight="13680" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
+    <workbookView xWindow="3675" yWindow="1800" windowWidth="21600" windowHeight="13680" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="225">
   <si>
     <t>Demers, Kenny</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Nwokeji, Paul</t>
   </si>
   <si>
-    <t>Gorski, Skip</t>
-  </si>
-  <si>
     <t>Branning, Scott</t>
   </si>
   <si>
@@ -230,9 +227,6 @@
     <t>Drjpkonecny@gmail.com</t>
   </si>
   <si>
-    <t>O'Connel, Dennis</t>
-  </si>
-  <si>
     <t>dennis.p.oconnell@gmail.com</t>
   </si>
   <si>
@@ -323,9 +317,6 @@
     <t>marksflood1@gmail.com</t>
   </si>
   <si>
-    <t>gragmgorski@yahoo.com</t>
-  </si>
-  <si>
     <t>robertinnis@yahoo.com</t>
   </si>
   <si>
@@ -485,9 +476,6 @@
     <t>Tickets</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>Antrum, Glenn</t>
   </si>
   <si>
@@ -608,9 +596,6 @@
     <t>rbacewicz@aol.com</t>
   </si>
   <si>
-    <t>Bacewice, Joe</t>
-  </si>
-  <si>
     <t>j.bacewicz@comcast.net</t>
   </si>
   <si>
@@ -693,6 +678,39 @@
   </si>
   <si>
     <t>danielle.sullivan@briancenter.org</t>
+  </si>
+  <si>
+    <t>Draper, David</t>
+  </si>
+  <si>
+    <t>dbdraper234@gmail.com</t>
+  </si>
+  <si>
+    <t>Francois, Jeffrey</t>
+  </si>
+  <si>
+    <t>JeffreyJFrancois@Icloud.com</t>
+  </si>
+  <si>
+    <t>Allen, Lou</t>
+  </si>
+  <si>
+    <t>louisallen85@yahoo.com</t>
+  </si>
+  <si>
+    <t>Edwards, Matthew</t>
+  </si>
+  <si>
+    <t>msedwards30mse@gmail.com</t>
+  </si>
+  <si>
+    <t>Bacewicz, Joe</t>
+  </si>
+  <si>
+    <t>O'Connell, Dennis</t>
+  </si>
+  <si>
+    <t>Not Needed</t>
   </si>
 </sst>
 </file>
@@ -1077,7 +1095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F97E2D-D2EE-4E19-AA28-ED70E4256082}">
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" customWidth="1"/>
@@ -1086,43 +1104,44 @@
     <col min="4" max="4" width="14.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="9.85546875" customWidth="1"/>
     <col min="6" max="6" width="13.85546875" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>148</v>
+      <c r="G1" s="5" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="C2" s="1">
         <v>1977</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -1130,16 +1149,16 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" s="1">
         <v>1971</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -1147,16 +1166,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C4" s="1">
         <v>1998</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -1164,90 +1183,90 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>218</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1967</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>142</v>
+        <v>219</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="C6" s="1">
-        <v>1987</v>
+        <v>1967</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="G6" t="s">
-        <v>149</v>
+      <c r="G6" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>150</v>
+        <v>81</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="C7" s="1">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
       </c>
-      <c r="G7" t="s">
-        <v>149</v>
+      <c r="G7" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="C8" s="1">
-        <v>1970</v>
+        <v>1988</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>188</v>
+        <v>10</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>189</v>
+        <v>87</v>
       </c>
       <c r="C9" s="1">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
@@ -1255,16 +1274,16 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C10" s="1">
         <v>1972</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -1272,13 +1291,16 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>222</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="C11" s="1">
-        <v>1981</v>
+        <v>1972</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -1286,16 +1308,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>85</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1">
-        <v>2005</v>
+        <v>1981</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -1303,127 +1322,127 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>54</v>
+        <v>83</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="C13" s="1">
-        <v>1970</v>
+        <v>2005</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>152</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>153</v>
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
       </c>
       <c r="C14" s="1">
-        <v>2015</v>
+        <v>1970</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
-      <c r="G14" t="s">
-        <v>149</v>
+      <c r="G14" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>164</v>
+        <v>148</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2015</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="1">
-        <v>1998</v>
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="E16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>154</v>
+        <v>28</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>164</v>
+        <v>29</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1998</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
       </c>
-      <c r="G17" t="s">
-        <v>149</v>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C18" s="1">
-        <v>1996</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
-      <c r="G18" t="s">
-        <v>149</v>
+      <c r="G18" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>152</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>50</v>
+        <v>153</v>
       </c>
       <c r="C19" s="1">
-        <v>1989</v>
+        <v>1996</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>143</v>
@@ -1431,36 +1450,39 @@
       <c r="E19" t="b">
         <v>1</v>
       </c>
-      <c r="G19" t="s">
-        <v>149</v>
+      <c r="G19" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1">
-        <v>1969</v>
+        <v>1989</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>159</v>
+        <v>59</v>
       </c>
       <c r="C21" s="1">
-        <v>1978</v>
+        <v>1969</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>139</v>
@@ -1468,67 +1490,70 @@
       <c r="E21" t="b">
         <v>1</v>
       </c>
-      <c r="G21" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>198</v>
+        <v>155</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1978</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>192</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
+      </c>
+      <c r="G23" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>112</v>
+        <v>5</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C24" s="1">
+        <v>44</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>109</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" s="1">
         <v>1974</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" s="1">
-        <v>1982</v>
-      </c>
       <c r="D25" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
@@ -1536,67 +1561,73 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>193</v>
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="C26" s="1">
-        <v>1977</v>
+        <v>1982</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E26" t="b">
         <v>1</v>
+      </c>
+      <c r="G26" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>116</v>
+        <v>187</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>117</v>
+        <v>188</v>
       </c>
       <c r="C27" s="1">
         <v>1977</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
       </c>
-      <c r="G27" t="s">
-        <v>149</v>
+      <c r="G27" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>16</v>
-      </c>
-      <c r="B28" t="s">
-        <v>92</v>
+      <c r="A28" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="C28" s="1">
-        <v>1964</v>
+        <v>1977</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
+      </c>
+      <c r="G28" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>93</v>
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>90</v>
       </c>
       <c r="C29" s="1">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>142</v>
@@ -1604,84 +1635,93 @@
       <c r="E29" t="b">
         <v>1</v>
       </c>
+      <c r="G29" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="C30" s="1">
-        <v>1993</v>
+        <v>1969</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E30" t="b">
         <v>1</v>
-      </c>
-      <c r="G30" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>164</v>
+        <v>215</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1977</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
+      </c>
+      <c r="G31" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>199</v>
+        <v>111</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>200</v>
+        <v>112</v>
       </c>
       <c r="C32" s="1">
-        <v>1997</v>
+        <v>1993</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
+      </c>
+      <c r="G33" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C34" s="1">
-        <v>1982</v>
+        <v>41</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
@@ -1689,70 +1729,70 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>23</v>
-      </c>
-      <c r="B35" t="s">
-        <v>94</v>
+        <v>194</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>195</v>
       </c>
       <c r="C35" s="1">
-        <v>1979</v>
+        <v>1997</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C36" s="1">
-        <v>2005</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>144</v>
+        <v>197</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
+      </c>
+      <c r="G36" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>160</v>
+        <v>206</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>164</v>
+        <v>207</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1982</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
       </c>
-      <c r="G37" t="s">
-        <v>149</v>
+      <c r="G37" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B38" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C38" s="1">
-        <v>1971</v>
+        <v>1979</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
@@ -1760,113 +1800,119 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>71</v>
+        <v>179</v>
       </c>
       <c r="C39" s="1">
-        <v>1993</v>
+        <v>2005</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E39" t="b">
         <v>1</v>
       </c>
-      <c r="G39" t="s">
-        <v>149</v>
+      <c r="G39" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C40" s="1">
-        <v>1970</v>
+        <v>157</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="E40" t="b">
         <v>1</v>
       </c>
-      <c r="F40" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" t="s">
-        <v>149</v>
+      <c r="G40" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>19</v>
-      </c>
-      <c r="B41" t="s">
-        <v>96</v>
+        <v>216</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>217</v>
       </c>
       <c r="C41" s="1">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E41" t="b">
         <v>1</v>
+      </c>
+      <c r="G41" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>174</v>
+        <v>68</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="C42" s="1">
-        <v>2004</v>
+        <v>1993</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E42" t="b">
         <v>1</v>
       </c>
-      <c r="F42" t="b">
-        <v>1</v>
+      <c r="G42" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="C43" s="1">
-        <v>1996</v>
+        <v>1970</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E43" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>124</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>125</v>
+        <v>18</v>
+      </c>
+      <c r="B44" t="s">
+        <v>93</v>
       </c>
       <c r="C44" s="1">
-        <v>1995</v>
+        <v>1972</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="E44" t="b">
         <v>1</v>
@@ -1874,47 +1920,56 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>62</v>
+        <v>170</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>63</v>
+        <v>171</v>
       </c>
       <c r="C45" s="1">
-        <v>1979</v>
+        <v>2004</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E45" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>20</v>
-      </c>
-      <c r="B46" t="s">
-        <v>97</v>
+        <v>198</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>199</v>
       </c>
       <c r="C46" s="1">
-        <v>1979</v>
+        <v>1996</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
+      </c>
+      <c r="G46" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="C47" s="1">
-        <v>1986</v>
+        <v>1995</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>143</v>
@@ -1922,298 +1977,304 @@
       <c r="E47" t="b">
         <v>1</v>
       </c>
+      <c r="G47" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>118</v>
+        <v>61</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>119</v>
+        <v>62</v>
       </c>
       <c r="C48" s="1">
-        <v>1982</v>
+        <v>1979</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E48" t="b">
         <v>1</v>
-      </c>
-      <c r="G48" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" s="1">
+        <v>1979</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C49" s="1">
-        <v>1994</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="E49" t="b">
         <v>1</v>
+      </c>
+      <c r="G49" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="C50" s="1">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E50" t="b">
         <v>1</v>
-      </c>
-      <c r="G50" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="C51" s="1">
-        <v>2008</v>
+        <v>1982</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E51" t="b">
         <v>1</v>
+      </c>
+      <c r="G51" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>164</v>
+        <v>134</v>
+      </c>
+      <c r="C52" s="1">
+        <v>1994</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="E52" t="b">
         <v>1</v>
+      </c>
+      <c r="G52" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>2</v>
-      </c>
-      <c r="B53" t="s">
-        <v>99</v>
+        <v>26</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="C53" s="1">
-        <v>1987</v>
+        <v>1982</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E53" t="b">
         <v>1</v>
+      </c>
+      <c r="G53" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="C54" s="1">
-        <v>1981</v>
+        <v>2008</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E54" t="b">
         <v>1</v>
-      </c>
-      <c r="G54" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C55" s="1">
-        <v>1973</v>
+        <v>73</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="E55" t="b">
         <v>1</v>
-      </c>
-      <c r="G55" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>165</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>166</v>
+        <v>2</v>
+      </c>
+      <c r="B56" t="s">
+        <v>96</v>
       </c>
       <c r="C56" s="1">
-        <v>1978</v>
+        <v>1987</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E56" t="b">
         <v>1</v>
-      </c>
-      <c r="G56" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="C57" s="1">
-        <v>1989</v>
+        <v>1981</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E57" t="b">
         <v>1</v>
       </c>
-      <c r="G57" t="s">
-        <v>149</v>
+      <c r="G57" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>102</v>
+        <v>158</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>103</v>
+        <v>159</v>
       </c>
       <c r="C58" s="1">
-        <v>1981</v>
+        <v>1973</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E58" t="b">
         <v>1</v>
       </c>
-      <c r="G58" t="s">
-        <v>149</v>
+      <c r="G58" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>25</v>
-      </c>
-      <c r="B59" t="s">
-        <v>100</v>
+        <v>161</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="C59" s="1">
-        <v>1986</v>
+        <v>1978</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E59" t="b">
         <v>1</v>
+      </c>
+      <c r="G59" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>47</v>
+        <v>128</v>
       </c>
       <c r="C60" s="1">
-        <v>1966</v>
+        <v>1989</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E60" t="b">
         <v>1</v>
       </c>
-      <c r="G60" t="s">
-        <v>149</v>
+      <c r="G60" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C61" s="1">
-        <v>1992</v>
+        <v>1981</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E61" t="b">
         <v>1</v>
       </c>
-      <c r="G61" t="s">
-        <v>149</v>
+      <c r="G61" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>87</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>88</v>
+        <v>24</v>
+      </c>
+      <c r="B62" t="s">
+        <v>97</v>
       </c>
       <c r="C62" s="1">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E62" t="b">
+        <v>1</v>
+      </c>
+      <c r="G62" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="C63" s="1">
-        <v>1979</v>
+        <v>1966</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>139</v>
@@ -2221,141 +2282,150 @@
       <c r="E63" t="b">
         <v>1</v>
       </c>
+      <c r="G63" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>24</v>
-      </c>
-      <c r="B64" t="s">
-        <v>101</v>
+        <v>107</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>108</v>
       </c>
       <c r="C64" s="1">
-        <v>1979</v>
+        <v>1992</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E64" t="b">
         <v>1</v>
+      </c>
+      <c r="G64" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>167</v>
+        <v>85</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>168</v>
+        <v>86</v>
+      </c>
+      <c r="C65" s="1">
+        <v>1984</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="E65" t="b">
         <v>1</v>
-      </c>
-      <c r="G65" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1</v>
-      </c>
-      <c r="B66" t="s">
-        <v>104</v>
+        <v>64</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C66" s="1">
-        <v>1970</v>
+        <v>1979</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E66" t="b">
         <v>1</v>
       </c>
-      <c r="G66" t="s">
-        <v>149</v>
+      <c r="G66" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B67" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C67" s="1">
-        <v>2015</v>
+        <v>1979</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="E67" t="b">
         <v>1</v>
-      </c>
-      <c r="G67" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>64</v>
+        <v>163</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C68" s="1">
-        <v>1978</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="E68" t="b">
         <v>1</v>
+      </c>
+      <c r="G68" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>68</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>69</v>
+        <v>1</v>
+      </c>
+      <c r="B69" t="s">
+        <v>101</v>
       </c>
       <c r="C69" s="1">
-        <v>1974</v>
+        <v>1970</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E69" t="b">
         <v>1</v>
+      </c>
+      <c r="G69" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>180</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>181</v>
+        <v>3</v>
+      </c>
+      <c r="B70" t="s">
+        <v>102</v>
       </c>
       <c r="C70" s="1">
-        <v>1976</v>
+        <v>2015</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E70" t="b">
         <v>1</v>
+      </c>
+      <c r="G70" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>126</v>
+        <v>223</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>127</v>
+        <v>63</v>
       </c>
       <c r="C71" s="1">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E71" t="b">
         <v>1</v>
@@ -2363,16 +2433,16 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>7</v>
-      </c>
-      <c r="B72" t="s">
-        <v>106</v>
+        <v>66</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="C72" s="1">
-        <v>1969</v>
+        <v>1974</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E72" t="b">
         <v>1</v>
@@ -2380,36 +2450,36 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>36</v>
+        <v>176</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>164</v>
+        <v>177</v>
+      </c>
+      <c r="C73" s="1">
+        <v>1976</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="E73" t="b">
         <v>1</v>
       </c>
-      <c r="G73" t="s">
-        <v>149</v>
+      <c r="G73" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>178</v>
+        <v>123</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>179</v>
+        <v>124</v>
       </c>
       <c r="C74" s="1">
-        <v>2004</v>
+        <v>1980</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E74" t="b">
         <v>1</v>
@@ -2417,90 +2487,93 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>80</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>79</v>
+        <v>6</v>
+      </c>
+      <c r="B75" t="s">
+        <v>103</v>
       </c>
       <c r="C75" s="1">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E75" t="b">
         <v>1</v>
+      </c>
+      <c r="G75" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C76" s="1">
-        <v>1971</v>
+        <v>36</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E76" t="b">
+        <v>1</v>
+      </c>
+      <c r="G76" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>107</v>
+        <v>175</v>
       </c>
       <c r="C77" s="1">
-        <v>1985</v>
+        <v>2004</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E77" t="b">
         <v>1</v>
-      </c>
-      <c r="G77" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="C78" s="1">
-        <v>1975</v>
+        <v>1968</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E78" t="b">
         <v>1</v>
       </c>
-      <c r="G78" t="s">
-        <v>149</v>
+      <c r="G78" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>13</v>
-      </c>
-      <c r="B79" t="s">
-        <v>108</v>
+        <v>14</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="C79" s="1">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E79" t="b">
         <v>1</v>
@@ -2508,309 +2581,327 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>194</v>
+        <v>11</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>195</v>
+        <v>104</v>
       </c>
       <c r="C80" s="1">
-        <v>1995</v>
+        <v>1985</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E80" t="b">
         <v>1</v>
+      </c>
+      <c r="G80" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="C81" s="1">
         <v>1975</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E81" t="b">
         <v>1</v>
       </c>
-      <c r="G81" t="s">
-        <v>149</v>
+      <c r="G81" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>186</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>187</v>
+        <v>12</v>
+      </c>
+      <c r="B82" t="s">
+        <v>105</v>
       </c>
       <c r="C82" s="1">
-        <v>1963</v>
+        <v>1970</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>210</v>
+        <v>139</v>
       </c>
       <c r="E82" t="b">
         <v>1</v>
+      </c>
+      <c r="G82" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>40</v>
+        <v>189</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>164</v>
+        <v>190</v>
+      </c>
+      <c r="C83" s="1">
+        <v>1995</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="E83" t="b">
         <v>1</v>
       </c>
-      <c r="G83" t="s">
-        <v>149</v>
+      <c r="G83" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="C84" s="1">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E84" t="b">
         <v>1</v>
       </c>
-      <c r="G84" t="s">
-        <v>149</v>
+      <c r="G84" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="C85" s="1">
-        <v>1967</v>
+        <v>1963</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>142</v>
+        <v>205</v>
       </c>
       <c r="E85" t="b">
         <v>1</v>
       </c>
-      <c r="G85" t="s">
-        <v>149</v>
+      <c r="G85" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>128</v>
+        <v>39</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C86" s="1">
-        <v>1993</v>
+        <v>40</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="E86" t="b">
         <v>1</v>
       </c>
-      <c r="G86" t="s">
-        <v>149</v>
+      <c r="G86" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="C87" s="1">
-        <v>2004</v>
+        <v>1976</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E87" t="b">
         <v>1</v>
       </c>
-      <c r="G87" t="s">
-        <v>149</v>
+      <c r="G87" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C88" s="1">
-        <v>1976</v>
+        <v>1967</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E88" t="b">
         <v>1</v>
       </c>
-      <c r="G88" t="s">
-        <v>149</v>
+      <c r="G88" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="C89" s="1">
-        <v>1970</v>
+        <v>1993</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E89" t="b">
         <v>1</v>
+      </c>
+      <c r="G89" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>205</v>
+        <v>131</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>206</v>
+        <v>132</v>
+      </c>
+      <c r="C90" s="1">
+        <v>2004</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="E90" t="b">
         <v>1</v>
+      </c>
+      <c r="G90" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>217</v>
+        <v>167</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>218</v>
+        <v>168</v>
       </c>
       <c r="C91" s="1">
-        <v>1970</v>
+        <v>1976</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E91" t="b">
         <v>1</v>
+      </c>
+      <c r="G91" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="C92" s="1">
-        <v>2016</v>
+        <v>1970</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E92" t="b">
         <v>1</v>
       </c>
-      <c r="G92" t="s">
-        <v>149</v>
+      <c r="G92" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C93" s="1">
-        <v>2000</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>144</v>
+        <v>201</v>
       </c>
       <c r="E93" t="b">
         <v>1</v>
+      </c>
+      <c r="G93" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>17</v>
-      </c>
-      <c r="B94" t="s">
-        <v>109</v>
+        <v>212</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>213</v>
       </c>
       <c r="C94" s="1">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E94" t="b">
         <v>1</v>
-      </c>
-      <c r="G94" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="C95" s="1">
-        <v>1975</v>
+        <v>2016</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E95" t="b">
         <v>1</v>
+      </c>
+      <c r="G95" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>9</v>
+        <v>191</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>78</v>
+        <v>169</v>
       </c>
       <c r="C96" s="1">
-        <v>1989</v>
+        <v>2000</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E96" t="b">
         <v>1</v>
@@ -2818,10 +2909,13 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>22</v>
+        <v>16</v>
+      </c>
+      <c r="B97" t="s">
+        <v>106</v>
       </c>
       <c r="C97" s="1">
-        <v>1979</v>
+        <v>1969</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>139</v>
@@ -2829,39 +2923,39 @@
       <c r="E97" t="b">
         <v>1</v>
       </c>
+      <c r="G97" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="C98" s="1">
-        <v>2006</v>
+        <v>1975</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E98" t="b">
         <v>1</v>
-      </c>
-      <c r="G98" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>207</v>
+        <v>8</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>208</v>
+        <v>76</v>
       </c>
       <c r="C99" s="1">
-        <v>2019</v>
+        <v>1989</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E99" t="b">
         <v>1</v>
@@ -2869,16 +2963,13 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>214</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="C100" s="1">
-        <v>1998</v>
+        <v>1979</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="E100" t="b">
         <v>1</v>
@@ -2886,121 +2977,185 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C101" s="1">
-        <v>1975</v>
+        <v>2006</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E101" t="b">
         <v>1</v>
       </c>
-      <c r="G101" t="s">
-        <v>149</v>
+      <c r="G101" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C102" s="1">
+        <v>2019</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E102" t="b">
+        <v>1</v>
+      </c>
+      <c r="G102" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>209</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C103" s="1">
+        <v>1998</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E103" t="b">
+        <v>1</v>
+      </c>
+      <c r="G103" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>50</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C104" s="1">
+        <v>1975</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E104" t="b">
+        <v>1</v>
+      </c>
+      <c r="G104" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>210</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C105" s="1">
         <v>1970</v>
       </c>
-      <c r="D102" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E102" t="b">
+      <c r="D105" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E105" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B5" r:id="rId1" xr:uid="{8227A597-9225-4357-B8B6-9F19CC6D2D47}"/>
-    <hyperlink ref="B16" r:id="rId2" xr:uid="{C440EE30-529A-4080-AE83-A4A978C3E02B}"/>
-    <hyperlink ref="B73" r:id="rId3" xr:uid="{C5FAAB38-5F1C-4A08-8709-401E7E23E0D1}"/>
-    <hyperlink ref="B78" r:id="rId4" xr:uid="{109EA93A-660A-4099-B212-FD77BC4B5297}"/>
-    <hyperlink ref="B83" r:id="rId5" xr:uid="{4FC29F3F-346D-4C86-81DD-BA31CA08B134}"/>
-    <hyperlink ref="B31" r:id="rId6" xr:uid="{98703E9F-F4A5-4829-8BBF-B9F807C63E68}"/>
-    <hyperlink ref="B89" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
-    <hyperlink ref="B23" r:id="rId8" xr:uid="{804D2DB9-BDF1-463B-9BD3-ACBFC15F041A}"/>
-    <hyperlink ref="B60" r:id="rId9" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
-    <hyperlink ref="B76" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
-    <hyperlink ref="B19" r:id="rId11" xr:uid="{DF6F8079-E647-4079-9719-72DC2FF3791C}"/>
-    <hyperlink ref="B101" r:id="rId12" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
-    <hyperlink ref="B98" r:id="rId13" xr:uid="{ECCFE763-5E69-4122-B27B-DA1C21FADA86}"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{8227A597-9225-4357-B8B6-9F19CC6D2D47}"/>
+    <hyperlink ref="B17" r:id="rId2" xr:uid="{C440EE30-529A-4080-AE83-A4A978C3E02B}"/>
+    <hyperlink ref="B76" r:id="rId3" xr:uid="{C5FAAB38-5F1C-4A08-8709-401E7E23E0D1}"/>
+    <hyperlink ref="B81" r:id="rId4" xr:uid="{109EA93A-660A-4099-B212-FD77BC4B5297}"/>
+    <hyperlink ref="B86" r:id="rId5" xr:uid="{4FC29F3F-346D-4C86-81DD-BA31CA08B134}"/>
+    <hyperlink ref="B34" r:id="rId6" xr:uid="{98703E9F-F4A5-4829-8BBF-B9F807C63E68}"/>
+    <hyperlink ref="B92" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
+    <hyperlink ref="B24" r:id="rId8" xr:uid="{804D2DB9-BDF1-463B-9BD3-ACBFC15F041A}"/>
+    <hyperlink ref="B63" r:id="rId9" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
+    <hyperlink ref="B79" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
+    <hyperlink ref="B20" r:id="rId11" xr:uid="{DF6F8079-E647-4079-9719-72DC2FF3791C}"/>
+    <hyperlink ref="B104" r:id="rId12" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
+    <hyperlink ref="B101" r:id="rId13" xr:uid="{ECCFE763-5E69-4122-B27B-DA1C21FADA86}"/>
     <hyperlink ref="B2" r:id="rId14" xr:uid="{8869974B-11E2-4A99-8438-9F9B8ABEB9F6}"/>
-    <hyperlink ref="B20" r:id="rId15" display="mailto:elizabeth.casarella@gmail.com" xr:uid="{C150E814-8C96-4E50-8A55-5EB3344749B1}"/>
-    <hyperlink ref="B81" r:id="rId16" display="mailto:paul@levelbreaker.com" xr:uid="{9746CC3F-863E-4E18-931A-FADD4ED10BF2}"/>
-    <hyperlink ref="B45" r:id="rId17" xr:uid="{316BCF75-05DF-4572-9F46-9F76127C0677}"/>
-    <hyperlink ref="B68" r:id="rId18" display="mailto:dennis.p.oconnell@gmail.com" xr:uid="{57197F8F-1C51-4977-936A-74B15D239DF7}"/>
-    <hyperlink ref="B63" r:id="rId19" display="mailto:hef714@aol.com" xr:uid="{A4825BC7-F2DD-43E9-A39B-48544C54E403}"/>
-    <hyperlink ref="B69" r:id="rId20" xr:uid="{53A4A1D2-46D5-45C1-BB62-DA92169DD070}"/>
-    <hyperlink ref="B39" r:id="rId21" xr:uid="{A871275A-577B-4F01-A590-B30FBADA40A1}"/>
-    <hyperlink ref="B95" r:id="rId22" xr:uid="{7E7AC9EC-4484-43DC-8B81-7AA0BCCFA407}"/>
-    <hyperlink ref="B54" r:id="rId23" display="mailto:Gjhusky52@yahoo.com" xr:uid="{1F5D9E16-5BA9-4F8F-B8CF-14485F325E5D}"/>
-    <hyperlink ref="B96" r:id="rId24" display="mailto:s.vibberts@yahoo.com" xr:uid="{CD95CA65-C8C5-44B3-8AFC-2E088AEC194C}"/>
-    <hyperlink ref="B75" r:id="rId25" display="mailto:oldparsonage3@gmail.com" xr:uid="{DC8DA8C9-CCEA-4FC3-AA05-1EF34B65B0C1}"/>
-    <hyperlink ref="B47" r:id="rId26" xr:uid="{C2395B48-B35E-4045-A136-C8B31BE4A5FC}"/>
-    <hyperlink ref="B6" r:id="rId27" xr:uid="{37F7977A-EC68-4733-8738-6C53C959B816}"/>
-    <hyperlink ref="B12" r:id="rId28" display="mailto:cwb84122@gmail.com" xr:uid="{A209B655-7CEF-4F8D-BFEE-DFB49C33870B}"/>
-    <hyperlink ref="B62" r:id="rId29" display="mailto:Npmyers@sbcglobal.net" xr:uid="{46F1EE8C-941D-4D6B-A27A-3BDDA65A15CE}"/>
-    <hyperlink ref="B8" r:id="rId30" xr:uid="{647703FF-1796-4612-923D-2A3CF89F5A46}"/>
-    <hyperlink ref="B29" r:id="rId31" xr:uid="{D4F421DD-A322-4F00-A209-B464A28664A6}"/>
-    <hyperlink ref="B50" r:id="rId32" xr:uid="{5FF15619-CFAB-48CB-8BF0-78013919701C}"/>
-    <hyperlink ref="B58" r:id="rId33" display="mailto:Kmills8080@gmail.com" xr:uid="{6653A4F2-00C8-4ACF-A9B2-950ABB23037C}"/>
-    <hyperlink ref="B52" r:id="rId34" xr:uid="{0F8932AA-3F92-4F04-A82F-C839649C3558}"/>
-    <hyperlink ref="B77" r:id="rId35" xr:uid="{74573551-A238-45F0-95FA-078470676D33}"/>
-    <hyperlink ref="B61" r:id="rId36" xr:uid="{F093A50A-9255-43F2-873A-E61FB97B7B6E}"/>
-    <hyperlink ref="B24" r:id="rId37" display="mailto:joecorbo@icloud.com" xr:uid="{9664FD56-34AE-4697-8A23-BBA8942C6ABA}"/>
-    <hyperlink ref="B30" r:id="rId38" display="mailto:lostdogs@charter.net" xr:uid="{95D046AE-D83E-4029-8E4D-F457CDD3F23E}"/>
-    <hyperlink ref="B27" r:id="rId39" xr:uid="{93D1D532-1D29-4735-B6C3-7B9B46F15302}"/>
-    <hyperlink ref="B48" r:id="rId40" display="mailto:langer0125@gmail.com" xr:uid="{EF3BA7C4-32BE-431A-9979-8B42711B0D73}"/>
-    <hyperlink ref="B92" r:id="rId41" display="mailto:Ntjr05@gmail.com" xr:uid="{38DDEC56-F2AD-4C66-8377-3BFC9B7BDDB9}"/>
-    <hyperlink ref="B84" r:id="rId42" display="mailto:gregsinay3@gmail.com" xr:uid="{004C878C-63EB-40FC-B549-87CFABDE66E1}"/>
-    <hyperlink ref="B44" r:id="rId43" display="mailto:Suj9283@yahoo.com" xr:uid="{E8FF833B-A9E0-4AED-A7DB-065ED67E2244}"/>
-    <hyperlink ref="B71" r:id="rId44" display="mailto:djpal@zoominternet.net" xr:uid="{FAF882CB-F959-4D5E-B4E0-3608ADC9DA13}"/>
-    <hyperlink ref="B86" r:id="rId45" display="mailto:sosikiii@msn.com" xr:uid="{218E6BB5-6D46-4A2B-BD2C-6CF05A021B3C}"/>
-    <hyperlink ref="B51" r:id="rId46" display="mailto:Robertmlunn@gmail.com" xr:uid="{33551D8E-478C-410F-9E21-46488F70F42D}"/>
-    <hyperlink ref="B87" r:id="rId47" display="mailto:brisparks@gmail.com" xr:uid="{E8A49946-13F1-4C59-AD3D-A3E5B9D77EFF}"/>
-    <hyperlink ref="B49" r:id="rId48" display="mailto:Dlew44@gmail.com" xr:uid="{25AC56D9-918C-4162-BE04-DAA69217239F}"/>
-    <hyperlink ref="B7" r:id="rId49" xr:uid="{02619D1B-E12D-411C-8267-1EA72D337FA4}"/>
-    <hyperlink ref="B14" r:id="rId50" xr:uid="{297F912D-F1B3-4511-B9FB-7F6A5151679A}"/>
-    <hyperlink ref="B17" r:id="rId51" xr:uid="{23A72ED8-42A8-4AD2-AED4-16447BAE4A08}"/>
-    <hyperlink ref="B18" r:id="rId52" xr:uid="{5484D007-8240-489C-A613-B2C0F0F2AC56}"/>
-    <hyperlink ref="B21" r:id="rId53" xr:uid="{D01BE816-0B5A-4446-924C-46E6BAD18108}"/>
-    <hyperlink ref="B37" r:id="rId54" xr:uid="{276C5002-FCF1-4B64-9438-E4287F3F2787}"/>
-    <hyperlink ref="B55" r:id="rId55" xr:uid="{05B37D53-659E-462F-9D42-00105B550079}"/>
-    <hyperlink ref="B56" r:id="rId56" xr:uid="{F7EC428E-8409-4830-9429-9C5E7ABB09A4}"/>
-    <hyperlink ref="B65" r:id="rId57" xr:uid="{EE1C2C4D-03AE-46ED-A073-46B29C8D3689}"/>
-    <hyperlink ref="B85" r:id="rId58" xr:uid="{4C733EB2-A8CB-4A19-80B4-31601DA15BF2}"/>
-    <hyperlink ref="B88" r:id="rId59" xr:uid="{77C5CEA7-AAB7-4C0E-8FED-A2F21F462250}"/>
-    <hyperlink ref="B93" r:id="rId60" display="mailto:ryantimko@hotmail.com" xr:uid="{D3F25966-9FE3-42C3-94BB-54469D722B9E}"/>
-    <hyperlink ref="B42" r:id="rId61" display="mailto:bill.irwin58@gmail.com" xr:uid="{21398664-274B-466E-AEF3-003790919F40}"/>
-    <hyperlink ref="B40" r:id="rId62" display="mailto:Hogan6523@Yahoo.com" xr:uid="{8F033920-5D36-4035-9970-BF7A906D9337}"/>
-    <hyperlink ref="B74" r:id="rId63" display="mailto:justperk2@gmail.com" xr:uid="{3915D652-1507-4F3C-AEB3-935E95D07A08}"/>
-    <hyperlink ref="B70" r:id="rId64" display="mailto:bernard.e.palmer@gmail.com" xr:uid="{4E7DEDEB-BA72-4331-A716-378C6A511DCC}"/>
-    <hyperlink ref="B36" r:id="rId65" display="mailto:fogs14@yahoo.com" xr:uid="{E734B4DB-161E-4386-9BE4-4D2A768C19C0}"/>
+    <hyperlink ref="B21" r:id="rId15" display="mailto:elizabeth.casarella@gmail.com" xr:uid="{C150E814-8C96-4E50-8A55-5EB3344749B1}"/>
+    <hyperlink ref="B84" r:id="rId16" display="mailto:paul@levelbreaker.com" xr:uid="{9746CC3F-863E-4E18-931A-FADD4ED10BF2}"/>
+    <hyperlink ref="B48" r:id="rId17" xr:uid="{316BCF75-05DF-4572-9F46-9F76127C0677}"/>
+    <hyperlink ref="B71" r:id="rId18" display="mailto:dennis.p.oconnell@gmail.com" xr:uid="{57197F8F-1C51-4977-936A-74B15D239DF7}"/>
+    <hyperlink ref="B66" r:id="rId19" display="mailto:hef714@aol.com" xr:uid="{A4825BC7-F2DD-43E9-A39B-48544C54E403}"/>
+    <hyperlink ref="B72" r:id="rId20" xr:uid="{53A4A1D2-46D5-45C1-BB62-DA92169DD070}"/>
+    <hyperlink ref="B42" r:id="rId21" xr:uid="{A871275A-577B-4F01-A590-B30FBADA40A1}"/>
+    <hyperlink ref="B98" r:id="rId22" xr:uid="{7E7AC9EC-4484-43DC-8B81-7AA0BCCFA407}"/>
+    <hyperlink ref="B57" r:id="rId23" display="mailto:Gjhusky52@yahoo.com" xr:uid="{1F5D9E16-5BA9-4F8F-B8CF-14485F325E5D}"/>
+    <hyperlink ref="B99" r:id="rId24" display="mailto:s.vibberts@yahoo.com" xr:uid="{CD95CA65-C8C5-44B3-8AFC-2E088AEC194C}"/>
+    <hyperlink ref="B78" r:id="rId25" display="mailto:oldparsonage3@gmail.com" xr:uid="{DC8DA8C9-CCEA-4FC3-AA05-1EF34B65B0C1}"/>
+    <hyperlink ref="B50" r:id="rId26" xr:uid="{C2395B48-B35E-4045-A136-C8B31BE4A5FC}"/>
+    <hyperlink ref="B7" r:id="rId27" xr:uid="{37F7977A-EC68-4733-8738-6C53C959B816}"/>
+    <hyperlink ref="B13" r:id="rId28" display="mailto:cwb84122@gmail.com" xr:uid="{A209B655-7CEF-4F8D-BFEE-DFB49C33870B}"/>
+    <hyperlink ref="B65" r:id="rId29" display="mailto:Npmyers@sbcglobal.net" xr:uid="{46F1EE8C-941D-4D6B-A27A-3BDDA65A15CE}"/>
+    <hyperlink ref="B9" r:id="rId30" xr:uid="{647703FF-1796-4612-923D-2A3CF89F5A46}"/>
+    <hyperlink ref="B30" r:id="rId31" xr:uid="{D4F421DD-A322-4F00-A209-B464A28664A6}"/>
+    <hyperlink ref="B53" r:id="rId32" xr:uid="{5FF15619-CFAB-48CB-8BF0-78013919701C}"/>
+    <hyperlink ref="B61" r:id="rId33" display="mailto:Kmills8080@gmail.com" xr:uid="{6653A4F2-00C8-4ACF-A9B2-950ABB23037C}"/>
+    <hyperlink ref="B55" r:id="rId34" xr:uid="{0F8932AA-3F92-4F04-A82F-C839649C3558}"/>
+    <hyperlink ref="B80" r:id="rId35" xr:uid="{74573551-A238-45F0-95FA-078470676D33}"/>
+    <hyperlink ref="B64" r:id="rId36" xr:uid="{F093A50A-9255-43F2-873A-E61FB97B7B6E}"/>
+    <hyperlink ref="B25" r:id="rId37" display="mailto:joecorbo@icloud.com" xr:uid="{9664FD56-34AE-4697-8A23-BBA8942C6ABA}"/>
+    <hyperlink ref="B32" r:id="rId38" display="mailto:lostdogs@charter.net" xr:uid="{95D046AE-D83E-4029-8E4D-F457CDD3F23E}"/>
+    <hyperlink ref="B28" r:id="rId39" xr:uid="{93D1D532-1D29-4735-B6C3-7B9B46F15302}"/>
+    <hyperlink ref="B51" r:id="rId40" display="mailto:langer0125@gmail.com" xr:uid="{EF3BA7C4-32BE-431A-9979-8B42711B0D73}"/>
+    <hyperlink ref="B95" r:id="rId41" display="mailto:Ntjr05@gmail.com" xr:uid="{38DDEC56-F2AD-4C66-8377-3BFC9B7BDDB9}"/>
+    <hyperlink ref="B87" r:id="rId42" display="mailto:gregsinay3@gmail.com" xr:uid="{004C878C-63EB-40FC-B549-87CFABDE66E1}"/>
+    <hyperlink ref="B47" r:id="rId43" display="mailto:Suj9283@yahoo.com" xr:uid="{E8FF833B-A9E0-4AED-A7DB-065ED67E2244}"/>
+    <hyperlink ref="B74" r:id="rId44" display="mailto:djpal@zoominternet.net" xr:uid="{FAF882CB-F959-4D5E-B4E0-3608ADC9DA13}"/>
+    <hyperlink ref="B89" r:id="rId45" display="mailto:sosikiii@msn.com" xr:uid="{218E6BB5-6D46-4A2B-BD2C-6CF05A021B3C}"/>
+    <hyperlink ref="B54" r:id="rId46" display="mailto:Robertmlunn@gmail.com" xr:uid="{33551D8E-478C-410F-9E21-46488F70F42D}"/>
+    <hyperlink ref="B90" r:id="rId47" display="mailto:brisparks@gmail.com" xr:uid="{E8A49946-13F1-4C59-AD3D-A3E5B9D77EFF}"/>
+    <hyperlink ref="B52" r:id="rId48" display="mailto:Dlew44@gmail.com" xr:uid="{25AC56D9-918C-4162-BE04-DAA69217239F}"/>
+    <hyperlink ref="B8" r:id="rId49" xr:uid="{02619D1B-E12D-411C-8267-1EA72D337FA4}"/>
+    <hyperlink ref="B15" r:id="rId50" xr:uid="{297F912D-F1B3-4511-B9FB-7F6A5151679A}"/>
+    <hyperlink ref="B18" r:id="rId51" xr:uid="{23A72ED8-42A8-4AD2-AED4-16447BAE4A08}"/>
+    <hyperlink ref="B19" r:id="rId52" xr:uid="{5484D007-8240-489C-A613-B2C0F0F2AC56}"/>
+    <hyperlink ref="B22" r:id="rId53" xr:uid="{D01BE816-0B5A-4446-924C-46E6BAD18108}"/>
+    <hyperlink ref="B40" r:id="rId54" xr:uid="{276C5002-FCF1-4B64-9438-E4287F3F2787}"/>
+    <hyperlink ref="B58" r:id="rId55" xr:uid="{05B37D53-659E-462F-9D42-00105B550079}"/>
+    <hyperlink ref="B59" r:id="rId56" xr:uid="{F7EC428E-8409-4830-9429-9C5E7ABB09A4}"/>
+    <hyperlink ref="B68" r:id="rId57" xr:uid="{EE1C2C4D-03AE-46ED-A073-46B29C8D3689}"/>
+    <hyperlink ref="B88" r:id="rId58" xr:uid="{4C733EB2-A8CB-4A19-80B4-31601DA15BF2}"/>
+    <hyperlink ref="B91" r:id="rId59" xr:uid="{77C5CEA7-AAB7-4C0E-8FED-A2F21F462250}"/>
+    <hyperlink ref="B96" r:id="rId60" display="mailto:ryantimko@hotmail.com" xr:uid="{D3F25966-9FE3-42C3-94BB-54469D722B9E}"/>
+    <hyperlink ref="B45" r:id="rId61" display="mailto:bill.irwin58@gmail.com" xr:uid="{21398664-274B-466E-AEF3-003790919F40}"/>
+    <hyperlink ref="B43" r:id="rId62" display="mailto:Hogan6523@Yahoo.com" xr:uid="{8F033920-5D36-4035-9970-BF7A906D9337}"/>
+    <hyperlink ref="B77" r:id="rId63" xr:uid="{3915D652-1507-4F3C-AEB3-935E95D07A08}"/>
+    <hyperlink ref="B73" r:id="rId64" display="mailto:bernard.e.palmer@gmail.com" xr:uid="{4E7DEDEB-BA72-4331-A716-378C6A511DCC}"/>
+    <hyperlink ref="B39" r:id="rId65" display="mailto:fogs14@yahoo.com" xr:uid="{E734B4DB-161E-4386-9BE4-4D2A768C19C0}"/>
     <hyperlink ref="B4" r:id="rId66" display="mailto:Robertalfaro@outlook.com" xr:uid="{94ECE3FB-34A8-40D2-A511-C6F49E1F79C8}"/>
-    <hyperlink ref="B82" r:id="rId67" xr:uid="{8042AEE0-2132-486D-AFC6-008B86CDABF9}"/>
-    <hyperlink ref="B26" r:id="rId68" display="mailto:rmdecambre@gmail.com" xr:uid="{61906EF9-7178-4E37-9EF5-F697B7AF8714}"/>
-    <hyperlink ref="B80" r:id="rId69" xr:uid="{C73311BF-B167-4642-BFA3-507299A38EFE}"/>
-    <hyperlink ref="B22" r:id="rId70" xr:uid="{A7D0DDDF-0E1D-4EAA-BC8A-6B20E1097E98}"/>
-    <hyperlink ref="B34" r:id="rId71" display="mailto:tfink9@juno.com" xr:uid="{34A73A04-8440-48B2-9348-0E4A6602D420}"/>
-    <hyperlink ref="B33" r:id="rId72" xr:uid="{0BB6B871-9927-4DD2-B508-224D22FD6229}"/>
-    <hyperlink ref="B90" r:id="rId73" xr:uid="{6DBAAB43-CE57-45EC-BCA9-CB408BBC84B6}"/>
-    <hyperlink ref="B99" r:id="rId74" xr:uid="{DB8385C7-8934-4CD0-B87E-4D74991BD43E}"/>
-    <hyperlink ref="B102" r:id="rId75" xr:uid="{CEB5326F-2589-4355-9CCD-6A3D6FC84E4A}"/>
-    <hyperlink ref="B91" r:id="rId76" xr:uid="{4A20E15A-8219-4697-83CE-53E329D1A594}"/>
+    <hyperlink ref="B85" r:id="rId67" xr:uid="{8042AEE0-2132-486D-AFC6-008B86CDABF9}"/>
+    <hyperlink ref="B27" r:id="rId68" display="mailto:rmdecambre@gmail.com" xr:uid="{61906EF9-7178-4E37-9EF5-F697B7AF8714}"/>
+    <hyperlink ref="B83" r:id="rId69" xr:uid="{C73311BF-B167-4642-BFA3-507299A38EFE}"/>
+    <hyperlink ref="B23" r:id="rId70" xr:uid="{A7D0DDDF-0E1D-4EAA-BC8A-6B20E1097E98}"/>
+    <hyperlink ref="B37" r:id="rId71" display="mailto:tfink9@juno.com" xr:uid="{34A73A04-8440-48B2-9348-0E4A6602D420}"/>
+    <hyperlink ref="B36" r:id="rId72" xr:uid="{0BB6B871-9927-4DD2-B508-224D22FD6229}"/>
+    <hyperlink ref="B93" r:id="rId73" xr:uid="{6DBAAB43-CE57-45EC-BCA9-CB408BBC84B6}"/>
+    <hyperlink ref="B102" r:id="rId74" xr:uid="{DB8385C7-8934-4CD0-B87E-4D74991BD43E}"/>
+    <hyperlink ref="B105" r:id="rId75" xr:uid="{CEB5326F-2589-4355-9CCD-6A3D6FC84E4A}"/>
+    <hyperlink ref="B94" r:id="rId76" xr:uid="{4A20E15A-8219-4697-83CE-53E329D1A594}"/>
+    <hyperlink ref="B31" r:id="rId77" xr:uid="{CB15C81B-047D-40F8-BDE8-B1539A6E2F0B}"/>
+    <hyperlink ref="B41" r:id="rId78" xr:uid="{B485936F-7DCD-4862-9E33-EEA8B063A75F}"/>
+    <hyperlink ref="B11" r:id="rId79" xr:uid="{74BFC159-A59B-4245-BC6C-B882819624B3}"/>
+    <hyperlink ref="B33" r:id="rId80" xr:uid="{F3187CCB-7830-43D4-9E21-FF900FE7F868}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId77"/>
+  <pageSetup orientation="portrait" r:id="rId81"/>
 </worksheet>
 </file>
--- a/UConnBleedBlue/wwwroot/Data/Players.xlsx
+++ b/UConnBleedBlue/wwwroot/Data/Players.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\UConnBleedBlue\UConnBleedBlue\wwwroot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5621FBBB-6759-4E49-A8C1-1C1714F16EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF32069B-6656-4FE1-927B-04463074C214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="1800" windowWidth="21600" windowHeight="13680" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
+    <workbookView xWindow="1950" yWindow="1800" windowWidth="21600" windowHeight="13680" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="242">
   <si>
     <t>Demers, Kenny</t>
   </si>
@@ -104,9 +104,6 @@
     <t>Walton, Ted</t>
   </si>
   <si>
-    <t>Flood, Mark</t>
-  </si>
-  <si>
     <t>Ney, Tom</t>
   </si>
   <si>
@@ -236,12 +233,6 @@
     <t>hef714@aol.com</t>
   </si>
   <si>
-    <t>O'Roark, Mike</t>
-  </si>
-  <si>
-    <t>mikeoroark23@gmail.com</t>
-  </si>
-  <si>
     <t>Henrich, Joe</t>
   </si>
   <si>
@@ -314,9 +305,6 @@
     <t>kpdemers073@gmail.com</t>
   </si>
   <si>
-    <t>marksflood1@gmail.com</t>
-  </si>
-  <si>
     <t>robertinnis@yahoo.com</t>
   </si>
   <si>
@@ -365,12 +353,6 @@
     <t>Dmurphy287@charter.net</t>
   </si>
   <si>
-    <t>Corbo, Joe</t>
-  </si>
-  <si>
-    <t>joecorbo@icloud.com</t>
-  </si>
-  <si>
     <t>Dunn, Steven</t>
   </si>
   <si>
@@ -711,6 +693,75 @@
   </si>
   <si>
     <t>Not Needed</t>
+  </si>
+  <si>
+    <t>Dixon, Andre</t>
+  </si>
+  <si>
+    <t>Sowell, Taurien</t>
+  </si>
+  <si>
+    <t>Sowell47@gmail.com</t>
+  </si>
+  <si>
+    <t>jbarrett@draws.com</t>
+  </si>
+  <si>
+    <t>npmyers@sbcglobal.net</t>
+  </si>
+  <si>
+    <t>Hunt, Philip</t>
+  </si>
+  <si>
+    <t>Phuntone9@gmail.com</t>
+  </si>
+  <si>
+    <t>Ahmed, Rasool</t>
+  </si>
+  <si>
+    <t>rasool@icgglobal.com</t>
+  </si>
+  <si>
+    <t>Brouse, Steve</t>
+  </si>
+  <si>
+    <t>Steven.brouse@gmail.com</t>
+  </si>
+  <si>
+    <t>Bailey, Jim</t>
+  </si>
+  <si>
+    <t>j.b.internationalcellars@gmail.com</t>
+  </si>
+  <si>
+    <t>Shirreffs, Bryant</t>
+  </si>
+  <si>
+    <t>Bryant.shirreffs@yahoo.com</t>
+  </si>
+  <si>
+    <t>Purcell, John</t>
+  </si>
+  <si>
+    <t>jcpurl@aol.com</t>
+  </si>
+  <si>
+    <t>Claflin, Jeremy</t>
+  </si>
+  <si>
+    <t>jeremyclaflin6@gmail.com</t>
+  </si>
+  <si>
+    <t>Landolfi, Mark</t>
+  </si>
+  <si>
+    <t>landolfimark285@gmail.com</t>
+  </si>
+  <si>
+    <t>Fenton, Rich</t>
+  </si>
+  <si>
+    <t>rfenton2015@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F97E2D-D2EE-4E19-AA28-ED70E4256082}">
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" customWidth="1"/>
@@ -1109,39 +1160,39 @@
   <sheetData>
     <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="G1" s="5" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="C2" s="1">
         <v>1977</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -1149,16 +1200,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1971</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>138</v>
+        <v>226</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -1166,67 +1211,67 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>181</v>
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
       </c>
       <c r="C4" s="1">
-        <v>1998</v>
+        <v>1971</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>218</v>
+        <v>174</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>219</v>
+        <v>175</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1998</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
-      </c>
-      <c r="G5" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>212</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1967</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1">
-        <v>1987</v>
+        <v>1967</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -1237,16 +1282,16 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>147</v>
+        <v>79</v>
       </c>
       <c r="C8" s="1">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -1257,81 +1302,96 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="C9" s="1">
-        <v>1970</v>
+        <v>1988</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>184</v>
+        <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>185</v>
+        <v>84</v>
       </c>
       <c r="C10" s="1">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>222</v>
+        <v>178</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C11" s="1">
         <v>1972</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>216</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>180</v>
       </c>
       <c r="C12" s="1">
-        <v>1981</v>
+        <v>1972</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>230</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="C13" s="1">
-        <v>2005</v>
+        <v>1973</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
@@ -1339,184 +1399,187 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="s">
-        <v>53</v>
+        <v>9</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>222</v>
       </c>
       <c r="C14" s="1">
-        <v>1970</v>
+        <v>1981</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
-      <c r="G14" s="1">
-        <v>2</v>
+      <c r="G14" s="1" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>149</v>
+        <v>81</v>
       </c>
       <c r="C15" s="1">
-        <v>2015</v>
+        <v>2005</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
-      </c>
-      <c r="G15" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>160</v>
+        <v>52</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1970</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="C17" s="1">
-        <v>1998</v>
+        <v>2015</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
       </c>
-      <c r="F17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>224</v>
+      <c r="G17" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>151</v>
+        <v>85</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
-      </c>
-      <c r="G18" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>152</v>
+        <v>27</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>153</v>
+        <v>28</v>
       </c>
       <c r="C19" s="1">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
       </c>
-      <c r="G19" s="1">
-        <v>2</v>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>228</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>49</v>
+        <v>229</v>
       </c>
       <c r="C20" s="1">
-        <v>1989</v>
+        <v>2008</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
-      </c>
-      <c r="G20" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="1">
-        <v>1969</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="E21" t="b">
         <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C22" s="1">
-        <v>1978</v>
+        <v>1996</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>193</v>
+        <v>48</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1989</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>134</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
@@ -1527,147 +1590,144 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>160</v>
+        <v>58</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1969</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="E24" t="b">
         <v>1</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="C25" s="1">
-        <v>1974</v>
+        <v>1978</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
       </c>
+      <c r="G25" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" s="1">
+      <c r="A26" t="s">
+        <v>186</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1978</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>236</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="1">
         <v>1982</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E26" t="b">
-        <v>1</v>
-      </c>
-      <c r="G26" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C27" s="1">
+      <c r="D29" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C30" s="1">
         <v>1977</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E27" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C28" s="1">
-        <v>1977</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E28" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" s="1">
-        <v>1964</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" s="1">
-        <v>1969</v>
-      </c>
       <c r="D30" s="1" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E30" t="b">
         <v>1</v>
       </c>
+      <c r="G30" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>214</v>
+      <c r="A31" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>215</v>
+        <v>108</v>
       </c>
       <c r="C31" s="1">
         <v>1977</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
@@ -1678,30 +1738,36 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>111</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>112</v>
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>87</v>
       </c>
       <c r="C32" s="1">
-        <v>1993</v>
+        <v>1964</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
       </c>
       <c r="G32" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>221</v>
+        <v>88</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1969</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
@@ -1712,67 +1778,68 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>208</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>160</v>
+        <v>219</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="1">
+        <v>2009</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="C35" s="1">
-        <v>1997</v>
+        <v>1977</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="E35" t="b">
         <v>1</v>
       </c>
       <c r="G35" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>196</v>
+        <v>105</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>197</v>
+        <v>106</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1993</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>134</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
       </c>
       <c r="G36" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C37" s="1">
-        <v>1982</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>136</v>
+        <v>215</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
@@ -1783,16 +1850,16 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>22</v>
-      </c>
-      <c r="B38" t="s">
-        <v>92</v>
-      </c>
-      <c r="C38" s="1">
-        <v>1979</v>
+        <v>202</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
@@ -1800,56 +1867,41 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="C39" s="1">
-        <v>2005</v>
+        <v>1997</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E39" t="b">
         <v>1</v>
       </c>
       <c r="G39" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>156</v>
+        <v>240</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>160</v>
+        <v>241</v>
       </c>
       <c r="E40" t="b">
         <v>1</v>
-      </c>
-      <c r="G40" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C41" s="1">
-        <v>1970</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>139</v>
+        <v>191</v>
       </c>
       <c r="E41" t="b">
         <v>1</v>
@@ -1860,22 +1912,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>68</v>
+        <v>200</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>69</v>
+        <v>201</v>
       </c>
       <c r="C42" s="1">
-        <v>1993</v>
+        <v>1982</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E42" t="b">
         <v>1</v>
       </c>
       <c r="G42" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -1886,55 +1938,52 @@
         <v>173</v>
       </c>
       <c r="C43" s="1">
-        <v>1970</v>
+        <v>2005</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E43" t="b">
         <v>1</v>
       </c>
-      <c r="F43" t="b">
-        <v>1</v>
-      </c>
       <c r="G43" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>18</v>
-      </c>
-      <c r="B44" t="s">
-        <v>93</v>
-      </c>
-      <c r="C44" s="1">
-        <v>1972</v>
+        <v>150</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="E44" t="b">
         <v>1</v>
+      </c>
+      <c r="G44" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="C45" s="1">
-        <v>2004</v>
+        <v>1970</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E45" t="b">
-        <v>1</v>
-      </c>
-      <c r="F45" t="b">
         <v>1</v>
       </c>
       <c r="G45" s="1">
@@ -1943,16 +1992,16 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>198</v>
+        <v>65</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>199</v>
+        <v>66</v>
       </c>
       <c r="C46" s="1">
-        <v>1996</v>
+        <v>1993</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
@@ -1963,36 +2012,39 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C47" s="1">
-        <v>1995</v>
+        <v>1970</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
       </c>
+      <c r="F47" t="b">
+        <v>1</v>
+      </c>
       <c r="G47" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>61</v>
+        <v>224</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>62</v>
+        <v>225</v>
       </c>
       <c r="C48" s="1">
-        <v>1979</v>
+        <v>1998</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E48" t="b">
         <v>1</v>
@@ -2000,53 +2052,59 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>19</v>
-      </c>
-      <c r="B49" t="s">
-        <v>94</v>
+        <v>18</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="C49" s="1">
-        <v>1979</v>
+        <v>1972</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E49" t="b">
         <v>1</v>
       </c>
-      <c r="G49" s="1">
-        <v>2</v>
+      <c r="G49" s="1" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="C50" s="1">
-        <v>1986</v>
+        <v>2004</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E50" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>115</v>
+        <v>192</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>116</v>
+        <v>193</v>
       </c>
       <c r="C51" s="1">
-        <v>1982</v>
+        <v>1996</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E51" t="b">
         <v>1</v>
@@ -2057,16 +2115,16 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="C52" s="1">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E52" t="b">
         <v>1</v>
@@ -2077,53 +2135,53 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="C53" s="1">
-        <v>1982</v>
+        <v>1979</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E53" t="b">
         <v>1</v>
-      </c>
-      <c r="G53" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>129</v>
-      </c>
-      <c r="B54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B54" t="s">
+        <v>90</v>
+      </c>
+      <c r="C54" s="1">
+        <v>1979</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C54" s="1">
-        <v>2008</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="E54" t="b">
         <v>1</v>
+      </c>
+      <c r="G54" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>72</v>
+        <v>238</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>160</v>
+        <v>239</v>
+      </c>
+      <c r="C55" s="1">
+        <v>1989</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="E55" t="b">
         <v>1</v>
@@ -2131,33 +2189,36 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>2</v>
-      </c>
-      <c r="B56" t="s">
-        <v>96</v>
+        <v>76</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="C56" s="1">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="C57" s="1">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E57" t="b">
         <v>1</v>
@@ -2168,13 +2229,13 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="C58" s="1">
-        <v>1973</v>
+        <v>1994</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>137</v>
@@ -2188,16 +2249,16 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>161</v>
+        <v>25</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="C59" s="1">
-        <v>1978</v>
+        <v>1982</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E59" t="b">
         <v>1</v>
@@ -2208,76 +2269,73 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C60" s="1">
-        <v>1989</v>
+        <v>2008</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E60" t="b">
         <v>1</v>
       </c>
-      <c r="G60" s="1">
-        <v>1</v>
+      <c r="G60" s="1" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C61" s="1">
-        <v>1981</v>
+        <v>70</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="E61" t="b">
         <v>1</v>
-      </c>
-      <c r="G61" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B62" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C62" s="1">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E62" t="b">
         <v>1</v>
       </c>
       <c r="G62" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="C63" s="1">
-        <v>1966</v>
+        <v>1981</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E63" t="b">
         <v>1</v>
@@ -2288,16 +2346,16 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="C64" s="1">
-        <v>1992</v>
+        <v>1973</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="E64" t="b">
         <v>1</v>
@@ -2308,64 +2366,76 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>85</v>
+        <v>155</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>86</v>
+        <v>156</v>
       </c>
       <c r="C65" s="1">
-        <v>1984</v>
+        <v>1978</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E65" t="b">
         <v>1</v>
+      </c>
+      <c r="G65" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>65</v>
+        <v>223</v>
       </c>
       <c r="C66" s="1">
-        <v>1979</v>
+        <v>1984</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E66" t="b">
         <v>1</v>
       </c>
-      <c r="G66" s="1">
-        <v>2</v>
+      <c r="G66" s="1" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>23</v>
-      </c>
-      <c r="B67" t="s">
-        <v>98</v>
+        <v>121</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="C67" s="1">
-        <v>1979</v>
+        <v>1989</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E67" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>163</v>
+        <v>95</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>164</v>
+        <v>96</v>
+      </c>
+      <c r="C68" s="1">
+        <v>1981</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="E68" t="b">
         <v>1</v>
@@ -2376,36 +2446,36 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B69" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C69" s="1">
-        <v>1970</v>
+        <v>1986</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E69" t="b">
         <v>1</v>
       </c>
       <c r="G69" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>3</v>
-      </c>
-      <c r="B70" t="s">
-        <v>102</v>
+        <v>44</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="C70" s="1">
-        <v>2015</v>
+        <v>1966</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="E70" t="b">
         <v>1</v>
@@ -2416,33 +2486,36 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>223</v>
+        <v>103</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="C71" s="1">
-        <v>1978</v>
+        <v>1992</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E71" t="b">
         <v>1</v>
+      </c>
+      <c r="G71" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="C72" s="1">
-        <v>1974</v>
+        <v>1984</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E72" t="b">
         <v>1</v>
@@ -2450,16 +2523,16 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>176</v>
+        <v>63</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>177</v>
+        <v>64</v>
       </c>
       <c r="C73" s="1">
-        <v>1976</v>
+        <v>1979</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E73" t="b">
         <v>1</v>
@@ -2470,16 +2543,16 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="C74" s="1">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E74" t="b">
         <v>1</v>
@@ -2487,16 +2560,10 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>6</v>
-      </c>
-      <c r="B75" t="s">
-        <v>103</v>
-      </c>
-      <c r="C75" s="1">
-        <v>1969</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>139</v>
+        <v>157</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="E75" t="b">
         <v>1</v>
@@ -2507,110 +2574,110 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>35</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>160</v>
+        <v>1</v>
+      </c>
+      <c r="B76" t="s">
+        <v>97</v>
+      </c>
+      <c r="C76" s="1">
+        <v>1970</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="E76" t="b">
         <v>1</v>
       </c>
       <c r="G76" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>174</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>175</v>
+        <v>3</v>
+      </c>
+      <c r="B77" t="s">
+        <v>98</v>
       </c>
       <c r="C77" s="1">
-        <v>2004</v>
+        <v>2015</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E77" t="b">
         <v>1</v>
+      </c>
+      <c r="G77" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>78</v>
+        <v>217</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="C78" s="1">
-        <v>1968</v>
+        <v>1978</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E78" t="b">
         <v>1</v>
-      </c>
-      <c r="G78" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>14</v>
+        <v>170</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>47</v>
+        <v>171</v>
       </c>
       <c r="C79" s="1">
-        <v>1971</v>
+        <v>1976</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E79" t="b">
         <v>1</v>
+      </c>
+      <c r="G79" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="C80" s="1">
-        <v>1985</v>
+        <v>1980</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E80" t="b">
         <v>1</v>
-      </c>
-      <c r="G80" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>37</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>38</v>
+        <v>6</v>
+      </c>
+      <c r="B81" t="s">
+        <v>99</v>
       </c>
       <c r="C81" s="1">
-        <v>1975</v>
+        <v>1969</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E81" t="b">
         <v>1</v>
@@ -2621,16 +2688,16 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>12</v>
-      </c>
-      <c r="B82" t="s">
-        <v>105</v>
-      </c>
-      <c r="C82" s="1">
-        <v>1970</v>
+        <v>34</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="E82" t="b">
         <v>1</v>
@@ -2641,36 +2708,33 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="C83" s="1">
-        <v>1995</v>
+        <v>2004</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E83" t="b">
         <v>1</v>
-      </c>
-      <c r="G83" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="C84" s="1">
-        <v>1975</v>
+        <v>1968</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E84" t="b">
         <v>1</v>
@@ -2681,16 +2745,16 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>183</v>
+        <v>46</v>
       </c>
       <c r="C85" s="1">
-        <v>1963</v>
+        <v>1971</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>205</v>
+        <v>132</v>
       </c>
       <c r="E85" t="b">
         <v>1</v>
@@ -2701,16 +2765,16 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>160</v>
+        <v>100</v>
+      </c>
+      <c r="C86" s="1">
+        <v>1985</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="E86" t="b">
         <v>1</v>
@@ -2721,36 +2785,33 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>119</v>
+        <v>234</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>120</v>
+        <v>235</v>
       </c>
       <c r="C87" s="1">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E87" t="b">
         <v>1</v>
-      </c>
-      <c r="G87" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>165</v>
+        <v>36</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>166</v>
+        <v>37</v>
       </c>
       <c r="C88" s="1">
-        <v>1967</v>
+        <v>1975</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E88" t="b">
         <v>1</v>
@@ -2761,16 +2822,16 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>125</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>126</v>
+        <v>12</v>
+      </c>
+      <c r="B89" t="s">
+        <v>101</v>
       </c>
       <c r="C89" s="1">
-        <v>1993</v>
+        <v>1970</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E89" t="b">
         <v>1</v>
@@ -2781,16 +2842,16 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>132</v>
+        <v>184</v>
       </c>
       <c r="C90" s="1">
-        <v>2004</v>
+        <v>1995</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E90" t="b">
         <v>1</v>
@@ -2801,16 +2862,16 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>168</v>
+        <v>59</v>
       </c>
       <c r="C91" s="1">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E91" t="b">
         <v>1</v>
@@ -2821,30 +2882,33 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>42</v>
+        <v>232</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>43</v>
+        <v>233</v>
       </c>
       <c r="C92" s="1">
-        <v>1970</v>
+        <v>2017</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E92" t="b">
         <v>1</v>
-      </c>
-      <c r="G92" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>201</v>
+        <v>177</v>
+      </c>
+      <c r="C93" s="1">
+        <v>1963</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="E93" t="b">
         <v>1</v>
@@ -2855,33 +2919,36 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>212</v>
+        <v>38</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C94" s="1">
-        <v>1970</v>
+        <v>39</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="E94" t="b">
         <v>1</v>
+      </c>
+      <c r="G94" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C95" s="1">
-        <v>2016</v>
+        <v>1976</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E95" t="b">
         <v>1</v>
@@ -2892,33 +2959,36 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C96" s="1">
-        <v>2000</v>
+        <v>1967</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E96" t="b">
         <v>1</v>
+      </c>
+      <c r="G96" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>16</v>
-      </c>
-      <c r="B97" t="s">
-        <v>106</v>
+        <v>119</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="C97" s="1">
-        <v>1969</v>
+        <v>1993</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E97" t="b">
         <v>1</v>
@@ -2929,84 +2999,84 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>70</v>
+        <v>220</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C98" s="1">
-        <v>1975</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>137</v>
+        <v>221</v>
       </c>
       <c r="E98" t="b">
         <v>1</v>
+      </c>
+      <c r="G98" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>8</v>
+        <v>125</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="C99" s="1">
-        <v>1989</v>
+        <v>2004</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E99" t="b">
         <v>1</v>
+      </c>
+      <c r="G99" s="1">
+        <v>4</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>21</v>
+        <v>161</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="C100" s="1">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E100" t="b">
         <v>1</v>
+      </c>
+      <c r="G100" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C101" s="1">
-        <v>2006</v>
+        <v>1970</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E101" t="b">
         <v>1</v>
       </c>
-      <c r="G101" s="1">
-        <v>5</v>
+      <c r="G101" s="1" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C102" s="1">
-        <v>2019</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="E102" t="b">
         <v>1</v>
@@ -3017,36 +3087,36 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C103" s="1">
-        <v>1998</v>
+        <v>1970</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E103" t="b">
         <v>1</v>
       </c>
-      <c r="G103" s="1">
-        <v>2</v>
+      <c r="G103" s="1" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="C104" s="1">
-        <v>1975</v>
+        <v>2016</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E104" t="b">
         <v>1</v>
@@ -3057,105 +3127,290 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>211</v>
+        <v>163</v>
       </c>
       <c r="C105" s="1">
+        <v>2000</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E105" t="b">
+        <v>1</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>16</v>
+      </c>
+      <c r="B106" t="s">
+        <v>102</v>
+      </c>
+      <c r="C106" s="1">
+        <v>1969</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E106" t="b">
+        <v>1</v>
+      </c>
+      <c r="G106" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>67</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C107" s="1">
+        <v>1975</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E107" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>8</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C108" s="1">
+        <v>1989</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E108" t="b">
+        <v>1</v>
+      </c>
+      <c r="G108" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>21</v>
+      </c>
+      <c r="C109" s="1">
+        <v>1979</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E109" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>53</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C110" s="1">
+        <v>2006</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E110" t="b">
+        <v>1</v>
+      </c>
+      <c r="G110" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>196</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C111" s="1">
+        <v>2019</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E111" t="b">
+        <v>1</v>
+      </c>
+      <c r="G111" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>203</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C112" s="1">
+        <v>1998</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E112" t="b">
+        <v>1</v>
+      </c>
+      <c r="G112" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>49</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C113" s="1">
+        <v>1975</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E113" t="b">
+        <v>1</v>
+      </c>
+      <c r="G113" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>204</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C114" s="1">
         <v>1970</v>
       </c>
-      <c r="D105" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E105" t="b">
-        <v>1</v>
+      <c r="D114" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E114" t="b">
+        <v>1</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{8227A597-9225-4357-B8B6-9F19CC6D2D47}"/>
-    <hyperlink ref="B17" r:id="rId2" xr:uid="{C440EE30-529A-4080-AE83-A4A978C3E02B}"/>
-    <hyperlink ref="B76" r:id="rId3" xr:uid="{C5FAAB38-5F1C-4A08-8709-401E7E23E0D1}"/>
-    <hyperlink ref="B81" r:id="rId4" xr:uid="{109EA93A-660A-4099-B212-FD77BC4B5297}"/>
-    <hyperlink ref="B86" r:id="rId5" xr:uid="{4FC29F3F-346D-4C86-81DD-BA31CA08B134}"/>
-    <hyperlink ref="B34" r:id="rId6" xr:uid="{98703E9F-F4A5-4829-8BBF-B9F807C63E68}"/>
-    <hyperlink ref="B92" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
-    <hyperlink ref="B24" r:id="rId8" xr:uid="{804D2DB9-BDF1-463B-9BD3-ACBFC15F041A}"/>
-    <hyperlink ref="B63" r:id="rId9" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
-    <hyperlink ref="B79" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
-    <hyperlink ref="B20" r:id="rId11" xr:uid="{DF6F8079-E647-4079-9719-72DC2FF3791C}"/>
-    <hyperlink ref="B104" r:id="rId12" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
-    <hyperlink ref="B101" r:id="rId13" xr:uid="{ECCFE763-5E69-4122-B27B-DA1C21FADA86}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{8227A597-9225-4357-B8B6-9F19CC6D2D47}"/>
+    <hyperlink ref="B19" r:id="rId2" xr:uid="{C440EE30-529A-4080-AE83-A4A978C3E02B}"/>
+    <hyperlink ref="B82" r:id="rId3" xr:uid="{C5FAAB38-5F1C-4A08-8709-401E7E23E0D1}"/>
+    <hyperlink ref="B88" r:id="rId4" xr:uid="{109EA93A-660A-4099-B212-FD77BC4B5297}"/>
+    <hyperlink ref="B94" r:id="rId5" xr:uid="{4FC29F3F-346D-4C86-81DD-BA31CA08B134}"/>
+    <hyperlink ref="B38" r:id="rId6" xr:uid="{98703E9F-F4A5-4829-8BBF-B9F807C63E68}"/>
+    <hyperlink ref="B101" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
+    <hyperlink ref="B27" r:id="rId8" xr:uid="{804D2DB9-BDF1-463B-9BD3-ACBFC15F041A}"/>
+    <hyperlink ref="B70" r:id="rId9" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
+    <hyperlink ref="B85" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
+    <hyperlink ref="B23" r:id="rId11" xr:uid="{DF6F8079-E647-4079-9719-72DC2FF3791C}"/>
+    <hyperlink ref="B113" r:id="rId12" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
+    <hyperlink ref="B110" r:id="rId13" xr:uid="{ECCFE763-5E69-4122-B27B-DA1C21FADA86}"/>
     <hyperlink ref="B2" r:id="rId14" xr:uid="{8869974B-11E2-4A99-8438-9F9B8ABEB9F6}"/>
-    <hyperlink ref="B21" r:id="rId15" display="mailto:elizabeth.casarella@gmail.com" xr:uid="{C150E814-8C96-4E50-8A55-5EB3344749B1}"/>
-    <hyperlink ref="B84" r:id="rId16" display="mailto:paul@levelbreaker.com" xr:uid="{9746CC3F-863E-4E18-931A-FADD4ED10BF2}"/>
-    <hyperlink ref="B48" r:id="rId17" xr:uid="{316BCF75-05DF-4572-9F46-9F76127C0677}"/>
-    <hyperlink ref="B71" r:id="rId18" display="mailto:dennis.p.oconnell@gmail.com" xr:uid="{57197F8F-1C51-4977-936A-74B15D239DF7}"/>
-    <hyperlink ref="B66" r:id="rId19" display="mailto:hef714@aol.com" xr:uid="{A4825BC7-F2DD-43E9-A39B-48544C54E403}"/>
-    <hyperlink ref="B72" r:id="rId20" xr:uid="{53A4A1D2-46D5-45C1-BB62-DA92169DD070}"/>
-    <hyperlink ref="B42" r:id="rId21" xr:uid="{A871275A-577B-4F01-A590-B30FBADA40A1}"/>
-    <hyperlink ref="B98" r:id="rId22" xr:uid="{7E7AC9EC-4484-43DC-8B81-7AA0BCCFA407}"/>
-    <hyperlink ref="B57" r:id="rId23" display="mailto:Gjhusky52@yahoo.com" xr:uid="{1F5D9E16-5BA9-4F8F-B8CF-14485F325E5D}"/>
-    <hyperlink ref="B99" r:id="rId24" display="mailto:s.vibberts@yahoo.com" xr:uid="{CD95CA65-C8C5-44B3-8AFC-2E088AEC194C}"/>
-    <hyperlink ref="B78" r:id="rId25" display="mailto:oldparsonage3@gmail.com" xr:uid="{DC8DA8C9-CCEA-4FC3-AA05-1EF34B65B0C1}"/>
-    <hyperlink ref="B50" r:id="rId26" xr:uid="{C2395B48-B35E-4045-A136-C8B31BE4A5FC}"/>
-    <hyperlink ref="B7" r:id="rId27" xr:uid="{37F7977A-EC68-4733-8738-6C53C959B816}"/>
-    <hyperlink ref="B13" r:id="rId28" display="mailto:cwb84122@gmail.com" xr:uid="{A209B655-7CEF-4F8D-BFEE-DFB49C33870B}"/>
-    <hyperlink ref="B65" r:id="rId29" display="mailto:Npmyers@sbcglobal.net" xr:uid="{46F1EE8C-941D-4D6B-A27A-3BDDA65A15CE}"/>
-    <hyperlink ref="B9" r:id="rId30" xr:uid="{647703FF-1796-4612-923D-2A3CF89F5A46}"/>
-    <hyperlink ref="B30" r:id="rId31" xr:uid="{D4F421DD-A322-4F00-A209-B464A28664A6}"/>
-    <hyperlink ref="B53" r:id="rId32" xr:uid="{5FF15619-CFAB-48CB-8BF0-78013919701C}"/>
-    <hyperlink ref="B61" r:id="rId33" display="mailto:Kmills8080@gmail.com" xr:uid="{6653A4F2-00C8-4ACF-A9B2-950ABB23037C}"/>
-    <hyperlink ref="B55" r:id="rId34" xr:uid="{0F8932AA-3F92-4F04-A82F-C839649C3558}"/>
-    <hyperlink ref="B80" r:id="rId35" xr:uid="{74573551-A238-45F0-95FA-078470676D33}"/>
-    <hyperlink ref="B64" r:id="rId36" xr:uid="{F093A50A-9255-43F2-873A-E61FB97B7B6E}"/>
-    <hyperlink ref="B25" r:id="rId37" display="mailto:joecorbo@icloud.com" xr:uid="{9664FD56-34AE-4697-8A23-BBA8942C6ABA}"/>
-    <hyperlink ref="B32" r:id="rId38" display="mailto:lostdogs@charter.net" xr:uid="{95D046AE-D83E-4029-8E4D-F457CDD3F23E}"/>
-    <hyperlink ref="B28" r:id="rId39" xr:uid="{93D1D532-1D29-4735-B6C3-7B9B46F15302}"/>
-    <hyperlink ref="B51" r:id="rId40" display="mailto:langer0125@gmail.com" xr:uid="{EF3BA7C4-32BE-431A-9979-8B42711B0D73}"/>
-    <hyperlink ref="B95" r:id="rId41" display="mailto:Ntjr05@gmail.com" xr:uid="{38DDEC56-F2AD-4C66-8377-3BFC9B7BDDB9}"/>
-    <hyperlink ref="B87" r:id="rId42" display="mailto:gregsinay3@gmail.com" xr:uid="{004C878C-63EB-40FC-B549-87CFABDE66E1}"/>
-    <hyperlink ref="B47" r:id="rId43" display="mailto:Suj9283@yahoo.com" xr:uid="{E8FF833B-A9E0-4AED-A7DB-065ED67E2244}"/>
-    <hyperlink ref="B74" r:id="rId44" display="mailto:djpal@zoominternet.net" xr:uid="{FAF882CB-F959-4D5E-B4E0-3608ADC9DA13}"/>
-    <hyperlink ref="B89" r:id="rId45" display="mailto:sosikiii@msn.com" xr:uid="{218E6BB5-6D46-4A2B-BD2C-6CF05A021B3C}"/>
-    <hyperlink ref="B54" r:id="rId46" display="mailto:Robertmlunn@gmail.com" xr:uid="{33551D8E-478C-410F-9E21-46488F70F42D}"/>
-    <hyperlink ref="B90" r:id="rId47" display="mailto:brisparks@gmail.com" xr:uid="{E8A49946-13F1-4C59-AD3D-A3E5B9D77EFF}"/>
-    <hyperlink ref="B52" r:id="rId48" display="mailto:Dlew44@gmail.com" xr:uid="{25AC56D9-918C-4162-BE04-DAA69217239F}"/>
-    <hyperlink ref="B8" r:id="rId49" xr:uid="{02619D1B-E12D-411C-8267-1EA72D337FA4}"/>
-    <hyperlink ref="B15" r:id="rId50" xr:uid="{297F912D-F1B3-4511-B9FB-7F6A5151679A}"/>
-    <hyperlink ref="B18" r:id="rId51" xr:uid="{23A72ED8-42A8-4AD2-AED4-16447BAE4A08}"/>
-    <hyperlink ref="B19" r:id="rId52" xr:uid="{5484D007-8240-489C-A613-B2C0F0F2AC56}"/>
-    <hyperlink ref="B22" r:id="rId53" xr:uid="{D01BE816-0B5A-4446-924C-46E6BAD18108}"/>
-    <hyperlink ref="B40" r:id="rId54" xr:uid="{276C5002-FCF1-4B64-9438-E4287F3F2787}"/>
-    <hyperlink ref="B58" r:id="rId55" xr:uid="{05B37D53-659E-462F-9D42-00105B550079}"/>
-    <hyperlink ref="B59" r:id="rId56" xr:uid="{F7EC428E-8409-4830-9429-9C5E7ABB09A4}"/>
-    <hyperlink ref="B68" r:id="rId57" xr:uid="{EE1C2C4D-03AE-46ED-A073-46B29C8D3689}"/>
-    <hyperlink ref="B88" r:id="rId58" xr:uid="{4C733EB2-A8CB-4A19-80B4-31601DA15BF2}"/>
-    <hyperlink ref="B91" r:id="rId59" xr:uid="{77C5CEA7-AAB7-4C0E-8FED-A2F21F462250}"/>
-    <hyperlink ref="B96" r:id="rId60" display="mailto:ryantimko@hotmail.com" xr:uid="{D3F25966-9FE3-42C3-94BB-54469D722B9E}"/>
-    <hyperlink ref="B45" r:id="rId61" display="mailto:bill.irwin58@gmail.com" xr:uid="{21398664-274B-466E-AEF3-003790919F40}"/>
-    <hyperlink ref="B43" r:id="rId62" display="mailto:Hogan6523@Yahoo.com" xr:uid="{8F033920-5D36-4035-9970-BF7A906D9337}"/>
-    <hyperlink ref="B77" r:id="rId63" xr:uid="{3915D652-1507-4F3C-AEB3-935E95D07A08}"/>
-    <hyperlink ref="B73" r:id="rId64" display="mailto:bernard.e.palmer@gmail.com" xr:uid="{4E7DEDEB-BA72-4331-A716-378C6A511DCC}"/>
-    <hyperlink ref="B39" r:id="rId65" display="mailto:fogs14@yahoo.com" xr:uid="{E734B4DB-161E-4386-9BE4-4D2A768C19C0}"/>
-    <hyperlink ref="B4" r:id="rId66" display="mailto:Robertalfaro@outlook.com" xr:uid="{94ECE3FB-34A8-40D2-A511-C6F49E1F79C8}"/>
-    <hyperlink ref="B85" r:id="rId67" xr:uid="{8042AEE0-2132-486D-AFC6-008B86CDABF9}"/>
-    <hyperlink ref="B27" r:id="rId68" display="mailto:rmdecambre@gmail.com" xr:uid="{61906EF9-7178-4E37-9EF5-F697B7AF8714}"/>
-    <hyperlink ref="B83" r:id="rId69" xr:uid="{C73311BF-B167-4642-BFA3-507299A38EFE}"/>
-    <hyperlink ref="B23" r:id="rId70" xr:uid="{A7D0DDDF-0E1D-4EAA-BC8A-6B20E1097E98}"/>
-    <hyperlink ref="B37" r:id="rId71" display="mailto:tfink9@juno.com" xr:uid="{34A73A04-8440-48B2-9348-0E4A6602D420}"/>
-    <hyperlink ref="B36" r:id="rId72" xr:uid="{0BB6B871-9927-4DD2-B508-224D22FD6229}"/>
-    <hyperlink ref="B93" r:id="rId73" xr:uid="{6DBAAB43-CE57-45EC-BCA9-CB408BBC84B6}"/>
-    <hyperlink ref="B102" r:id="rId74" xr:uid="{DB8385C7-8934-4CD0-B87E-4D74991BD43E}"/>
-    <hyperlink ref="B105" r:id="rId75" xr:uid="{CEB5326F-2589-4355-9CCD-6A3D6FC84E4A}"/>
-    <hyperlink ref="B94" r:id="rId76" xr:uid="{4A20E15A-8219-4697-83CE-53E329D1A594}"/>
-    <hyperlink ref="B31" r:id="rId77" xr:uid="{CB15C81B-047D-40F8-BDE8-B1539A6E2F0B}"/>
-    <hyperlink ref="B41" r:id="rId78" xr:uid="{B485936F-7DCD-4862-9E33-EEA8B063A75F}"/>
-    <hyperlink ref="B11" r:id="rId79" xr:uid="{74BFC159-A59B-4245-BC6C-B882819624B3}"/>
-    <hyperlink ref="B33" r:id="rId80" xr:uid="{F3187CCB-7830-43D4-9E21-FF900FE7F868}"/>
+    <hyperlink ref="B24" r:id="rId15" display="mailto:elizabeth.casarella@gmail.com" xr:uid="{C150E814-8C96-4E50-8A55-5EB3344749B1}"/>
+    <hyperlink ref="B91" r:id="rId16" display="mailto:paul@levelbreaker.com" xr:uid="{9746CC3F-863E-4E18-931A-FADD4ED10BF2}"/>
+    <hyperlink ref="B53" r:id="rId17" xr:uid="{316BCF75-05DF-4572-9F46-9F76127C0677}"/>
+    <hyperlink ref="B78" r:id="rId18" xr:uid="{57197F8F-1C51-4977-936A-74B15D239DF7}"/>
+    <hyperlink ref="B73" r:id="rId19" display="mailto:hef714@aol.com" xr:uid="{A4825BC7-F2DD-43E9-A39B-48544C54E403}"/>
+    <hyperlink ref="B46" r:id="rId20" xr:uid="{A871275A-577B-4F01-A590-B30FBADA40A1}"/>
+    <hyperlink ref="B107" r:id="rId21" xr:uid="{7E7AC9EC-4484-43DC-8B81-7AA0BCCFA407}"/>
+    <hyperlink ref="B63" r:id="rId22" display="mailto:Gjhusky52@yahoo.com" xr:uid="{1F5D9E16-5BA9-4F8F-B8CF-14485F325E5D}"/>
+    <hyperlink ref="B108" r:id="rId23" display="mailto:s.vibberts@yahoo.com" xr:uid="{CD95CA65-C8C5-44B3-8AFC-2E088AEC194C}"/>
+    <hyperlink ref="B84" r:id="rId24" display="mailto:oldparsonage3@gmail.com" xr:uid="{DC8DA8C9-CCEA-4FC3-AA05-1EF34B65B0C1}"/>
+    <hyperlink ref="B56" r:id="rId25" xr:uid="{C2395B48-B35E-4045-A136-C8B31BE4A5FC}"/>
+    <hyperlink ref="B8" r:id="rId26" xr:uid="{37F7977A-EC68-4733-8738-6C53C959B816}"/>
+    <hyperlink ref="B15" r:id="rId27" xr:uid="{A209B655-7CEF-4F8D-BFEE-DFB49C33870B}"/>
+    <hyperlink ref="B72" r:id="rId28" xr:uid="{46F1EE8C-941D-4D6B-A27A-3BDDA65A15CE}"/>
+    <hyperlink ref="B10" r:id="rId29" xr:uid="{647703FF-1796-4612-923D-2A3CF89F5A46}"/>
+    <hyperlink ref="B33" r:id="rId30" xr:uid="{D4F421DD-A322-4F00-A209-B464A28664A6}"/>
+    <hyperlink ref="B59" r:id="rId31" xr:uid="{5FF15619-CFAB-48CB-8BF0-78013919701C}"/>
+    <hyperlink ref="B68" r:id="rId32" display="mailto:Kmills8080@gmail.com" xr:uid="{6653A4F2-00C8-4ACF-A9B2-950ABB23037C}"/>
+    <hyperlink ref="B61" r:id="rId33" xr:uid="{0F8932AA-3F92-4F04-A82F-C839649C3558}"/>
+    <hyperlink ref="B86" r:id="rId34" xr:uid="{74573551-A238-45F0-95FA-078470676D33}"/>
+    <hyperlink ref="B71" r:id="rId35" xr:uid="{F093A50A-9255-43F2-873A-E61FB97B7B6E}"/>
+    <hyperlink ref="B36" r:id="rId36" display="mailto:lostdogs@charter.net" xr:uid="{95D046AE-D83E-4029-8E4D-F457CDD3F23E}"/>
+    <hyperlink ref="B31" r:id="rId37" xr:uid="{93D1D532-1D29-4735-B6C3-7B9B46F15302}"/>
+    <hyperlink ref="B57" r:id="rId38" display="mailto:langer0125@gmail.com" xr:uid="{EF3BA7C4-32BE-431A-9979-8B42711B0D73}"/>
+    <hyperlink ref="B104" r:id="rId39" display="mailto:Ntjr05@gmail.com" xr:uid="{38DDEC56-F2AD-4C66-8377-3BFC9B7BDDB9}"/>
+    <hyperlink ref="B95" r:id="rId40" display="mailto:gregsinay3@gmail.com" xr:uid="{004C878C-63EB-40FC-B549-87CFABDE66E1}"/>
+    <hyperlink ref="B52" r:id="rId41" display="mailto:Suj9283@yahoo.com" xr:uid="{E8FF833B-A9E0-4AED-A7DB-065ED67E2244}"/>
+    <hyperlink ref="B80" r:id="rId42" xr:uid="{FAF882CB-F959-4D5E-B4E0-3608ADC9DA13}"/>
+    <hyperlink ref="B97" r:id="rId43" display="mailto:sosikiii@msn.com" xr:uid="{218E6BB5-6D46-4A2B-BD2C-6CF05A021B3C}"/>
+    <hyperlink ref="B60" r:id="rId44" xr:uid="{33551D8E-478C-410F-9E21-46488F70F42D}"/>
+    <hyperlink ref="B99" r:id="rId45" display="mailto:brisparks@gmail.com" xr:uid="{E8A49946-13F1-4C59-AD3D-A3E5B9D77EFF}"/>
+    <hyperlink ref="B58" r:id="rId46" display="mailto:Dlew44@gmail.com" xr:uid="{25AC56D9-918C-4162-BE04-DAA69217239F}"/>
+    <hyperlink ref="B9" r:id="rId47" xr:uid="{02619D1B-E12D-411C-8267-1EA72D337FA4}"/>
+    <hyperlink ref="B17" r:id="rId48" xr:uid="{297F912D-F1B3-4511-B9FB-7F6A5151679A}"/>
+    <hyperlink ref="B21" r:id="rId49" xr:uid="{23A72ED8-42A8-4AD2-AED4-16447BAE4A08}"/>
+    <hyperlink ref="B22" r:id="rId50" xr:uid="{5484D007-8240-489C-A613-B2C0F0F2AC56}"/>
+    <hyperlink ref="B25" r:id="rId51" xr:uid="{D01BE816-0B5A-4446-924C-46E6BAD18108}"/>
+    <hyperlink ref="B44" r:id="rId52" xr:uid="{276C5002-FCF1-4B64-9438-E4287F3F2787}"/>
+    <hyperlink ref="B64" r:id="rId53" xr:uid="{05B37D53-659E-462F-9D42-00105B550079}"/>
+    <hyperlink ref="B65" r:id="rId54" xr:uid="{F7EC428E-8409-4830-9429-9C5E7ABB09A4}"/>
+    <hyperlink ref="B75" r:id="rId55" xr:uid="{EE1C2C4D-03AE-46ED-A073-46B29C8D3689}"/>
+    <hyperlink ref="B96" r:id="rId56" xr:uid="{4C733EB2-A8CB-4A19-80B4-31601DA15BF2}"/>
+    <hyperlink ref="B100" r:id="rId57" xr:uid="{77C5CEA7-AAB7-4C0E-8FED-A2F21F462250}"/>
+    <hyperlink ref="B105" r:id="rId58" xr:uid="{D3F25966-9FE3-42C3-94BB-54469D722B9E}"/>
+    <hyperlink ref="B50" r:id="rId59" display="mailto:bill.irwin58@gmail.com" xr:uid="{21398664-274B-466E-AEF3-003790919F40}"/>
+    <hyperlink ref="B47" r:id="rId60" display="mailto:Hogan6523@Yahoo.com" xr:uid="{8F033920-5D36-4035-9970-BF7A906D9337}"/>
+    <hyperlink ref="B83" r:id="rId61" xr:uid="{3915D652-1507-4F3C-AEB3-935E95D07A08}"/>
+    <hyperlink ref="B79" r:id="rId62" display="mailto:bernard.e.palmer@gmail.com" xr:uid="{4E7DEDEB-BA72-4331-A716-378C6A511DCC}"/>
+    <hyperlink ref="B43" r:id="rId63" display="mailto:fogs14@yahoo.com" xr:uid="{E734B4DB-161E-4386-9BE4-4D2A768C19C0}"/>
+    <hyperlink ref="B5" r:id="rId64" xr:uid="{94ECE3FB-34A8-40D2-A511-C6F49E1F79C8}"/>
+    <hyperlink ref="B93" r:id="rId65" xr:uid="{8042AEE0-2132-486D-AFC6-008B86CDABF9}"/>
+    <hyperlink ref="B30" r:id="rId66" display="mailto:rmdecambre@gmail.com" xr:uid="{61906EF9-7178-4E37-9EF5-F697B7AF8714}"/>
+    <hyperlink ref="B90" r:id="rId67" xr:uid="{C73311BF-B167-4642-BFA3-507299A38EFE}"/>
+    <hyperlink ref="B26" r:id="rId68" xr:uid="{A7D0DDDF-0E1D-4EAA-BC8A-6B20E1097E98}"/>
+    <hyperlink ref="B42" r:id="rId69" display="mailto:tfink9@juno.com" xr:uid="{34A73A04-8440-48B2-9348-0E4A6602D420}"/>
+    <hyperlink ref="B41" r:id="rId70" xr:uid="{0BB6B871-9927-4DD2-B508-224D22FD6229}"/>
+    <hyperlink ref="B102" r:id="rId71" xr:uid="{6DBAAB43-CE57-45EC-BCA9-CB408BBC84B6}"/>
+    <hyperlink ref="B111" r:id="rId72" xr:uid="{DB8385C7-8934-4CD0-B87E-4D74991BD43E}"/>
+    <hyperlink ref="B114" r:id="rId73" xr:uid="{CEB5326F-2589-4355-9CCD-6A3D6FC84E4A}"/>
+    <hyperlink ref="B103" r:id="rId74" xr:uid="{4A20E15A-8219-4697-83CE-53E329D1A594}"/>
+    <hyperlink ref="B35" r:id="rId75" xr:uid="{CB15C81B-047D-40F8-BDE8-B1539A6E2F0B}"/>
+    <hyperlink ref="B45" r:id="rId76" xr:uid="{B485936F-7DCD-4862-9E33-EEA8B063A75F}"/>
+    <hyperlink ref="B12" r:id="rId77" xr:uid="{74BFC159-A59B-4245-BC6C-B882819624B3}"/>
+    <hyperlink ref="B37" r:id="rId78" xr:uid="{F3187CCB-7830-43D4-9E21-FF900FE7F868}"/>
+    <hyperlink ref="B98" r:id="rId79" display="mailto:Sowell47@gmail.com" xr:uid="{03411C75-D37D-4435-805E-31377118488D}"/>
+    <hyperlink ref="B14" r:id="rId80" xr:uid="{6DB4A5CC-5D1F-4EF9-932C-678F4FC22DA9}"/>
+    <hyperlink ref="B18" r:id="rId81" xr:uid="{CF88E969-EAAC-46AC-8516-43C895BD47AD}"/>
+    <hyperlink ref="B49" r:id="rId82" xr:uid="{FC781576-FE15-492B-950C-DC624C8FF2B0}"/>
+    <hyperlink ref="B74" r:id="rId83" xr:uid="{0486C015-E59C-4C68-91D3-4ACAD00E12CD}"/>
+    <hyperlink ref="B48" r:id="rId84" display="mailto:Phuntone9@gmail.com" xr:uid="{97AD22F5-2C24-4F75-816F-70DD5E10F7E3}"/>
+    <hyperlink ref="B3" r:id="rId85" display="mailto:rasool@icgglobal.com" xr:uid="{8CC08D82-DC80-4069-A607-F03D467D475C}"/>
+    <hyperlink ref="B20" r:id="rId86" display="mailto:Steven.brouse@gmail.com" xr:uid="{0E704A9F-B2C5-4BBF-8D88-3BAC495E147F}"/>
+    <hyperlink ref="B13" r:id="rId87" display="mailto:j.b.internationalcellars@gmail.com" xr:uid="{839EF4EB-A6F8-43A3-B660-F7D49F2E61D4}"/>
+    <hyperlink ref="B92" r:id="rId88" display="mailto:Bryant.shirreffs@yahoo.com" xr:uid="{BA1A9DD0-A412-4686-BC81-5FFC622C25A9}"/>
+    <hyperlink ref="B87" r:id="rId89" display="mailto:jcpurl@aol.com" xr:uid="{E4621CD0-F8C1-458A-9567-BDCA1089D95C}"/>
+    <hyperlink ref="B28" r:id="rId90" display="mailto:jeremyclaflin6@gmail.com" xr:uid="{7538A4E0-FA80-4082-AB29-64F526F8CC24}"/>
+    <hyperlink ref="B55" r:id="rId91" display="mailto:landolfimark285@gmail.com" xr:uid="{20BF721A-932E-4360-ABD6-6884414072C6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId81"/>
+  <pageSetup orientation="portrait" r:id="rId92"/>
 </worksheet>
 </file>
--- a/UConnBleedBlue/wwwroot/Data/Players.xlsx
+++ b/UConnBleedBlue/wwwroot/Data/Players.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\UConnBleedBlue\UConnBleedBlue\wwwroot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF32069B-6656-4FE1-927B-04463074C214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C3B5AF-A999-49BE-922F-CCB9691D4DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1800" windowWidth="21600" windowHeight="13680" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
+    <workbookView xWindow="17355" yWindow="705" windowWidth="10350" windowHeight="13455" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="245">
   <si>
     <t>Demers, Kenny</t>
   </si>
@@ -707,9 +707,6 @@
     <t>jbarrett@draws.com</t>
   </si>
   <si>
-    <t>npmyers@sbcglobal.net</t>
-  </si>
-  <si>
     <t>Hunt, Philip</t>
   </si>
   <si>
@@ -762,6 +759,18 @@
   </si>
   <si>
     <t>rfenton2015@gmail.com</t>
+  </si>
+  <si>
+    <t>Moynihan, Dennis</t>
+  </si>
+  <si>
+    <t>moynihanjr@gmail.com</t>
+  </si>
+  <si>
+    <t>Wallace, Razul</t>
+  </si>
+  <si>
+    <t>Razulwallace@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -850,9 +859,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -890,7 +899,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -996,7 +1005,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1138,7 +1147,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1146,7 +1155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F97E2D-D2EE-4E19-AA28-ED70E4256082}">
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" customWidth="1"/>
@@ -1200,10 +1209,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>227</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -1382,10 +1391,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="C13" s="1">
         <v>1973</v>
@@ -1516,10 +1525,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>227</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>229</v>
       </c>
       <c r="C20" s="1">
         <v>2008</v>
@@ -1661,10 +1670,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>235</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>237</v>
       </c>
       <c r="C28" s="1">
         <v>2016</v>
@@ -1887,10 +1896,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>239</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>241</v>
       </c>
       <c r="E40" t="b">
         <v>1</v>
@@ -2035,10 +2044,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>223</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="C48" s="1">
         <v>1998</v>
@@ -2172,10 +2181,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>237</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="C55" s="1">
         <v>1989</v>
@@ -2386,13 +2395,13 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>223</v>
+        <v>122</v>
       </c>
       <c r="C66" s="1">
-        <v>1984</v>
+        <v>1989</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>134</v>
@@ -2400,88 +2409,85 @@
       <c r="E66" t="b">
         <v>1</v>
       </c>
-      <c r="G66" s="1" t="s">
-        <v>218</v>
+      <c r="G66" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="C67" s="1">
-        <v>1989</v>
+        <v>1981</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E67" t="b">
         <v>1</v>
       </c>
       <c r="G67" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>95</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>96</v>
+        <v>23</v>
+      </c>
+      <c r="B68" t="s">
+        <v>93</v>
       </c>
       <c r="C68" s="1">
-        <v>1981</v>
+        <v>1986</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E68" t="b">
         <v>1</v>
       </c>
       <c r="G68" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>23</v>
-      </c>
-      <c r="B69" t="s">
-        <v>93</v>
+        <v>44</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="C69" s="1">
-        <v>1986</v>
+        <v>1966</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E69" t="b">
         <v>1</v>
       </c>
       <c r="G69" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>44</v>
+        <v>241</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>45</v>
+        <v>242</v>
       </c>
       <c r="C70" s="1">
-        <v>1966</v>
+        <v>1992</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E70" t="b">
         <v>1</v>
-      </c>
-      <c r="G70" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -2785,10 +2791,10 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>233</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>235</v>
       </c>
       <c r="C87" s="1">
         <v>1977</v>
@@ -2882,10 +2888,10 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>231</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="C92" s="1">
         <v>2017</v>
@@ -3204,13 +3210,16 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>21</v>
+        <v>243</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="C109" s="1">
-        <v>1979</v>
+        <v>2002</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E109" t="b">
         <v>1</v>
@@ -3218,33 +3227,27 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>53</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="C110" s="1">
-        <v>2006</v>
+        <v>1979</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E110" t="b">
         <v>1</v>
-      </c>
-      <c r="G110" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>196</v>
+        <v>53</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="C111" s="1">
-        <v>2019</v>
+        <v>2006</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>135</v>
@@ -3253,21 +3256,21 @@
         <v>1</v>
       </c>
       <c r="G111" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C112" s="1">
-        <v>1998</v>
+        <v>2019</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E112" t="b">
         <v>1</v>
@@ -3278,16 +3281,16 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>49</v>
+        <v>203</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>50</v>
+        <v>198</v>
       </c>
       <c r="C113" s="1">
-        <v>1975</v>
+        <v>1998</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E113" t="b">
         <v>1</v>
@@ -3298,21 +3301,41 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>49</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C114" s="1">
+        <v>1975</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E114" t="b">
+        <v>1</v>
+      </c>
+      <c r="G114" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>204</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B115" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C114" s="1">
+      <c r="C115" s="1">
         <v>1970</v>
       </c>
-      <c r="D114" s="1" t="s">
+      <c r="D115" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E114" t="b">
-        <v>1</v>
-      </c>
-      <c r="G114" s="1" t="s">
+      <c r="E115" t="b">
+        <v>1</v>
+      </c>
+      <c r="G115" s="1" t="s">
         <v>218</v>
       </c>
     </row>
@@ -3326,11 +3349,11 @@
     <hyperlink ref="B38" r:id="rId6" xr:uid="{98703E9F-F4A5-4829-8BBF-B9F807C63E68}"/>
     <hyperlink ref="B101" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
     <hyperlink ref="B27" r:id="rId8" xr:uid="{804D2DB9-BDF1-463B-9BD3-ACBFC15F041A}"/>
-    <hyperlink ref="B70" r:id="rId9" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
+    <hyperlink ref="B69" r:id="rId9" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
     <hyperlink ref="B85" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
     <hyperlink ref="B23" r:id="rId11" xr:uid="{DF6F8079-E647-4079-9719-72DC2FF3791C}"/>
-    <hyperlink ref="B113" r:id="rId12" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
-    <hyperlink ref="B110" r:id="rId13" xr:uid="{ECCFE763-5E69-4122-B27B-DA1C21FADA86}"/>
+    <hyperlink ref="B114" r:id="rId12" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
+    <hyperlink ref="B111" r:id="rId13" xr:uid="{ECCFE763-5E69-4122-B27B-DA1C21FADA86}"/>
     <hyperlink ref="B2" r:id="rId14" xr:uid="{8869974B-11E2-4A99-8438-9F9B8ABEB9F6}"/>
     <hyperlink ref="B24" r:id="rId15" display="mailto:elizabeth.casarella@gmail.com" xr:uid="{C150E814-8C96-4E50-8A55-5EB3344749B1}"/>
     <hyperlink ref="B91" r:id="rId16" display="mailto:paul@levelbreaker.com" xr:uid="{9746CC3F-863E-4E18-931A-FADD4ED10BF2}"/>
@@ -3349,7 +3372,7 @@
     <hyperlink ref="B10" r:id="rId29" xr:uid="{647703FF-1796-4612-923D-2A3CF89F5A46}"/>
     <hyperlink ref="B33" r:id="rId30" xr:uid="{D4F421DD-A322-4F00-A209-B464A28664A6}"/>
     <hyperlink ref="B59" r:id="rId31" xr:uid="{5FF15619-CFAB-48CB-8BF0-78013919701C}"/>
-    <hyperlink ref="B68" r:id="rId32" display="mailto:Kmills8080@gmail.com" xr:uid="{6653A4F2-00C8-4ACF-A9B2-950ABB23037C}"/>
+    <hyperlink ref="B67" r:id="rId32" display="mailto:Kmills8080@gmail.com" xr:uid="{6653A4F2-00C8-4ACF-A9B2-950ABB23037C}"/>
     <hyperlink ref="B61" r:id="rId33" xr:uid="{0F8932AA-3F92-4F04-A82F-C839649C3558}"/>
     <hyperlink ref="B86" r:id="rId34" xr:uid="{74573551-A238-45F0-95FA-078470676D33}"/>
     <hyperlink ref="B71" r:id="rId35" xr:uid="{F093A50A-9255-43F2-873A-E61FB97B7B6E}"/>
@@ -3389,8 +3412,8 @@
     <hyperlink ref="B42" r:id="rId69" display="mailto:tfink9@juno.com" xr:uid="{34A73A04-8440-48B2-9348-0E4A6602D420}"/>
     <hyperlink ref="B41" r:id="rId70" xr:uid="{0BB6B871-9927-4DD2-B508-224D22FD6229}"/>
     <hyperlink ref="B102" r:id="rId71" xr:uid="{6DBAAB43-CE57-45EC-BCA9-CB408BBC84B6}"/>
-    <hyperlink ref="B111" r:id="rId72" xr:uid="{DB8385C7-8934-4CD0-B87E-4D74991BD43E}"/>
-    <hyperlink ref="B114" r:id="rId73" xr:uid="{CEB5326F-2589-4355-9CCD-6A3D6FC84E4A}"/>
+    <hyperlink ref="B112" r:id="rId72" xr:uid="{DB8385C7-8934-4CD0-B87E-4D74991BD43E}"/>
+    <hyperlink ref="B115" r:id="rId73" xr:uid="{CEB5326F-2589-4355-9CCD-6A3D6FC84E4A}"/>
     <hyperlink ref="B103" r:id="rId74" xr:uid="{4A20E15A-8219-4697-83CE-53E329D1A594}"/>
     <hyperlink ref="B35" r:id="rId75" xr:uid="{CB15C81B-047D-40F8-BDE8-B1539A6E2F0B}"/>
     <hyperlink ref="B45" r:id="rId76" xr:uid="{B485936F-7DCD-4862-9E33-EEA8B063A75F}"/>
@@ -3409,8 +3432,10 @@
     <hyperlink ref="B87" r:id="rId89" display="mailto:jcpurl@aol.com" xr:uid="{E4621CD0-F8C1-458A-9567-BDCA1089D95C}"/>
     <hyperlink ref="B28" r:id="rId90" display="mailto:jeremyclaflin6@gmail.com" xr:uid="{7538A4E0-FA80-4082-AB29-64F526F8CC24}"/>
     <hyperlink ref="B55" r:id="rId91" display="mailto:landolfimark285@gmail.com" xr:uid="{20BF721A-932E-4360-ABD6-6884414072C6}"/>
+    <hyperlink ref="B70" r:id="rId92" display="mailto:moynihanjr@gmail.com" xr:uid="{09EAB6B8-1CC0-499B-A77D-568323DE9156}"/>
+    <hyperlink ref="B109" r:id="rId93" display="mailto:Razulwallace@gmail.com" xr:uid="{9C945E29-299D-45FA-BA11-7A092AE0F910}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId92"/>
+  <pageSetup orientation="portrait" r:id="rId94"/>
 </worksheet>
 </file>
--- a/UConnBleedBlue/wwwroot/Data/Players.xlsx
+++ b/UConnBleedBlue/wwwroot/Data/Players.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\UConnBleedBlue\UConnBleedBlue\wwwroot\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CSharpRepos\UConnBleedBlue\UConnBleedBlue\wwwroot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C3B5AF-A999-49BE-922F-CCB9691D4DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93EFADC-E4C9-40BC-9819-06B1F1430433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17355" yWindow="705" windowWidth="10350" windowHeight="13455" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="499">
   <si>
     <t>Demers, Kenny</t>
   </si>
@@ -101,9 +101,6 @@
     <t>Scaffidi, Paul</t>
   </si>
   <si>
-    <t>Walton, Ted</t>
-  </si>
-  <si>
     <t>Ney, Tom</t>
   </si>
   <si>
@@ -695,9 +692,6 @@
     <t>Not Needed</t>
   </si>
   <si>
-    <t>Dixon, Andre</t>
-  </si>
-  <si>
     <t>Sowell, Taurien</t>
   </si>
   <si>
@@ -771,6 +765,774 @@
   </si>
   <si>
     <t>Razulwallace@gmail.com</t>
+  </si>
+  <si>
+    <t>Bertero,CB</t>
+  </si>
+  <si>
+    <t>cbbertero@gmail.com</t>
+  </si>
+  <si>
+    <t>Palmer,Chris</t>
+  </si>
+  <si>
+    <t>cpalmer10@comcast.net</t>
+  </si>
+  <si>
+    <t>Panciera,David</t>
+  </si>
+  <si>
+    <t>david.panciera@cox.net</t>
+  </si>
+  <si>
+    <t>McMichael,FD</t>
+  </si>
+  <si>
+    <t>fdmcmichael@gmail.com</t>
+  </si>
+  <si>
+    <t>Hughes,Hank</t>
+  </si>
+  <si>
+    <t>huhsesh@upenn.edu</t>
+  </si>
+  <si>
+    <t>Casaz,JB</t>
+  </si>
+  <si>
+    <t>jbcasaz@msn.com</t>
+  </si>
+  <si>
+    <t>Solomon,A</t>
+  </si>
+  <si>
+    <t>asolomon47@windstream.net</t>
+  </si>
+  <si>
+    <t>DeBenedictis,Al</t>
+  </si>
+  <si>
+    <t>adebenedictis17@comcast.net</t>
+  </si>
+  <si>
+    <t>Spagnuolo,Al</t>
+  </si>
+  <si>
+    <t>texhusky@swbell.net</t>
+  </si>
+  <si>
+    <t>Cummings,Alan</t>
+  </si>
+  <si>
+    <t>alangc6@gmail.com</t>
+  </si>
+  <si>
+    <t>MacLellan,Allan</t>
+  </si>
+  <si>
+    <t>taurusii@comcast.net</t>
+  </si>
+  <si>
+    <t>Breiner,Andrew</t>
+  </si>
+  <si>
+    <t>andrew.a.breiner@gmail.com</t>
+  </si>
+  <si>
+    <t>Yuen,Andy</t>
+  </si>
+  <si>
+    <t>andrewyuen@att.net</t>
+  </si>
+  <si>
+    <t>Cholawa,Bill</t>
+  </si>
+  <si>
+    <t>wcholawa@yahoo.com</t>
+  </si>
+  <si>
+    <t>Leahy,Bill</t>
+  </si>
+  <si>
+    <t>cocaqusa@gmail.com</t>
+  </si>
+  <si>
+    <t>Miller,Bill</t>
+  </si>
+  <si>
+    <t>millerwn@comcast.net</t>
+  </si>
+  <si>
+    <t>Roth,Bob</t>
+  </si>
+  <si>
+    <t>robsroth@gmail.com</t>
+  </si>
+  <si>
+    <t>Tice,Bob</t>
+  </si>
+  <si>
+    <t>bob.tice@tse-systems.com</t>
+  </si>
+  <si>
+    <t>Weiss,Bob</t>
+  </si>
+  <si>
+    <t>bobweiss44@gmail.com</t>
+  </si>
+  <si>
+    <t>Hoffman,Brian</t>
+  </si>
+  <si>
+    <t>brihoffm@gmail.com</t>
+  </si>
+  <si>
+    <t>Smith,Brian</t>
+  </si>
+  <si>
+    <t>brian@smitty.com</t>
+  </si>
+  <si>
+    <t>Usher,Brian</t>
+  </si>
+  <si>
+    <t>bjusr@yahoo.com</t>
+  </si>
+  <si>
+    <t>Marine,Bruce</t>
+  </si>
+  <si>
+    <t>bmarine@insurancechoices.com</t>
+  </si>
+  <si>
+    <t>byrequest1@aol.com</t>
+  </si>
+  <si>
+    <t>Baylor,Cedric</t>
+  </si>
+  <si>
+    <t>stagger24@gmail.com</t>
+  </si>
+  <si>
+    <t>Spelman,Chris</t>
+  </si>
+  <si>
+    <t>spelbound40@gmail.com</t>
+  </si>
+  <si>
+    <t>Goode,Chuch</t>
+  </si>
+  <si>
+    <t>rom828chuck@msn.com</t>
+  </si>
+  <si>
+    <t>Bourdreau,D</t>
+  </si>
+  <si>
+    <t>ddboudreau@att.net</t>
+  </si>
+  <si>
+    <t>Brown,D</t>
+  </si>
+  <si>
+    <t>dfbrown31@gmail.com</t>
+  </si>
+  <si>
+    <t>Roberts,D</t>
+  </si>
+  <si>
+    <t>droberts@fbba.org</t>
+  </si>
+  <si>
+    <t>Rose,Dan</t>
+  </si>
+  <si>
+    <t>danrose517@yahoo.com</t>
+  </si>
+  <si>
+    <t>Schwartz,Darryl</t>
+  </si>
+  <si>
+    <t>coachschwartz@hotmail.com</t>
+  </si>
+  <si>
+    <t>Korponai,Dave</t>
+  </si>
+  <si>
+    <t>davidkorponai02@yahoo.com</t>
+  </si>
+  <si>
+    <t>Kupec,Dave</t>
+  </si>
+  <si>
+    <t>dkupec1@yahoo.com</t>
+  </si>
+  <si>
+    <t>LaLima,Dave</t>
+  </si>
+  <si>
+    <t>DjLaLima51@gmail.com</t>
+  </si>
+  <si>
+    <t>Carlucci,Dom</t>
+  </si>
+  <si>
+    <t>domignite@yahoo.com</t>
+  </si>
+  <si>
+    <t>Dickson,Don</t>
+  </si>
+  <si>
+    <t>d-dickson@tamu.edu</t>
+  </si>
+  <si>
+    <t>Gaffney,Doug</t>
+  </si>
+  <si>
+    <t>dgaffney7@aol.com</t>
+  </si>
+  <si>
+    <t>Harvey,Ed</t>
+  </si>
+  <si>
+    <t>edwardharvey@msn.com</t>
+  </si>
+  <si>
+    <t>Jasudowich,Ed</t>
+  </si>
+  <si>
+    <t>edsgolfin@msn.com</t>
+  </si>
+  <si>
+    <t>Sadlon,Ed</t>
+  </si>
+  <si>
+    <t>ed.sadlon@comcast.net</t>
+  </si>
+  <si>
+    <t>Peterson,Eric</t>
+  </si>
+  <si>
+    <t>rp639@yahoo.com</t>
+  </si>
+  <si>
+    <t>Meeker,Eugene</t>
+  </si>
+  <si>
+    <t>eeagle814@aol.com</t>
+  </si>
+  <si>
+    <t>Blackney,Gary</t>
+  </si>
+  <si>
+    <t>grblackney@live.com</t>
+  </si>
+  <si>
+    <t>Campell,Gene</t>
+  </si>
+  <si>
+    <t>eugenecampbell@hotmail.com</t>
+  </si>
+  <si>
+    <t>Massa,Gene</t>
+  </si>
+  <si>
+    <t>massaeugene@sbcglobal.net</t>
+  </si>
+  <si>
+    <t>DeRoche,Garry</t>
+  </si>
+  <si>
+    <t>gerry@kgderoche.com</t>
+  </si>
+  <si>
+    <t>Gorski,Gregory</t>
+  </si>
+  <si>
+    <t>gragmgorski@yahoo.com</t>
+  </si>
+  <si>
+    <t>Cruz,Gus</t>
+  </si>
+  <si>
+    <t>gustavo.cruz@uconn.edu</t>
+  </si>
+  <si>
+    <t>Mazzocca,Gus</t>
+  </si>
+  <si>
+    <t>gusmazzocca2@gmail.com</t>
+  </si>
+  <si>
+    <t>Krukar,Henry</t>
+  </si>
+  <si>
+    <t>jkrukar@yahoo.com</t>
+  </si>
+  <si>
+    <t>Palasek,Henry</t>
+  </si>
+  <si>
+    <t>hpalasek@canbera.com</t>
+  </si>
+  <si>
+    <t>Parmalee,Henry</t>
+  </si>
+  <si>
+    <t>spinesense.hp@gmail.com</t>
+  </si>
+  <si>
+    <t>Beirne,J</t>
+  </si>
+  <si>
+    <t>jbeirne2316@yahoo.com</t>
+  </si>
+  <si>
+    <t>Muldowney,J</t>
+  </si>
+  <si>
+    <t>JMULDOWNEY0@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>Losh,Jack</t>
+  </si>
+  <si>
+    <t>highwyre9@aol.com</t>
+  </si>
+  <si>
+    <t>Mancuso,James</t>
+  </si>
+  <si>
+    <t>jim@certifiedelevator.com</t>
+  </si>
+  <si>
+    <t>Lesley,Lisa</t>
+  </si>
+  <si>
+    <t>Olzacki,James</t>
+  </si>
+  <si>
+    <t>zacko2@aol.com</t>
+  </si>
+  <si>
+    <t>Sproul,James</t>
+  </si>
+  <si>
+    <t>jsproul@sproulco.com</t>
+  </si>
+  <si>
+    <t>Pasqualoni,Jay</t>
+  </si>
+  <si>
+    <t>jay@atarza.com</t>
+  </si>
+  <si>
+    <t>Briggs,Jim</t>
+  </si>
+  <si>
+    <t>jimbriggsaz@gmail.com</t>
+  </si>
+  <si>
+    <t>Kern,Jim</t>
+  </si>
+  <si>
+    <t>kern_jim@msn.com</t>
+  </si>
+  <si>
+    <t>Corbo,Joe</t>
+  </si>
+  <si>
+    <t>joecorbo@icloud.com</t>
+  </si>
+  <si>
+    <t>Delucia,Joe</t>
+  </si>
+  <si>
+    <t>joedelucia@aol.com</t>
+  </si>
+  <si>
+    <t>Klinger,Joe</t>
+  </si>
+  <si>
+    <t>joeandpatct@cox.net</t>
+  </si>
+  <si>
+    <t>Pascale,Joe</t>
+  </si>
+  <si>
+    <t>joebucks99@aol.com</t>
+  </si>
+  <si>
+    <t>Smey,Joseph</t>
+  </si>
+  <si>
+    <t>joseph.smey@uconn.edu</t>
+  </si>
+  <si>
+    <t>Billingslea,John</t>
+  </si>
+  <si>
+    <t>rembeau@aol.com</t>
+  </si>
+  <si>
+    <t>Crisp,Jiohn</t>
+  </si>
+  <si>
+    <t>mailto:jcrisp@co.volusia.fl.us</t>
+  </si>
+  <si>
+    <t>Sadak,John</t>
+  </si>
+  <si>
+    <t>jaysfour@comcast.net</t>
+  </si>
+  <si>
+    <t>Sweeney,Tom</t>
+  </si>
+  <si>
+    <t>DaniaSweeney@aol.com</t>
+  </si>
+  <si>
+    <t>Stoddard,John</t>
+  </si>
+  <si>
+    <t>stod33@wctel.net</t>
+  </si>
+  <si>
+    <t>Trumbull,John</t>
+  </si>
+  <si>
+    <t>johntrumbull@att.net</t>
+  </si>
+  <si>
+    <t>Murphy,Justin</t>
+  </si>
+  <si>
+    <t>jmmurphy@outlook.com</t>
+  </si>
+  <si>
+    <t>Kraham,Keith</t>
+  </si>
+  <si>
+    <t>keith.kraham@gmail.com</t>
+  </si>
+  <si>
+    <t>Donlon,Ken</t>
+  </si>
+  <si>
+    <t>kjdonlon@gmail.com</t>
+  </si>
+  <si>
+    <t>Linder,Ken</t>
+  </si>
+  <si>
+    <t>kenly129@charter.net</t>
+  </si>
+  <si>
+    <t>Reyes,Kendall</t>
+  </si>
+  <si>
+    <t>krey926@gmail.com</t>
+  </si>
+  <si>
+    <t>Ward,Leah</t>
+  </si>
+  <si>
+    <t>leah.williams.ward@gmail.com</t>
+  </si>
+  <si>
+    <t>Solomon,Les</t>
+  </si>
+  <si>
+    <t>lsolomon3012@gmail.com</t>
+  </si>
+  <si>
+    <t>Feldman,Mark</t>
+  </si>
+  <si>
+    <t>feldmanm686@gmail.com</t>
+  </si>
+  <si>
+    <t>Flood,Mark</t>
+  </si>
+  <si>
+    <t>marksflood1@gmail.com</t>
+  </si>
+  <si>
+    <t>Malek,Mark</t>
+  </si>
+  <si>
+    <t>malekmark@hotmail.com</t>
+  </si>
+  <si>
+    <t>McEwen,Mark</t>
+  </si>
+  <si>
+    <t>mark.mcewen51@yahoo.com</t>
+  </si>
+  <si>
+    <t>Murphy,Mark</t>
+  </si>
+  <si>
+    <t>mark.murphy6@icloud.com</t>
+  </si>
+  <si>
+    <t>Olivier,Mathieu</t>
+  </si>
+  <si>
+    <t>mathieu.olivier1@gmail.com</t>
+  </si>
+  <si>
+    <t>Cersosimo,Matt</t>
+  </si>
+  <si>
+    <t>CersosimoMatt@gmail.com</t>
+  </si>
+  <si>
+    <t>Burton,Mike</t>
+  </si>
+  <si>
+    <t>Mike.Burton@cenveo.com</t>
+  </si>
+  <si>
+    <t>O'Roark,Mike</t>
+  </si>
+  <si>
+    <t>mikeoroark23@gmail.com</t>
+  </si>
+  <si>
+    <t>Pucko,Mike</t>
+  </si>
+  <si>
+    <t>mrpucko@verizon.net</t>
+  </si>
+  <si>
+    <t>Trottier,Norm</t>
+  </si>
+  <si>
+    <t>normtro@hotmail.com</t>
+  </si>
+  <si>
+    <t>Moran,P</t>
+  </si>
+  <si>
+    <t>pmoran8487@aol.com</t>
+  </si>
+  <si>
+    <t>D'Onofrio,Patrick</t>
+  </si>
+  <si>
+    <t>patrickdnfr@gmail.com</t>
+  </si>
+  <si>
+    <t>Gruner,Paul</t>
+  </si>
+  <si>
+    <t>paullgruner@aol.com</t>
+  </si>
+  <si>
+    <t>Mariano,Paul</t>
+  </si>
+  <si>
+    <t>pjmariano@charteroakfinancial.com</t>
+  </si>
+  <si>
+    <t>Tortolani,Paur</t>
+  </si>
+  <si>
+    <t>ptortolani@att.net</t>
+  </si>
+  <si>
+    <t>Lavenia,Pete</t>
+  </si>
+  <si>
+    <t>Doran,Phil</t>
+  </si>
+  <si>
+    <t>pdoran1@aol.com</t>
+  </si>
+  <si>
+    <t>Friedman,Phillip</t>
+  </si>
+  <si>
+    <t>pfafriedman@gmail.com</t>
+  </si>
+  <si>
+    <t>McCue,Randy</t>
+  </si>
+  <si>
+    <t>rrmccu@optonline.net</t>
+  </si>
+  <si>
+    <t>Giguire,Ray</t>
+  </si>
+  <si>
+    <t>rwgiguere@yahoo.com</t>
+  </si>
+  <si>
+    <t>Albonizio,Rick</t>
+  </si>
+  <si>
+    <t>zbird17@aol.com</t>
+  </si>
+  <si>
+    <t>Painter,Richard</t>
+  </si>
+  <si>
+    <t>richard2222@yahoo.com</t>
+  </si>
+  <si>
+    <t>McCollum,Ricky</t>
+  </si>
+  <si>
+    <t>rmccollum@cvsdvt.org</t>
+  </si>
+  <si>
+    <t>Ziemiecki,Rob</t>
+  </si>
+  <si>
+    <t>12946bahn@gmail.com</t>
+  </si>
+  <si>
+    <t>Ambrose,Rob</t>
+  </si>
+  <si>
+    <t>rambrose@towson.edu</t>
+  </si>
+  <si>
+    <t>Mansfield,Ron</t>
+  </si>
+  <si>
+    <t>ron.mansfield@att.net</t>
+  </si>
+  <si>
+    <t>Kehoe,Scott</t>
+  </si>
+  <si>
+    <t>Sweitzer,Scott</t>
+  </si>
+  <si>
+    <t>scottsweitzer12@gmail.com</t>
+  </si>
+  <si>
+    <t>Rajczewski,Stan</t>
+  </si>
+  <si>
+    <t>otuc@sbcglobal.net</t>
+  </si>
+  <si>
+    <t>Dixon,Steve</t>
+  </si>
+  <si>
+    <t>sddixon46@gmail.com</t>
+  </si>
+  <si>
+    <t>King,Steve</t>
+  </si>
+  <si>
+    <t>sakings@aol.com</t>
+  </si>
+  <si>
+    <t>Flig,Steve</t>
+  </si>
+  <si>
+    <t>sflig1@gmail.com</t>
+  </si>
+  <si>
+    <t>Small,Taber</t>
+  </si>
+  <si>
+    <t>tabersmall@yahoo.com</t>
+  </si>
+  <si>
+    <t>Mack,Taylor</t>
+  </si>
+  <si>
+    <t>29tmack@gmail.com</t>
+  </si>
+  <si>
+    <t>Clark,Terry</t>
+  </si>
+  <si>
+    <t>terrypclark@comcast.net</t>
+  </si>
+  <si>
+    <t>Ramsey,Terry</t>
+  </si>
+  <si>
+    <t>tkramsey29@gmail.com</t>
+  </si>
+  <si>
+    <t>Howarth,Tom</t>
+  </si>
+  <si>
+    <t>tom.Howarth67@gmail.com</t>
+  </si>
+  <si>
+    <t>Szarzynski,Tom</t>
+  </si>
+  <si>
+    <t>theszars@msn.com</t>
+  </si>
+  <si>
+    <t>Myers,Tommy</t>
+  </si>
+  <si>
+    <t>thomas.myers@uconn.edu</t>
+  </si>
+  <si>
+    <t>Stockton,T</t>
+  </si>
+  <si>
+    <t>tstockton@bsu.edu</t>
+  </si>
+  <si>
+    <t>Canzani,Vic</t>
+  </si>
+  <si>
+    <t>vcanzani@gmail.com</t>
+  </si>
+  <si>
+    <t>Kinon,Vic</t>
+  </si>
+  <si>
+    <t>vkinon@sh-law.com</t>
+  </si>
+  <si>
+    <t>Radzevich,Vic</t>
+  </si>
+  <si>
+    <t>vicj.radzevich@gmail.com</t>
+  </si>
+  <si>
+    <t>Clements,Vic</t>
+  </si>
+  <si>
+    <t>sueclements49@gmail.com</t>
+  </si>
+  <si>
+    <t>Iovino,Vic</t>
+  </si>
+  <si>
+    <t>viniovino@gmail.com</t>
+  </si>
+  <si>
+    <t>Anderson,Wally</t>
+  </si>
+  <si>
+    <t>wally@walteranderson3.com</t>
+  </si>
+  <si>
+    <t>Gilliard,Wilbur</t>
+  </si>
+  <si>
+    <t>hawkinsstreetmarketing@gmail.com</t>
+  </si>
+  <si>
+    <t>Hogan,William</t>
+  </si>
+  <si>
+    <t>bhogan847@hotmail.com</t>
   </si>
 </sst>
 </file>
@@ -1155,7 +1917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F97E2D-D2EE-4E19-AA28-ED70E4256082}">
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G242"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" customWidth="1"/>
@@ -1169,39 +1931,39 @@
   <sheetData>
     <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="G1" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="C2" s="1">
         <v>1977</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -1209,118 +1971,94 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>225</v>
+        <v>444</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
+        <v>445</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1971</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>132</v>
+        <v>223</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>224</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>174</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>175</v>
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
       </c>
       <c r="C5" s="1">
-        <v>1998</v>
+        <v>1971</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>213</v>
+        <v>174</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1998</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>134</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
-      </c>
-      <c r="G6" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>211</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1967</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>133</v>
+        <v>212</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>452</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1987</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1">
-        <v>2</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1">
-        <v>1988</v>
+        <v>1967</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
@@ -1331,56 +2069,44 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>493</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1970</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>218</v>
+        <v>494</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="C11" s="1">
-        <v>1972</v>
+        <v>1987</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>218</v>
+      <c r="G11" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>216</v>
+        <v>139</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="C12" s="1">
-        <v>1972</v>
+        <v>1988</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -1391,110 +2117,107 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>229</v>
+        <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>230</v>
+        <v>83</v>
       </c>
       <c r="C13" s="1">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>177</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>222</v>
+        <v>178</v>
       </c>
       <c r="C14" s="1">
-        <v>1981</v>
+        <v>1972</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>215</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="C15" s="1">
-        <v>2005</v>
+        <v>1972</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" t="s">
-        <v>52</v>
+        <v>227</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>228</v>
       </c>
       <c r="C16" s="1">
-        <v>1970</v>
+        <v>1973</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
-      </c>
-      <c r="G16" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>142</v>
+        <v>9</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>143</v>
+        <v>220</v>
       </c>
       <c r="C17" s="1">
-        <v>2015</v>
+        <v>1981</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
       </c>
-      <c r="G17" s="1">
-        <v>2</v>
+      <c r="G17" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>4</v>
+        <v>290</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>154</v>
+        <v>291</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
@@ -1502,39 +2225,24 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>348</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="1">
-        <v>1998</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E19" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>218</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>227</v>
+        <v>79</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>228</v>
+        <v>80</v>
       </c>
       <c r="C20" s="1">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
@@ -1542,107 +2250,74 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>144</v>
+        <v>243</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>154</v>
+        <v>244</v>
       </c>
       <c r="E21" t="b">
         <v>1</v>
-      </c>
-      <c r="G21" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>146</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>147</v>
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>51</v>
       </c>
       <c r="C22" s="1">
-        <v>1996</v>
+        <v>1970</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" s="1">
-        <v>1989</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E23" t="b">
-        <v>1</v>
-      </c>
-      <c r="G23" s="1">
-        <v>2</v>
+        <v>377</v>
+      </c>
+      <c r="B23" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1969</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E24" t="b">
-        <v>1</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>218</v>
+        <v>328</v>
+      </c>
+      <c r="B24" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>148</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C25" s="1">
-        <v>1978</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>130</v>
+        <v>296</v>
+      </c>
+      <c r="B25" t="s">
+        <v>297</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
-      </c>
-      <c r="G25" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>186</v>
+        <v>141</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>187</v>
+        <v>142</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2015</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="E26" t="b">
         <v>1</v>
@@ -1653,16 +2328,16 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="1">
-        <v>1978</v>
+        <v>84</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
@@ -1670,307 +2345,231 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>235</v>
+        <v>26</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>236</v>
+        <v>27</v>
       </c>
       <c r="C28" s="1">
-        <v>2016</v>
+        <v>1998</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
       </c>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C29" s="1">
-        <v>1982</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>130</v>
+      <c r="A29" t="s">
+        <v>265</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
       </c>
-      <c r="G29" s="1">
-        <v>2</v>
-      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>181</v>
+      <c r="A30" t="s">
+        <v>363</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C30" s="1">
-        <v>1977</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E30" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="1">
-        <v>1</v>
+        <v>364</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>107</v>
+      <c r="A31" t="s">
+        <v>225</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>108</v>
+        <v>226</v>
       </c>
       <c r="C31" s="1">
-        <v>1977</v>
+        <v>2008</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
-      </c>
-      <c r="G31" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>87</v>
-      </c>
-      <c r="C32" s="1">
-        <v>1964</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>136</v>
+        <v>298</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>299</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
-      </c>
-      <c r="G32" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>0</v>
+        <v>417</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C33" s="1">
-        <v>1969</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E33" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="1">
-        <v>2</v>
+        <v>418</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>219</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="1">
-        <v>2009</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>135</v>
+        <v>143</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>218</v>
+      <c r="G34" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>208</v>
+        <v>330</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C35" s="1">
-        <v>1977</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E35" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" s="1">
-        <v>2</v>
+        <v>331</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="C36" s="1">
-        <v>1993</v>
+        <v>1996</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
       </c>
       <c r="G36" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>214</v>
+        <v>483</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E37" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="1">
-        <v>2</v>
+        <v>484</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>202</v>
+        <v>46</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>154</v>
+        <v>47</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1989</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
+      </c>
+      <c r="G38" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>188</v>
+        <v>312</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C39" s="1">
-        <v>1997</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>137</v>
+        <v>313</v>
       </c>
       <c r="E39" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>239</v>
+        <v>56</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>240</v>
+        <v>57</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1969</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="E40" t="b">
         <v>1</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>190</v>
+        <v>253</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="E41" t="b">
         <v>1</v>
-      </c>
-      <c r="G41" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>200</v>
+        <v>147</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="C42" s="1">
-        <v>1982</v>
+        <v>1978</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E42" t="b">
         <v>1</v>
       </c>
       <c r="G42" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>172</v>
+        <v>415</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C43" s="1">
-        <v>2005</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E43" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" s="1">
-        <v>2</v>
+        <v>416</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="E44" t="b">
         <v>1</v>
@@ -1981,139 +2580,85 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>210</v>
+        <v>5</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>211</v>
+        <v>42</v>
       </c>
       <c r="C45" s="1">
-        <v>1970</v>
+        <v>1978</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E45" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>65</v>
+        <v>269</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C46" s="1">
-        <v>1993</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>134</v>
+        <v>270</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
-      </c>
-      <c r="G46" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>166</v>
+        <v>233</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>167</v>
+        <v>234</v>
       </c>
       <c r="C47" s="1">
-        <v>1970</v>
+        <v>2016</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E47" t="b">
-        <v>1</v>
-      </c>
-      <c r="F47" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>223</v>
+        <v>471</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C48" s="1">
-        <v>1998</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E48" t="b">
-        <v>1</v>
+        <v>472</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>18</v>
+        <v>489</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C49" s="1">
-        <v>1972</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E49" t="b">
-        <v>1</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>218</v>
+        <v>490</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>164</v>
+        <v>367</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C50" s="1">
-        <v>2004</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E50" t="b">
-        <v>1</v>
-      </c>
-      <c r="F50" t="b">
-        <v>1</v>
-      </c>
-      <c r="G50" s="1">
-        <v>1</v>
+        <v>368</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>192</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>193</v>
+      <c r="A51" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="C51" s="1">
-        <v>1996</v>
+        <v>1982</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="E51" t="b">
         <v>1</v>
@@ -2123,91 +2668,55 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>115</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C52" s="1">
-        <v>1995</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E52" t="b">
-        <v>1</v>
-      </c>
-      <c r="G52" s="1">
-        <v>2</v>
+      <c r="A52" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C53" s="1">
-        <v>1979</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E53" t="b">
-        <v>1</v>
+      <c r="A53" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>19</v>
-      </c>
-      <c r="B54" t="s">
-        <v>90</v>
-      </c>
-      <c r="C54" s="1">
-        <v>1979</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>130</v>
+      <c r="A54" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>262</v>
       </c>
       <c r="E54" t="b">
         <v>1</v>
-      </c>
-      <c r="G54" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="C55" s="1">
-        <v>1989</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>134</v>
+        <v>258</v>
       </c>
       <c r="E55" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>76</v>
+      <c r="A56" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>77</v>
+        <v>181</v>
       </c>
       <c r="C56" s="1">
-        <v>1986</v>
+        <v>1977</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E56" t="b">
         <v>1</v>
@@ -2217,17 +2726,17 @@
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>109</v>
+      <c r="A57" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C57" s="1">
-        <v>1982</v>
+        <v>1977</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E57" t="b">
         <v>1</v>
@@ -2237,37 +2746,25 @@
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>127</v>
+      <c r="A58" s="2" t="s">
+        <v>369</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C58" s="1">
-        <v>1994</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E58" t="b">
-        <v>1</v>
-      </c>
-      <c r="G58" s="1">
-        <v>2</v>
+        <v>370</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>25</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>91</v>
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>86</v>
       </c>
       <c r="C59" s="1">
-        <v>1982</v>
+        <v>1964</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E59" t="b">
         <v>1</v>
@@ -2278,153 +2775,90 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="C60" s="1">
-        <v>2008</v>
+        <v>1969</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E60" t="b">
         <v>1</v>
       </c>
-      <c r="G60" s="1" t="s">
-        <v>218</v>
+      <c r="G60" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>69</v>
+        <v>334</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E61" t="b">
-        <v>1</v>
+        <v>335</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>2</v>
-      </c>
-      <c r="B62" t="s">
-        <v>92</v>
-      </c>
-      <c r="C62" s="1">
-        <v>1987</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>134</v>
+        <v>314</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>315</v>
       </c>
       <c r="E62" t="b">
         <v>1</v>
-      </c>
-      <c r="G62" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>71</v>
+        <v>461</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>72</v>
+        <v>462</v>
       </c>
       <c r="C63" s="1">
-        <v>1981</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E63" t="b">
-        <v>1</v>
-      </c>
-      <c r="G63" s="1">
-        <v>2</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>152</v>
+        <v>393</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C64" s="1">
-        <v>1973</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E64" t="b">
-        <v>1</v>
-      </c>
-      <c r="G64" s="1">
-        <v>2</v>
+        <v>394</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>155</v>
+        <v>427</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C65" s="1">
-        <v>1978</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E65" t="b">
-        <v>1</v>
-      </c>
-      <c r="G65" s="1">
-        <v>2</v>
+        <v>428</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>121</v>
+        <v>436</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C66" s="1">
-        <v>1989</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E66" t="b">
-        <v>1</v>
-      </c>
-      <c r="G66" s="1">
-        <v>1</v>
+        <v>437</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>95</v>
+        <v>207</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>96</v>
+        <v>208</v>
       </c>
       <c r="C67" s="1">
-        <v>1981</v>
+        <v>1977</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E67" t="b">
         <v>1</v>
@@ -2435,16 +2869,16 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>23</v>
-      </c>
-      <c r="B68" t="s">
-        <v>93</v>
+        <v>104</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="C68" s="1">
-        <v>1986</v>
+        <v>1993</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E68" t="b">
         <v>1</v>
@@ -2455,16 +2889,10 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>44</v>
+        <v>213</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C69" s="1">
-        <v>1966</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>133</v>
+        <v>214</v>
       </c>
       <c r="E69" t="b">
         <v>1</v>
@@ -2475,16 +2903,16 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C70" s="1">
-        <v>1992</v>
+        <v>39</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="E70" t="b">
         <v>1</v>
@@ -2492,161 +2920,125 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>103</v>
+        <v>187</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>104</v>
+        <v>188</v>
       </c>
       <c r="C71" s="1">
-        <v>1992</v>
+        <v>1997</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E71" t="b">
         <v>1</v>
       </c>
       <c r="G71" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C72" s="1">
-        <v>1984</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E72" t="b">
-        <v>1</v>
+        <v>404</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>237</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C73" s="1">
-        <v>1979</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>130</v>
+        <v>238</v>
       </c>
       <c r="E73" t="b">
         <v>1</v>
-      </c>
-      <c r="G73" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>22</v>
+        <v>189</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C74" s="1">
-        <v>1979</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="E74" t="b">
         <v>1</v>
+      </c>
+      <c r="G74" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>157</v>
+        <v>199</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>158</v>
+        <v>200</v>
+      </c>
+      <c r="C75" s="1">
+        <v>1982</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="E75" t="b">
         <v>1</v>
       </c>
       <c r="G75" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B76" t="s">
-        <v>97</v>
-      </c>
-      <c r="C76" s="1">
-        <v>1970</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E76" t="b">
-        <v>1</v>
-      </c>
-      <c r="G76" s="1">
-        <v>2</v>
+        <v>465</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>3</v>
-      </c>
-      <c r="B77" t="s">
-        <v>98</v>
-      </c>
-      <c r="C77" s="1">
-        <v>2015</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E77" t="b">
-        <v>1</v>
-      </c>
-      <c r="G77" s="1">
-        <v>2</v>
+        <v>405</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>217</v>
+        <v>171</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>62</v>
+        <v>172</v>
       </c>
       <c r="C78" s="1">
-        <v>1978</v>
+        <v>2005</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E78" t="b">
         <v>1</v>
+      </c>
+      <c r="G78" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C79" s="1">
-        <v>1976</v>
+        <v>150</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="E79" t="b">
         <v>1</v>
@@ -2657,184 +3049,106 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>117</v>
+        <v>209</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>118</v>
+        <v>210</v>
       </c>
       <c r="C80" s="1">
-        <v>1980</v>
+        <v>1970</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E80" t="b">
+        <v>1</v>
+      </c>
+      <c r="G80" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>6</v>
-      </c>
-      <c r="B81" t="s">
-        <v>99</v>
-      </c>
-      <c r="C81" s="1">
-        <v>1969</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E81" t="b">
-        <v>1</v>
-      </c>
-      <c r="G81" s="1">
-        <v>2</v>
+        <v>438</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>34</v>
+        <v>316</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>154</v>
+        <v>317</v>
       </c>
       <c r="E82" t="b">
         <v>1</v>
-      </c>
-      <c r="G82" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>168</v>
+        <v>442</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C83" s="1">
-        <v>2004</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E83" t="b">
-        <v>1</v>
+        <v>443</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>75</v>
+        <v>495</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C84" s="1">
-        <v>1968</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E84" t="b">
-        <v>1</v>
-      </c>
-      <c r="G84" s="1">
-        <v>2</v>
+        <v>496</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>14</v>
+        <v>294</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C85" s="1">
-        <v>1971</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>132</v>
+        <v>295</v>
       </c>
       <c r="E85" t="b">
         <v>1</v>
-      </c>
-      <c r="G85" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>11</v>
+        <v>336</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C86" s="1">
-        <v>1985</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E86" t="b">
-        <v>1</v>
-      </c>
-      <c r="G86" s="1">
-        <v>2</v>
+        <v>337</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>233</v>
+        <v>429</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="C87" s="1">
-        <v>1977</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E87" t="b">
-        <v>1</v>
+        <v>430</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C88" s="1">
-        <v>1975</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>131</v>
+        <v>319</v>
       </c>
       <c r="E88" t="b">
         <v>1</v>
-      </c>
-      <c r="G88" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>12</v>
-      </c>
-      <c r="B89" t="s">
-        <v>101</v>
+        <v>64</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C89" s="1">
-        <v>1970</v>
+        <v>1993</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>133</v>
@@ -2848,207 +3162,156 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>183</v>
+        <v>281</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C90" s="1">
-        <v>1995</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>137</v>
+        <v>282</v>
       </c>
       <c r="E90" t="b">
         <v>1</v>
-      </c>
-      <c r="G90" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>59</v>
+        <v>166</v>
       </c>
       <c r="C91" s="1">
-        <v>1975</v>
+        <v>1970</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E91" t="b">
         <v>1</v>
       </c>
+      <c r="F91" t="b">
+        <v>1</v>
+      </c>
       <c r="G91" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>231</v>
+        <v>497</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C92" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E92" t="b">
-        <v>1</v>
+        <v>498</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>176</v>
+        <v>475</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C93" s="1">
-        <v>1963</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E93" t="b">
-        <v>1</v>
-      </c>
-      <c r="G93" s="1">
-        <v>2</v>
+        <v>476</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>38</v>
+        <v>221</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>154</v>
+        <v>222</v>
+      </c>
+      <c r="C94" s="1">
+        <v>1998</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="E94" t="b">
         <v>1</v>
-      </c>
-      <c r="G94" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>113</v>
+        <v>251</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C95" s="1">
-        <v>1976</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>131</v>
+        <v>252</v>
       </c>
       <c r="E95" t="b">
         <v>1</v>
-      </c>
-      <c r="G95" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="C96" s="1">
-        <v>1967</v>
+        <v>1972</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E96" t="b">
         <v>1</v>
       </c>
-      <c r="G96" s="1">
-        <v>2</v>
+      <c r="G96" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>119</v>
+        <v>491</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C97" s="1">
-        <v>1993</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E97" t="b">
-        <v>1</v>
-      </c>
-      <c r="G97" s="1">
-        <v>2</v>
+        <v>492</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>220</v>
+        <v>163</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>221</v>
+        <v>164</v>
+      </c>
+      <c r="C98" s="1">
+        <v>2004</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>134</v>
       </c>
       <c r="E98" t="b">
         <v>1</v>
       </c>
+      <c r="F98" t="b">
+        <v>1</v>
+      </c>
       <c r="G98" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>125</v>
+        <v>320</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C99" s="1">
-        <v>2004</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>135</v>
+        <v>321</v>
       </c>
       <c r="E99" t="b">
         <v>1</v>
-      </c>
-      <c r="G99" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="C100" s="1">
-        <v>1976</v>
+        <v>1996</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E100" t="b">
         <v>1</v>
@@ -3059,130 +3322,76 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>42</v>
+        <v>115</v>
       </c>
       <c r="C101" s="1">
-        <v>1970</v>
+        <v>1995</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E101" t="b">
         <v>1</v>
       </c>
-      <c r="G101" s="1" t="s">
-        <v>218</v>
+      <c r="G101" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>194</v>
+        <v>456</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E102" t="b">
-        <v>1</v>
-      </c>
-      <c r="G102" s="1">
-        <v>2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>206</v>
+        <v>365</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C103" s="1">
-        <v>1970</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E103" t="b">
-        <v>1</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>218</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>111</v>
+        <v>463</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C104" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E104" t="b">
-        <v>1</v>
-      </c>
-      <c r="G104" s="1">
-        <v>2</v>
+        <v>464</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>185</v>
+        <v>485</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C105" s="1">
-        <v>2000</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E105" t="b">
-        <v>1</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>218</v>
+        <v>486</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>16</v>
-      </c>
-      <c r="B106" t="s">
-        <v>102</v>
-      </c>
-      <c r="C106" s="1">
-        <v>1969</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E106" t="b">
-        <v>1</v>
-      </c>
-      <c r="G106" s="1">
-        <v>2</v>
+        <v>371</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C107" s="1">
-        <v>1975</v>
+        <v>1979</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E107" t="b">
         <v>1</v>
@@ -3190,127 +3399,76 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>8</v>
+        <v>306</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C108" s="1">
-        <v>1989</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>134</v>
+        <v>307</v>
       </c>
       <c r="E108" t="b">
         <v>1</v>
-      </c>
-      <c r="G108" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>243</v>
+        <v>391</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="C109" s="1">
-        <v>2002</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E109" t="b">
-        <v>1</v>
+        <v>392</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>21</v>
-      </c>
-      <c r="C110" s="1">
-        <v>1979</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E110" t="b">
-        <v>1</v>
+        <v>342</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C111" s="1">
-        <v>2006</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>135</v>
+        <v>309</v>
       </c>
       <c r="E111" t="b">
         <v>1</v>
-      </c>
-      <c r="G111" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>196</v>
+        <v>356</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C112" s="1">
-        <v>2019</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>135</v>
+        <v>289</v>
       </c>
       <c r="E112" t="b">
         <v>1</v>
-      </c>
-      <c r="G112" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>203</v>
+        <v>310</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C113" s="1">
-        <v>1998</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>137</v>
+        <v>311</v>
       </c>
       <c r="E113" t="b">
         <v>1</v>
-      </c>
-      <c r="G113" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>49</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>50</v>
+        <v>19</v>
+      </c>
+      <c r="B114" t="s">
+        <v>89</v>
       </c>
       <c r="C114" s="1">
-        <v>1975</v>
+        <v>1979</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E114" t="b">
         <v>1</v>
@@ -3321,13 +3479,13 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="C115" s="1">
-        <v>1970</v>
+        <v>1989</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>133</v>
@@ -3335,107 +3493,1854 @@
       <c r="E115" t="b">
         <v>1</v>
       </c>
-      <c r="G115" s="1" t="s">
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>75</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C116" s="1">
+        <v>1986</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E116" t="b">
+        <v>1</v>
+      </c>
+      <c r="G116" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>108</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C117" s="1">
+        <v>1982</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E117" t="b">
+        <v>1</v>
+      </c>
+      <c r="G117" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>435</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>271</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E119" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>126</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C120" s="1">
+        <v>1994</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E120" t="b">
+        <v>1</v>
+      </c>
+      <c r="G120" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>395</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>352</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>24</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C123" s="1">
+        <v>1982</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E123" t="b">
+        <v>1</v>
+      </c>
+      <c r="G123" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>122</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C124" s="1">
+        <v>2008</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E124" t="b">
+        <v>1</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>68</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E125" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>469</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>263</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E127" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>407</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>354</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>454</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>2</v>
+      </c>
+      <c r="B131" t="s">
+        <v>91</v>
+      </c>
+      <c r="C131" s="1">
+        <v>1987</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E131" t="b">
+        <v>1</v>
+      </c>
+      <c r="G131" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>431</v>
+      </c>
+      <c r="B132" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>287</v>
+      </c>
+      <c r="B133" t="s">
+        <v>288</v>
+      </c>
+      <c r="E133" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>70</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C134" s="1">
+        <v>1981</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E134" t="b">
+        <v>1</v>
+      </c>
+      <c r="G134" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>332</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>340</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>151</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C137" s="1">
+        <v>1973</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E137" t="b">
+        <v>1</v>
+      </c>
+      <c r="G137" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>448</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>440</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>409</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>154</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C141" s="1">
+        <v>1978</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E141" t="b">
+        <v>1</v>
+      </c>
+      <c r="G141" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>249</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E142" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>326</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E143" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>120</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C144" s="1">
+        <v>1989</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E144" t="b">
+        <v>1</v>
+      </c>
+      <c r="G144" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>273</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E145" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>94</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C146" s="1">
+        <v>1981</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E146" t="b">
+        <v>1</v>
+      </c>
+      <c r="G146" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>22</v>
+      </c>
+      <c r="B147" t="s">
+        <v>92</v>
+      </c>
+      <c r="C147" s="1">
+        <v>1986</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E147" t="b">
+        <v>1</v>
+      </c>
+      <c r="G147" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>425</v>
+      </c>
+      <c r="B148" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>43</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C149" s="1">
+        <v>1966</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E149" t="b">
+        <v>1</v>
+      </c>
+      <c r="G149" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>239</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C150" s="1">
+        <v>1992</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E150" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>350</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>102</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C152" s="1">
+        <v>1992</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E152" t="b">
+        <v>1</v>
+      </c>
+      <c r="G152" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>389</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>411</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>81</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C155" s="1">
+        <v>1984</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E155" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>479</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>62</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C157" s="1">
+        <v>1979</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E157" t="b">
+        <v>1</v>
+      </c>
+      <c r="G157" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>21</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C158" s="1">
+        <v>1979</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E158" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>156</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E159" t="b">
+        <v>1</v>
+      </c>
+      <c r="G159" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>1</v>
+      </c>
+      <c r="B160" t="s">
+        <v>96</v>
+      </c>
+      <c r="C160" s="1">
+        <v>1970</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E160" t="b">
+        <v>1</v>
+      </c>
+      <c r="G160" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>3</v>
+      </c>
+      <c r="B161" t="s">
+        <v>97</v>
+      </c>
+      <c r="C161" s="1">
+        <v>2015</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E161" t="b">
+        <v>1</v>
+      </c>
+      <c r="G161" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>216</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C162" s="1">
+        <v>1978</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E162" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>413</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>357</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>419</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>446</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>344</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>245</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E168" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>169</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C169" s="1">
+        <v>1976</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E169" t="b">
+        <v>1</v>
+      </c>
+      <c r="G169" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>116</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C170" s="1">
+        <v>1980</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E170" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>247</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E171" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>346</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>373</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>361</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>6</v>
+      </c>
+      <c r="B175" t="s">
+        <v>98</v>
+      </c>
+      <c r="C175" s="1">
+        <v>1969</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E175" t="b">
+        <v>1</v>
+      </c>
+      <c r="G175" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>33</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E176" t="b">
+        <v>1</v>
+      </c>
+      <c r="G176" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>167</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C177" s="1">
+        <v>2004</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E177" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>324</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E178" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>74</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C179" s="1">
+        <v>1968</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E179" t="b">
+        <v>1</v>
+      </c>
+      <c r="G179" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>14</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C180" s="1">
+        <v>1971</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E180" t="b">
+        <v>1</v>
+      </c>
+      <c r="G180" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>11</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C181" s="1">
+        <v>1985</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E181" t="b">
+        <v>1</v>
+      </c>
+      <c r="G181" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>421</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>231</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C183" s="1">
+        <v>1977</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E183" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>487</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>473</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>459</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>35</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C187" s="1">
+        <v>1975</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E187" t="b">
+        <v>1</v>
+      </c>
+      <c r="G187" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>397</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>300</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E189" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>12</v>
+      </c>
+      <c r="B190" t="s">
+        <v>100</v>
+      </c>
+      <c r="C190" s="1">
+        <v>1970</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E190" t="b">
+        <v>1</v>
+      </c>
+      <c r="G190" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>182</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C191" s="1">
+        <v>1995</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E191" t="b">
+        <v>1</v>
+      </c>
+      <c r="G191" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>302</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E192" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>275</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E193" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>381</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>322</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E195" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>20</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C196" s="1">
+        <v>1975</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E196" t="b">
+        <v>1</v>
+      </c>
+      <c r="G196" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>304</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E197" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>229</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C198" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E198" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>175</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C199" s="1">
+        <v>1963</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E199" t="b">
+        <v>1</v>
+      </c>
+      <c r="G199" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>37</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E200" t="b">
+        <v>1</v>
+      </c>
+      <c r="G200" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>112</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C201" s="1">
+        <v>1976</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E201" t="b">
+        <v>1</v>
+      </c>
+      <c r="G201" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>467</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>375</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>283</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="E204" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>158</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C205" s="1">
+        <v>1967</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E205" t="b">
+        <v>1</v>
+      </c>
+      <c r="G205" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>401</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>255</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E207" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>118</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C208" s="1">
+        <v>1993</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E208" t="b">
+        <v>1</v>
+      </c>
+      <c r="G208" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
         <v>218</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E209" t="b">
+        <v>1</v>
+      </c>
+      <c r="G209" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>259</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E210" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>124</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C211" s="1">
+        <v>2004</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E211" t="b">
+        <v>1</v>
+      </c>
+      <c r="G211" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>160</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C212" s="1">
+        <v>1976</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E212" t="b">
+        <v>1</v>
+      </c>
+      <c r="G212" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>292</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E213" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>359</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>481</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>385</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>40</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C217" s="1">
+        <v>1970</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E217" t="b">
+        <v>1</v>
+      </c>
+      <c r="G217" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>193</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E218" t="b">
+        <v>1</v>
+      </c>
+      <c r="G218" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>205</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C219" s="1">
+        <v>1970</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E219" t="b">
+        <v>1</v>
+      </c>
+      <c r="G219" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>383</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>457</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>477</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>110</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C223" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E223" t="b">
+        <v>1</v>
+      </c>
+      <c r="G223" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>277</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="E224" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>184</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C225" s="1">
+        <v>2000</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E225" t="b">
+        <v>1</v>
+      </c>
+      <c r="G225" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>16</v>
+      </c>
+      <c r="B226" t="s">
+        <v>101</v>
+      </c>
+      <c r="C226" s="1">
+        <v>1969</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E226" t="b">
+        <v>1</v>
+      </c>
+      <c r="G226" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>66</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C227" s="1">
+        <v>1975</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E227" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>433</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>423</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>387</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>285</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E231" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>8</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C232" s="1">
+        <v>1989</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E232" t="b">
+        <v>1</v>
+      </c>
+      <c r="G232" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>241</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C233" s="1">
+        <v>2002</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E233" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>399</v>
+      </c>
+      <c r="B234" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>52</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C235" s="1">
+        <v>2006</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E235" t="b">
+        <v>1</v>
+      </c>
+      <c r="G235" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>195</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C236" s="1">
+        <v>2019</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E236" t="b">
+        <v>1</v>
+      </c>
+      <c r="G236" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>279</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E237" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>202</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C238" s="1">
+        <v>1998</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E238" t="b">
+        <v>1</v>
+      </c>
+      <c r="G238" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>48</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C239" s="1">
+        <v>1975</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E239" t="b">
+        <v>1</v>
+      </c>
+      <c r="G239" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>267</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E240" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>450</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>203</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C242" s="1">
+        <v>1970</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E242" t="b">
+        <v>1</v>
+      </c>
+      <c r="G242" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{8227A597-9225-4357-B8B6-9F19CC6D2D47}"/>
-    <hyperlink ref="B19" r:id="rId2" xr:uid="{C440EE30-529A-4080-AE83-A4A978C3E02B}"/>
-    <hyperlink ref="B82" r:id="rId3" xr:uid="{C5FAAB38-5F1C-4A08-8709-401E7E23E0D1}"/>
-    <hyperlink ref="B88" r:id="rId4" xr:uid="{109EA93A-660A-4099-B212-FD77BC4B5297}"/>
-    <hyperlink ref="B94" r:id="rId5" xr:uid="{4FC29F3F-346D-4C86-81DD-BA31CA08B134}"/>
-    <hyperlink ref="B38" r:id="rId6" xr:uid="{98703E9F-F4A5-4829-8BBF-B9F807C63E68}"/>
-    <hyperlink ref="B101" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
-    <hyperlink ref="B27" r:id="rId8" xr:uid="{804D2DB9-BDF1-463B-9BD3-ACBFC15F041A}"/>
-    <hyperlink ref="B69" r:id="rId9" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
-    <hyperlink ref="B85" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
-    <hyperlink ref="B23" r:id="rId11" xr:uid="{DF6F8079-E647-4079-9719-72DC2FF3791C}"/>
-    <hyperlink ref="B114" r:id="rId12" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
-    <hyperlink ref="B111" r:id="rId13" xr:uid="{ECCFE763-5E69-4122-B27B-DA1C21FADA86}"/>
+    <hyperlink ref="B9" r:id="rId1" xr:uid="{8227A597-9225-4357-B8B6-9F19CC6D2D47}"/>
+    <hyperlink ref="B28" r:id="rId2" xr:uid="{C440EE30-529A-4080-AE83-A4A978C3E02B}"/>
+    <hyperlink ref="B176" r:id="rId3" xr:uid="{C5FAAB38-5F1C-4A08-8709-401E7E23E0D1}"/>
+    <hyperlink ref="B187" r:id="rId4" xr:uid="{109EA93A-660A-4099-B212-FD77BC4B5297}"/>
+    <hyperlink ref="B200" r:id="rId5" xr:uid="{4FC29F3F-346D-4C86-81DD-BA31CA08B134}"/>
+    <hyperlink ref="B70" r:id="rId6" xr:uid="{98703E9F-F4A5-4829-8BBF-B9F807C63E68}"/>
+    <hyperlink ref="B217" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
+    <hyperlink ref="B45" r:id="rId8" xr:uid="{804D2DB9-BDF1-463B-9BD3-ACBFC15F041A}"/>
+    <hyperlink ref="B149" r:id="rId9" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
+    <hyperlink ref="B180" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
+    <hyperlink ref="B38" r:id="rId11" xr:uid="{DF6F8079-E647-4079-9719-72DC2FF3791C}"/>
+    <hyperlink ref="B239" r:id="rId12" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
+    <hyperlink ref="B235" r:id="rId13" xr:uid="{ECCFE763-5E69-4122-B27B-DA1C21FADA86}"/>
     <hyperlink ref="B2" r:id="rId14" xr:uid="{8869974B-11E2-4A99-8438-9F9B8ABEB9F6}"/>
-    <hyperlink ref="B24" r:id="rId15" display="mailto:elizabeth.casarella@gmail.com" xr:uid="{C150E814-8C96-4E50-8A55-5EB3344749B1}"/>
-    <hyperlink ref="B91" r:id="rId16" display="mailto:paul@levelbreaker.com" xr:uid="{9746CC3F-863E-4E18-931A-FADD4ED10BF2}"/>
-    <hyperlink ref="B53" r:id="rId17" xr:uid="{316BCF75-05DF-4572-9F46-9F76127C0677}"/>
-    <hyperlink ref="B78" r:id="rId18" xr:uid="{57197F8F-1C51-4977-936A-74B15D239DF7}"/>
-    <hyperlink ref="B73" r:id="rId19" display="mailto:hef714@aol.com" xr:uid="{A4825BC7-F2DD-43E9-A39B-48544C54E403}"/>
-    <hyperlink ref="B46" r:id="rId20" xr:uid="{A871275A-577B-4F01-A590-B30FBADA40A1}"/>
-    <hyperlink ref="B107" r:id="rId21" xr:uid="{7E7AC9EC-4484-43DC-8B81-7AA0BCCFA407}"/>
-    <hyperlink ref="B63" r:id="rId22" display="mailto:Gjhusky52@yahoo.com" xr:uid="{1F5D9E16-5BA9-4F8F-B8CF-14485F325E5D}"/>
-    <hyperlink ref="B108" r:id="rId23" display="mailto:s.vibberts@yahoo.com" xr:uid="{CD95CA65-C8C5-44B3-8AFC-2E088AEC194C}"/>
-    <hyperlink ref="B84" r:id="rId24" display="mailto:oldparsonage3@gmail.com" xr:uid="{DC8DA8C9-CCEA-4FC3-AA05-1EF34B65B0C1}"/>
-    <hyperlink ref="B56" r:id="rId25" xr:uid="{C2395B48-B35E-4045-A136-C8B31BE4A5FC}"/>
-    <hyperlink ref="B8" r:id="rId26" xr:uid="{37F7977A-EC68-4733-8738-6C53C959B816}"/>
-    <hyperlink ref="B15" r:id="rId27" xr:uid="{A209B655-7CEF-4F8D-BFEE-DFB49C33870B}"/>
-    <hyperlink ref="B72" r:id="rId28" xr:uid="{46F1EE8C-941D-4D6B-A27A-3BDDA65A15CE}"/>
-    <hyperlink ref="B10" r:id="rId29" xr:uid="{647703FF-1796-4612-923D-2A3CF89F5A46}"/>
-    <hyperlink ref="B33" r:id="rId30" xr:uid="{D4F421DD-A322-4F00-A209-B464A28664A6}"/>
-    <hyperlink ref="B59" r:id="rId31" xr:uid="{5FF15619-CFAB-48CB-8BF0-78013919701C}"/>
-    <hyperlink ref="B67" r:id="rId32" display="mailto:Kmills8080@gmail.com" xr:uid="{6653A4F2-00C8-4ACF-A9B2-950ABB23037C}"/>
-    <hyperlink ref="B61" r:id="rId33" xr:uid="{0F8932AA-3F92-4F04-A82F-C839649C3558}"/>
-    <hyperlink ref="B86" r:id="rId34" xr:uid="{74573551-A238-45F0-95FA-078470676D33}"/>
-    <hyperlink ref="B71" r:id="rId35" xr:uid="{F093A50A-9255-43F2-873A-E61FB97B7B6E}"/>
-    <hyperlink ref="B36" r:id="rId36" display="mailto:lostdogs@charter.net" xr:uid="{95D046AE-D83E-4029-8E4D-F457CDD3F23E}"/>
-    <hyperlink ref="B31" r:id="rId37" xr:uid="{93D1D532-1D29-4735-B6C3-7B9B46F15302}"/>
-    <hyperlink ref="B57" r:id="rId38" display="mailto:langer0125@gmail.com" xr:uid="{EF3BA7C4-32BE-431A-9979-8B42711B0D73}"/>
-    <hyperlink ref="B104" r:id="rId39" display="mailto:Ntjr05@gmail.com" xr:uid="{38DDEC56-F2AD-4C66-8377-3BFC9B7BDDB9}"/>
-    <hyperlink ref="B95" r:id="rId40" display="mailto:gregsinay3@gmail.com" xr:uid="{004C878C-63EB-40FC-B549-87CFABDE66E1}"/>
-    <hyperlink ref="B52" r:id="rId41" display="mailto:Suj9283@yahoo.com" xr:uid="{E8FF833B-A9E0-4AED-A7DB-065ED67E2244}"/>
-    <hyperlink ref="B80" r:id="rId42" xr:uid="{FAF882CB-F959-4D5E-B4E0-3608ADC9DA13}"/>
-    <hyperlink ref="B97" r:id="rId43" display="mailto:sosikiii@msn.com" xr:uid="{218E6BB5-6D46-4A2B-BD2C-6CF05A021B3C}"/>
-    <hyperlink ref="B60" r:id="rId44" xr:uid="{33551D8E-478C-410F-9E21-46488F70F42D}"/>
-    <hyperlink ref="B99" r:id="rId45" display="mailto:brisparks@gmail.com" xr:uid="{E8A49946-13F1-4C59-AD3D-A3E5B9D77EFF}"/>
-    <hyperlink ref="B58" r:id="rId46" display="mailto:Dlew44@gmail.com" xr:uid="{25AC56D9-918C-4162-BE04-DAA69217239F}"/>
-    <hyperlink ref="B9" r:id="rId47" xr:uid="{02619D1B-E12D-411C-8267-1EA72D337FA4}"/>
-    <hyperlink ref="B17" r:id="rId48" xr:uid="{297F912D-F1B3-4511-B9FB-7F6A5151679A}"/>
-    <hyperlink ref="B21" r:id="rId49" xr:uid="{23A72ED8-42A8-4AD2-AED4-16447BAE4A08}"/>
-    <hyperlink ref="B22" r:id="rId50" xr:uid="{5484D007-8240-489C-A613-B2C0F0F2AC56}"/>
-    <hyperlink ref="B25" r:id="rId51" xr:uid="{D01BE816-0B5A-4446-924C-46E6BAD18108}"/>
-    <hyperlink ref="B44" r:id="rId52" xr:uid="{276C5002-FCF1-4B64-9438-E4287F3F2787}"/>
-    <hyperlink ref="B64" r:id="rId53" xr:uid="{05B37D53-659E-462F-9D42-00105B550079}"/>
-    <hyperlink ref="B65" r:id="rId54" xr:uid="{F7EC428E-8409-4830-9429-9C5E7ABB09A4}"/>
-    <hyperlink ref="B75" r:id="rId55" xr:uid="{EE1C2C4D-03AE-46ED-A073-46B29C8D3689}"/>
-    <hyperlink ref="B96" r:id="rId56" xr:uid="{4C733EB2-A8CB-4A19-80B4-31601DA15BF2}"/>
-    <hyperlink ref="B100" r:id="rId57" xr:uid="{77C5CEA7-AAB7-4C0E-8FED-A2F21F462250}"/>
-    <hyperlink ref="B105" r:id="rId58" xr:uid="{D3F25966-9FE3-42C3-94BB-54469D722B9E}"/>
-    <hyperlink ref="B50" r:id="rId59" display="mailto:bill.irwin58@gmail.com" xr:uid="{21398664-274B-466E-AEF3-003790919F40}"/>
-    <hyperlink ref="B47" r:id="rId60" display="mailto:Hogan6523@Yahoo.com" xr:uid="{8F033920-5D36-4035-9970-BF7A906D9337}"/>
-    <hyperlink ref="B83" r:id="rId61" xr:uid="{3915D652-1507-4F3C-AEB3-935E95D07A08}"/>
-    <hyperlink ref="B79" r:id="rId62" display="mailto:bernard.e.palmer@gmail.com" xr:uid="{4E7DEDEB-BA72-4331-A716-378C6A511DCC}"/>
-    <hyperlink ref="B43" r:id="rId63" display="mailto:fogs14@yahoo.com" xr:uid="{E734B4DB-161E-4386-9BE4-4D2A768C19C0}"/>
-    <hyperlink ref="B5" r:id="rId64" xr:uid="{94ECE3FB-34A8-40D2-A511-C6F49E1F79C8}"/>
-    <hyperlink ref="B93" r:id="rId65" xr:uid="{8042AEE0-2132-486D-AFC6-008B86CDABF9}"/>
-    <hyperlink ref="B30" r:id="rId66" display="mailto:rmdecambre@gmail.com" xr:uid="{61906EF9-7178-4E37-9EF5-F697B7AF8714}"/>
-    <hyperlink ref="B90" r:id="rId67" xr:uid="{C73311BF-B167-4642-BFA3-507299A38EFE}"/>
-    <hyperlink ref="B26" r:id="rId68" xr:uid="{A7D0DDDF-0E1D-4EAA-BC8A-6B20E1097E98}"/>
-    <hyperlink ref="B42" r:id="rId69" display="mailto:tfink9@juno.com" xr:uid="{34A73A04-8440-48B2-9348-0E4A6602D420}"/>
-    <hyperlink ref="B41" r:id="rId70" xr:uid="{0BB6B871-9927-4DD2-B508-224D22FD6229}"/>
-    <hyperlink ref="B102" r:id="rId71" xr:uid="{6DBAAB43-CE57-45EC-BCA9-CB408BBC84B6}"/>
-    <hyperlink ref="B112" r:id="rId72" xr:uid="{DB8385C7-8934-4CD0-B87E-4D74991BD43E}"/>
-    <hyperlink ref="B115" r:id="rId73" xr:uid="{CEB5326F-2589-4355-9CCD-6A3D6FC84E4A}"/>
-    <hyperlink ref="B103" r:id="rId74" xr:uid="{4A20E15A-8219-4697-83CE-53E329D1A594}"/>
-    <hyperlink ref="B35" r:id="rId75" xr:uid="{CB15C81B-047D-40F8-BDE8-B1539A6E2F0B}"/>
-    <hyperlink ref="B45" r:id="rId76" xr:uid="{B485936F-7DCD-4862-9E33-EEA8B063A75F}"/>
-    <hyperlink ref="B12" r:id="rId77" xr:uid="{74BFC159-A59B-4245-BC6C-B882819624B3}"/>
-    <hyperlink ref="B37" r:id="rId78" xr:uid="{F3187CCB-7830-43D4-9E21-FF900FE7F868}"/>
-    <hyperlink ref="B98" r:id="rId79" display="mailto:Sowell47@gmail.com" xr:uid="{03411C75-D37D-4435-805E-31377118488D}"/>
-    <hyperlink ref="B14" r:id="rId80" xr:uid="{6DB4A5CC-5D1F-4EF9-932C-678F4FC22DA9}"/>
-    <hyperlink ref="B18" r:id="rId81" xr:uid="{CF88E969-EAAC-46AC-8516-43C895BD47AD}"/>
-    <hyperlink ref="B49" r:id="rId82" xr:uid="{FC781576-FE15-492B-950C-DC624C8FF2B0}"/>
-    <hyperlink ref="B74" r:id="rId83" xr:uid="{0486C015-E59C-4C68-91D3-4ACAD00E12CD}"/>
-    <hyperlink ref="B48" r:id="rId84" display="mailto:Phuntone9@gmail.com" xr:uid="{97AD22F5-2C24-4F75-816F-70DD5E10F7E3}"/>
-    <hyperlink ref="B3" r:id="rId85" display="mailto:rasool@icgglobal.com" xr:uid="{8CC08D82-DC80-4069-A607-F03D467D475C}"/>
-    <hyperlink ref="B20" r:id="rId86" display="mailto:Steven.brouse@gmail.com" xr:uid="{0E704A9F-B2C5-4BBF-8D88-3BAC495E147F}"/>
-    <hyperlink ref="B13" r:id="rId87" display="mailto:j.b.internationalcellars@gmail.com" xr:uid="{839EF4EB-A6F8-43A3-B660-F7D49F2E61D4}"/>
-    <hyperlink ref="B92" r:id="rId88" display="mailto:Bryant.shirreffs@yahoo.com" xr:uid="{BA1A9DD0-A412-4686-BC81-5FFC622C25A9}"/>
-    <hyperlink ref="B87" r:id="rId89" display="mailto:jcpurl@aol.com" xr:uid="{E4621CD0-F8C1-458A-9567-BDCA1089D95C}"/>
-    <hyperlink ref="B28" r:id="rId90" display="mailto:jeremyclaflin6@gmail.com" xr:uid="{7538A4E0-FA80-4082-AB29-64F526F8CC24}"/>
-    <hyperlink ref="B55" r:id="rId91" display="mailto:landolfimark285@gmail.com" xr:uid="{20BF721A-932E-4360-ABD6-6884414072C6}"/>
-    <hyperlink ref="B70" r:id="rId92" display="mailto:moynihanjr@gmail.com" xr:uid="{09EAB6B8-1CC0-499B-A77D-568323DE9156}"/>
-    <hyperlink ref="B109" r:id="rId93" display="mailto:Razulwallace@gmail.com" xr:uid="{9C945E29-299D-45FA-BA11-7A092AE0F910}"/>
+    <hyperlink ref="B40" r:id="rId15" display="mailto:elizabeth.casarella@gmail.com" xr:uid="{C150E814-8C96-4E50-8A55-5EB3344749B1}"/>
+    <hyperlink ref="B196" r:id="rId16" display="mailto:paul@levelbreaker.com" xr:uid="{9746CC3F-863E-4E18-931A-FADD4ED10BF2}"/>
+    <hyperlink ref="B107" r:id="rId17" xr:uid="{316BCF75-05DF-4572-9F46-9F76127C0677}"/>
+    <hyperlink ref="B162" r:id="rId18" xr:uid="{57197F8F-1C51-4977-936A-74B15D239DF7}"/>
+    <hyperlink ref="B157" r:id="rId19" display="mailto:hef714@aol.com" xr:uid="{A4825BC7-F2DD-43E9-A39B-48544C54E403}"/>
+    <hyperlink ref="B89" r:id="rId20" xr:uid="{A871275A-577B-4F01-A590-B30FBADA40A1}"/>
+    <hyperlink ref="B227" r:id="rId21" xr:uid="{7E7AC9EC-4484-43DC-8B81-7AA0BCCFA407}"/>
+    <hyperlink ref="B134" r:id="rId22" display="mailto:Gjhusky52@yahoo.com" xr:uid="{1F5D9E16-5BA9-4F8F-B8CF-14485F325E5D}"/>
+    <hyperlink ref="B232" r:id="rId23" display="mailto:s.vibberts@yahoo.com" xr:uid="{CD95CA65-C8C5-44B3-8AFC-2E088AEC194C}"/>
+    <hyperlink ref="B179" r:id="rId24" display="mailto:oldparsonage3@gmail.com" xr:uid="{DC8DA8C9-CCEA-4FC3-AA05-1EF34B65B0C1}"/>
+    <hyperlink ref="B116" r:id="rId25" xr:uid="{C2395B48-B35E-4045-A136-C8B31BE4A5FC}"/>
+    <hyperlink ref="B11" r:id="rId26" xr:uid="{37F7977A-EC68-4733-8738-6C53C959B816}"/>
+    <hyperlink ref="B20" r:id="rId27" xr:uid="{A209B655-7CEF-4F8D-BFEE-DFB49C33870B}"/>
+    <hyperlink ref="B155" r:id="rId28" xr:uid="{46F1EE8C-941D-4D6B-A27A-3BDDA65A15CE}"/>
+    <hyperlink ref="B13" r:id="rId29" xr:uid="{647703FF-1796-4612-923D-2A3CF89F5A46}"/>
+    <hyperlink ref="B60" r:id="rId30" xr:uid="{D4F421DD-A322-4F00-A209-B464A28664A6}"/>
+    <hyperlink ref="B123" r:id="rId31" xr:uid="{5FF15619-CFAB-48CB-8BF0-78013919701C}"/>
+    <hyperlink ref="B146" r:id="rId32" display="mailto:Kmills8080@gmail.com" xr:uid="{6653A4F2-00C8-4ACF-A9B2-950ABB23037C}"/>
+    <hyperlink ref="B125" r:id="rId33" xr:uid="{0F8932AA-3F92-4F04-A82F-C839649C3558}"/>
+    <hyperlink ref="B181" r:id="rId34" xr:uid="{74573551-A238-45F0-95FA-078470676D33}"/>
+    <hyperlink ref="B152" r:id="rId35" xr:uid="{F093A50A-9255-43F2-873A-E61FB97B7B6E}"/>
+    <hyperlink ref="B68" r:id="rId36" display="mailto:lostdogs@charter.net" xr:uid="{95D046AE-D83E-4029-8E4D-F457CDD3F23E}"/>
+    <hyperlink ref="B57" r:id="rId37" xr:uid="{93D1D532-1D29-4735-B6C3-7B9B46F15302}"/>
+    <hyperlink ref="B117" r:id="rId38" display="mailto:langer0125@gmail.com" xr:uid="{EF3BA7C4-32BE-431A-9979-8B42711B0D73}"/>
+    <hyperlink ref="B223" r:id="rId39" display="mailto:Ntjr05@gmail.com" xr:uid="{38DDEC56-F2AD-4C66-8377-3BFC9B7BDDB9}"/>
+    <hyperlink ref="B201" r:id="rId40" display="mailto:gregsinay3@gmail.com" xr:uid="{004C878C-63EB-40FC-B549-87CFABDE66E1}"/>
+    <hyperlink ref="B101" r:id="rId41" display="mailto:Suj9283@yahoo.com" xr:uid="{E8FF833B-A9E0-4AED-A7DB-065ED67E2244}"/>
+    <hyperlink ref="B170" r:id="rId42" xr:uid="{FAF882CB-F959-4D5E-B4E0-3608ADC9DA13}"/>
+    <hyperlink ref="B208" r:id="rId43" display="mailto:sosikiii@msn.com" xr:uid="{218E6BB5-6D46-4A2B-BD2C-6CF05A021B3C}"/>
+    <hyperlink ref="B124" r:id="rId44" xr:uid="{33551D8E-478C-410F-9E21-46488F70F42D}"/>
+    <hyperlink ref="B211" r:id="rId45" display="mailto:brisparks@gmail.com" xr:uid="{E8A49946-13F1-4C59-AD3D-A3E5B9D77EFF}"/>
+    <hyperlink ref="B120" r:id="rId46" display="mailto:Dlew44@gmail.com" xr:uid="{25AC56D9-918C-4162-BE04-DAA69217239F}"/>
+    <hyperlink ref="B12" r:id="rId47" xr:uid="{02619D1B-E12D-411C-8267-1EA72D337FA4}"/>
+    <hyperlink ref="B26" r:id="rId48" xr:uid="{297F912D-F1B3-4511-B9FB-7F6A5151679A}"/>
+    <hyperlink ref="B34" r:id="rId49" xr:uid="{23A72ED8-42A8-4AD2-AED4-16447BAE4A08}"/>
+    <hyperlink ref="B36" r:id="rId50" xr:uid="{5484D007-8240-489C-A613-B2C0F0F2AC56}"/>
+    <hyperlink ref="B42" r:id="rId51" xr:uid="{D01BE816-0B5A-4446-924C-46E6BAD18108}"/>
+    <hyperlink ref="B79" r:id="rId52" xr:uid="{276C5002-FCF1-4B64-9438-E4287F3F2787}"/>
+    <hyperlink ref="B137" r:id="rId53" xr:uid="{05B37D53-659E-462F-9D42-00105B550079}"/>
+    <hyperlink ref="B141" r:id="rId54" xr:uid="{F7EC428E-8409-4830-9429-9C5E7ABB09A4}"/>
+    <hyperlink ref="B159" r:id="rId55" xr:uid="{EE1C2C4D-03AE-46ED-A073-46B29C8D3689}"/>
+    <hyperlink ref="B205" r:id="rId56" xr:uid="{4C733EB2-A8CB-4A19-80B4-31601DA15BF2}"/>
+    <hyperlink ref="B212" r:id="rId57" xr:uid="{77C5CEA7-AAB7-4C0E-8FED-A2F21F462250}"/>
+    <hyperlink ref="B225" r:id="rId58" xr:uid="{D3F25966-9FE3-42C3-94BB-54469D722B9E}"/>
+    <hyperlink ref="B98" r:id="rId59" display="mailto:bill.irwin58@gmail.com" xr:uid="{21398664-274B-466E-AEF3-003790919F40}"/>
+    <hyperlink ref="B91" r:id="rId60" display="mailto:Hogan6523@Yahoo.com" xr:uid="{8F033920-5D36-4035-9970-BF7A906D9337}"/>
+    <hyperlink ref="B177" r:id="rId61" xr:uid="{3915D652-1507-4F3C-AEB3-935E95D07A08}"/>
+    <hyperlink ref="B169" r:id="rId62" display="mailto:bernard.e.palmer@gmail.com" xr:uid="{4E7DEDEB-BA72-4331-A716-378C6A511DCC}"/>
+    <hyperlink ref="B78" r:id="rId63" display="mailto:fogs14@yahoo.com" xr:uid="{E734B4DB-161E-4386-9BE4-4D2A768C19C0}"/>
+    <hyperlink ref="B6" r:id="rId64" xr:uid="{94ECE3FB-34A8-40D2-A511-C6F49E1F79C8}"/>
+    <hyperlink ref="B199" r:id="rId65" xr:uid="{8042AEE0-2132-486D-AFC6-008B86CDABF9}"/>
+    <hyperlink ref="B56" r:id="rId66" display="mailto:rmdecambre@gmail.com" xr:uid="{61906EF9-7178-4E37-9EF5-F697B7AF8714}"/>
+    <hyperlink ref="B191" r:id="rId67" xr:uid="{C73311BF-B167-4642-BFA3-507299A38EFE}"/>
+    <hyperlink ref="B44" r:id="rId68" xr:uid="{A7D0DDDF-0E1D-4EAA-BC8A-6B20E1097E98}"/>
+    <hyperlink ref="B75" r:id="rId69" display="mailto:tfink9@juno.com" xr:uid="{34A73A04-8440-48B2-9348-0E4A6602D420}"/>
+    <hyperlink ref="B74" r:id="rId70" xr:uid="{0BB6B871-9927-4DD2-B508-224D22FD6229}"/>
+    <hyperlink ref="B218" r:id="rId71" xr:uid="{6DBAAB43-CE57-45EC-BCA9-CB408BBC84B6}"/>
+    <hyperlink ref="B236" r:id="rId72" xr:uid="{DB8385C7-8934-4CD0-B87E-4D74991BD43E}"/>
+    <hyperlink ref="B242" r:id="rId73" xr:uid="{CEB5326F-2589-4355-9CCD-6A3D6FC84E4A}"/>
+    <hyperlink ref="B219" r:id="rId74" xr:uid="{4A20E15A-8219-4697-83CE-53E329D1A594}"/>
+    <hyperlink ref="B67" r:id="rId75" xr:uid="{CB15C81B-047D-40F8-BDE8-B1539A6E2F0B}"/>
+    <hyperlink ref="B80" r:id="rId76" xr:uid="{B485936F-7DCD-4862-9E33-EEA8B063A75F}"/>
+    <hyperlink ref="B15" r:id="rId77" xr:uid="{74BFC159-A59B-4245-BC6C-B882819624B3}"/>
+    <hyperlink ref="B69" r:id="rId78" xr:uid="{F3187CCB-7830-43D4-9E21-FF900FE7F868}"/>
+    <hyperlink ref="B209" r:id="rId79" display="mailto:Sowell47@gmail.com" xr:uid="{03411C75-D37D-4435-805E-31377118488D}"/>
+    <hyperlink ref="B17" r:id="rId80" xr:uid="{6DB4A5CC-5D1F-4EF9-932C-678F4FC22DA9}"/>
+    <hyperlink ref="B27" r:id="rId81" xr:uid="{CF88E969-EAAC-46AC-8516-43C895BD47AD}"/>
+    <hyperlink ref="B96" r:id="rId82" xr:uid="{FC781576-FE15-492B-950C-DC624C8FF2B0}"/>
+    <hyperlink ref="B158" r:id="rId83" xr:uid="{0486C015-E59C-4C68-91D3-4ACAD00E12CD}"/>
+    <hyperlink ref="B94" r:id="rId84" display="mailto:Phuntone9@gmail.com" xr:uid="{97AD22F5-2C24-4F75-816F-70DD5E10F7E3}"/>
+    <hyperlink ref="B4" r:id="rId85" display="mailto:rasool@icgglobal.com" xr:uid="{8CC08D82-DC80-4069-A607-F03D467D475C}"/>
+    <hyperlink ref="B31" r:id="rId86" display="mailto:Steven.brouse@gmail.com" xr:uid="{0E704A9F-B2C5-4BBF-8D88-3BAC495E147F}"/>
+    <hyperlink ref="B16" r:id="rId87" display="mailto:j.b.internationalcellars@gmail.com" xr:uid="{839EF4EB-A6F8-43A3-B660-F7D49F2E61D4}"/>
+    <hyperlink ref="B198" r:id="rId88" display="mailto:Bryant.shirreffs@yahoo.com" xr:uid="{BA1A9DD0-A412-4686-BC81-5FFC622C25A9}"/>
+    <hyperlink ref="B183" r:id="rId89" display="mailto:jcpurl@aol.com" xr:uid="{E4621CD0-F8C1-458A-9567-BDCA1089D95C}"/>
+    <hyperlink ref="B47" r:id="rId90" display="mailto:jeremyclaflin6@gmail.com" xr:uid="{7538A4E0-FA80-4082-AB29-64F526F8CC24}"/>
+    <hyperlink ref="B115" r:id="rId91" display="mailto:landolfimark285@gmail.com" xr:uid="{20BF721A-932E-4360-ABD6-6884414072C6}"/>
+    <hyperlink ref="B150" r:id="rId92" display="mailto:moynihanjr@gmail.com" xr:uid="{09EAB6B8-1CC0-499B-A77D-568323DE9156}"/>
+    <hyperlink ref="B233" r:id="rId93" display="mailto:Razulwallace@gmail.com" xr:uid="{9C945E29-299D-45FA-BA11-7A092AE0F910}"/>
+    <hyperlink ref="B21" r:id="rId94" xr:uid="{6C755390-FCE5-44E8-BA6D-9E526EFB3191}"/>
+    <hyperlink ref="B168" r:id="rId95" xr:uid="{9BE879F8-944D-49CA-BDF0-CCE8169FD5BB}"/>
+    <hyperlink ref="B171" r:id="rId96" xr:uid="{540A47A4-EBFF-400C-8A2A-34A2B8B77B2D}"/>
+    <hyperlink ref="B142" r:id="rId97" xr:uid="{E13A9C92-7D31-49D1-BE2B-F27CA13491B5}"/>
+    <hyperlink ref="B95" r:id="rId98" xr:uid="{81BDB679-61B9-4944-986C-D6792DE6A5DB}"/>
+    <hyperlink ref="B41" r:id="rId99" xr:uid="{9B66D431-5F64-437B-9ED8-E1AA1BFEF87C}"/>
+    <hyperlink ref="B207" r:id="rId100" xr:uid="{2A6177C8-A0ED-4F54-8722-887534A734D3}"/>
+    <hyperlink ref="B55" r:id="rId101" xr:uid="{D91E0C62-76BF-46FA-9851-1CA99AA007AE}"/>
+    <hyperlink ref="B210" r:id="rId102" xr:uid="{7D0062DB-B731-433D-A351-DC4851587C48}"/>
+    <hyperlink ref="B54" r:id="rId103" xr:uid="{4CA45CB5-781C-4C0B-ADA3-5C566420DAE0}"/>
+    <hyperlink ref="B220" r:id="rId104" display="mailto:DaniaSweeney@aol.com" xr:uid="{14EDA941-F642-4041-9501-FBEC3A51835C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId94"/>
+  <pageSetup orientation="portrait" r:id="rId105"/>
 </worksheet>
 </file>
--- a/UConnBleedBlue/wwwroot/Data/Players.xlsx
+++ b/UConnBleedBlue/wwwroot/Data/Players.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CSharpRepos\UConnBleedBlue\UConnBleedBlue\wwwroot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93EFADC-E4C9-40BC-9819-06B1F1430433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7881F2-0E96-45EE-946C-725E93A6CCA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="501">
   <si>
     <t>Demers, Kenny</t>
   </si>
@@ -1533,6 +1533,12 @@
   </si>
   <si>
     <t>bhogan847@hotmail.com</t>
+  </si>
+  <si>
+    <t>Dougherty,Jim</t>
+  </si>
+  <si>
+    <t>CoachD1326@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -1917,14 +1923,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F97E2D-D2EE-4E19-AA28-ED70E4256082}">
-  <dimension ref="A1:G242"/>
+  <dimension ref="A1:G243"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" customWidth="1"/>
     <col min="2" max="2" width="33.7109375" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="1"/>
     <col min="4" max="4" width="14.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.85546875" customWidth="1"/>
     <col min="7" max="7" width="11.85546875" style="1" customWidth="1"/>
   </cols>
@@ -1942,7 +1948,7 @@
       <c r="D1" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F1" s="4" t="s">
@@ -1965,8 +1971,8 @@
       <c r="D2" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E2" t="b">
-        <v>1</v>
+      <c r="E2" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1976,6 +1982,9 @@
       <c r="B3" s="3" t="s">
         <v>445</v>
       </c>
+      <c r="E3" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -1984,8 +1993,8 @@
       <c r="B4" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E4" t="b">
-        <v>1</v>
+      <c r="E4" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2001,8 +2010,8 @@
       <c r="D5" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E5" t="b">
-        <v>1</v>
+      <c r="E5" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>217</v>
@@ -2021,8 +2030,8 @@
       <c r="D6" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E6" t="b">
-        <v>1</v>
+      <c r="E6" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2032,8 +2041,8 @@
       <c r="B7" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E7" t="b">
-        <v>1</v>
+      <c r="E7" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G7" s="1">
         <v>4</v>
@@ -2046,6 +2055,9 @@
       <c r="B8" s="3" t="s">
         <v>453</v>
       </c>
+      <c r="E8" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -2060,8 +2072,8 @@
       <c r="D9" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E9" t="b">
-        <v>1</v>
+      <c r="E9" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G9" s="1">
         <v>2</v>
@@ -2074,6 +2086,9 @@
       <c r="B10" s="3" t="s">
         <v>494</v>
       </c>
+      <c r="E10" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -2088,8 +2103,8 @@
       <c r="D11" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E11" t="b">
-        <v>1</v>
+      <c r="E11" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G11" s="1">
         <v>2</v>
@@ -2108,8 +2123,8 @@
       <c r="D12" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E12" t="b">
-        <v>1</v>
+      <c r="E12" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G12" s="1">
         <v>2</v>
@@ -2128,8 +2143,8 @@
       <c r="D13" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E13" t="b">
-        <v>1</v>
+      <c r="E13" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>217</v>
@@ -2148,8 +2163,8 @@
       <c r="D14" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E14" t="b">
-        <v>1</v>
+      <c r="E14" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>217</v>
@@ -2168,8 +2183,8 @@
       <c r="D15" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E15" t="b">
-        <v>1</v>
+      <c r="E15" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
@@ -2188,8 +2203,8 @@
       <c r="D16" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E16" t="b">
-        <v>1</v>
+      <c r="E16" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2205,8 +2220,8 @@
       <c r="D17" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E17" t="b">
-        <v>1</v>
+      <c r="E17" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>217</v>
@@ -2219,8 +2234,8 @@
       <c r="B18" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="E18" t="b">
-        <v>1</v>
+      <c r="E18" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2230,6 +2245,9 @@
       <c r="B19" s="3" t="s">
         <v>349</v>
       </c>
+      <c r="E19" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -2244,8 +2262,8 @@
       <c r="D20" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E20" t="b">
-        <v>1</v>
+      <c r="E20" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2255,8 +2273,8 @@
       <c r="B21" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="E21" t="b">
-        <v>1</v>
+      <c r="E21" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2272,8 +2290,8 @@
       <c r="D22" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E22" t="b">
-        <v>1</v>
+      <c r="E22" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G22" s="1">
         <v>2</v>
@@ -2286,6 +2304,9 @@
       <c r="B23" t="s">
         <v>378</v>
       </c>
+      <c r="E23" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
@@ -2294,6 +2315,9 @@
       <c r="B24" t="s">
         <v>329</v>
       </c>
+      <c r="E24" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
@@ -2302,8 +2326,8 @@
       <c r="B25" t="s">
         <v>297</v>
       </c>
-      <c r="E25" t="b">
-        <v>1</v>
+      <c r="E25" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2319,8 +2343,8 @@
       <c r="D26" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E26" t="b">
-        <v>1</v>
+      <c r="E26" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G26" s="1">
         <v>2</v>
@@ -2339,8 +2363,8 @@
       <c r="D27" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E27" t="b">
-        <v>1</v>
+      <c r="E27" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2356,8 +2380,8 @@
       <c r="D28" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E28" t="b">
-        <v>1</v>
+      <c r="E28" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -2373,8 +2397,8 @@
       <c r="B29" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="E29" t="b">
-        <v>1</v>
+      <c r="E29" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2384,6 +2408,9 @@
       <c r="B30" s="3" t="s">
         <v>364</v>
       </c>
+      <c r="E30" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
@@ -2398,8 +2425,8 @@
       <c r="D31" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E31" t="b">
-        <v>1</v>
+      <c r="E31" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2409,8 +2436,8 @@
       <c r="B32" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="E32" t="b">
-        <v>1</v>
+      <c r="E32" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2420,6 +2447,9 @@
       <c r="B33" s="3" t="s">
         <v>418</v>
       </c>
+      <c r="E33" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
@@ -2431,8 +2461,8 @@
       <c r="C34" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E34" t="b">
-        <v>1</v>
+      <c r="E34" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G34" s="1">
         <v>2</v>
@@ -2445,6 +2475,9 @@
       <c r="B35" s="3" t="s">
         <v>331</v>
       </c>
+      <c r="E35" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
@@ -2459,8 +2492,8 @@
       <c r="D36" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E36" t="b">
-        <v>1</v>
+      <c r="E36" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G36" s="1">
         <v>4</v>
@@ -2473,6 +2506,9 @@
       <c r="B37" s="3" t="s">
         <v>484</v>
       </c>
+      <c r="E37" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
@@ -2487,8 +2523,8 @@
       <c r="D38" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E38" t="b">
-        <v>1</v>
+      <c r="E38" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G38" s="1">
         <v>2</v>
@@ -2501,8 +2537,8 @@
       <c r="B39" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E39" t="b">
-        <v>1</v>
+      <c r="E39" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2518,8 +2554,8 @@
       <c r="D40" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E40" t="b">
-        <v>1</v>
+      <c r="E40" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>217</v>
@@ -2532,8 +2568,8 @@
       <c r="B41" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="E41" t="b">
-        <v>1</v>
+      <c r="E41" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2549,8 +2585,8 @@
       <c r="D42" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E42" t="b">
-        <v>1</v>
+      <c r="E42" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G42" s="1">
         <v>2</v>
@@ -2563,6 +2599,9 @@
       <c r="B43" s="3" t="s">
         <v>416</v>
       </c>
+      <c r="E43" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -2571,8 +2610,8 @@
       <c r="B44" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E44" t="b">
-        <v>1</v>
+      <c r="E44" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G44" s="1">
         <v>2</v>
@@ -2591,8 +2630,8 @@
       <c r="D45" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E45" t="b">
-        <v>1</v>
+      <c r="E45" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -2602,8 +2641,8 @@
       <c r="B46" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="E46" t="b">
-        <v>1</v>
+      <c r="E46" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -2619,8 +2658,8 @@
       <c r="D47" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E47" t="b">
-        <v>1</v>
+      <c r="E47" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -2630,6 +2669,9 @@
       <c r="B48" s="3" t="s">
         <v>472</v>
       </c>
+      <c r="E48" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
@@ -2638,6 +2680,9 @@
       <c r="B49" s="3" t="s">
         <v>490</v>
       </c>
+      <c r="E49" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
@@ -2646,6 +2691,9 @@
       <c r="B50" s="3" t="s">
         <v>368</v>
       </c>
+      <c r="E50" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
@@ -2660,8 +2708,8 @@
       <c r="D51" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E51" t="b">
-        <v>1</v>
+      <c r="E51" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G51" s="1">
         <v>2</v>
@@ -2674,6 +2722,9 @@
       <c r="B52" s="2" t="s">
         <v>380</v>
       </c>
+      <c r="E52" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
@@ -2682,6 +2733,9 @@
       <c r="B53" s="2" t="s">
         <v>339</v>
       </c>
+      <c r="E53" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
@@ -2690,8 +2744,8 @@
       <c r="B54" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="E54" t="b">
-        <v>1</v>
+      <c r="E54" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -2701,8 +2755,8 @@
       <c r="B55" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="E55" t="b">
-        <v>1</v>
+      <c r="E55" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -2718,8 +2772,8 @@
       <c r="D56" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E56" t="b">
-        <v>1</v>
+      <c r="E56" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G56" s="1">
         <v>1</v>
@@ -2738,8 +2792,8 @@
       <c r="D57" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E57" t="b">
-        <v>1</v>
+      <c r="E57" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G57" s="1">
         <v>2</v>
@@ -2752,6 +2806,9 @@
       <c r="B58" s="3" t="s">
         <v>370</v>
       </c>
+      <c r="E58" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
@@ -2766,7 +2823,7 @@
       <c r="D59" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E59" t="b">
+      <c r="E59" s="1" t="b">
         <v>1</v>
       </c>
       <c r="G59" s="1">
@@ -2786,7 +2843,7 @@
       <c r="D60" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E60" t="b">
+      <c r="E60" s="1" t="b">
         <v>1</v>
       </c>
       <c r="G60" s="1">
@@ -2800,6 +2857,9 @@
       <c r="B61" s="3" t="s">
         <v>335</v>
       </c>
+      <c r="E61" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
@@ -2808,8 +2868,8 @@
       <c r="B62" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="E62" t="b">
-        <v>1</v>
+      <c r="E62" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -2822,6 +2882,9 @@
       <c r="C63" s="1">
         <v>1967</v>
       </c>
+      <c r="E63" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
@@ -2830,6 +2893,9 @@
       <c r="B64" s="3" t="s">
         <v>394</v>
       </c>
+      <c r="E64" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
@@ -2838,210 +2904,219 @@
       <c r="B65" s="3" t="s">
         <v>428</v>
       </c>
+      <c r="E65" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>436</v>
+        <v>499</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>437</v>
+        <v>500</v>
+      </c>
+      <c r="C66" s="1">
+        <v>1982</v>
+      </c>
+      <c r="E66" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>207</v>
+        <v>436</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C67" s="1">
-        <v>1977</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E67" t="b">
-        <v>1</v>
-      </c>
-      <c r="G67" s="1">
-        <v>2</v>
+        <v>437</v>
+      </c>
+      <c r="E67" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>104</v>
+        <v>207</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>105</v>
+        <v>208</v>
       </c>
       <c r="C68" s="1">
-        <v>1993</v>
+        <v>1977</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E68" t="b">
-        <v>1</v>
+        <v>129</v>
+      </c>
+      <c r="E68" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G68" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>213</v>
+        <v>104</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="E69" t="b">
+        <v>105</v>
+      </c>
+      <c r="C69" s="1">
+        <v>1993</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E69" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1">
         <v>1</v>
-      </c>
-      <c r="G69" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E70" t="b">
-        <v>1</v>
+        <v>214</v>
+      </c>
+      <c r="E70" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C71" s="1">
-        <v>1997</v>
+        <v>39</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E71" t="b">
-        <v>1</v>
-      </c>
-      <c r="G71" s="1">
-        <v>1</v>
+        <v>153</v>
+      </c>
+      <c r="E71" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>403</v>
+        <v>187</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>404</v>
+        <v>188</v>
+      </c>
+      <c r="C72" s="1">
+        <v>1997</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E72" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>237</v>
+        <v>403</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="E73" t="b">
-        <v>1</v>
+        <v>404</v>
+      </c>
+      <c r="E73" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E74" t="b">
-        <v>1</v>
-      </c>
-      <c r="G74" s="1">
-        <v>2</v>
+        <v>238</v>
+      </c>
+      <c r="E74" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C75" s="1">
-        <v>1982</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E75" t="b">
-        <v>1</v>
+        <v>190</v>
+      </c>
+      <c r="E75" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G75" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>465</v>
+        <v>199</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>466</v>
+        <v>200</v>
+      </c>
+      <c r="C76" s="1">
+        <v>1982</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E76" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1">
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>405</v>
+        <v>465</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>406</v>
+        <v>466</v>
+      </c>
+      <c r="E77" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>171</v>
+        <v>405</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C78" s="1">
-        <v>2005</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E78" t="b">
-        <v>1</v>
-      </c>
-      <c r="G78" s="1">
-        <v>2</v>
+        <v>406</v>
+      </c>
+      <c r="E78" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>153</v>
+        <v>172</v>
+      </c>
+      <c r="C79" s="1">
+        <v>2005</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E79" t="b">
-        <v>1</v>
+        <v>134</v>
+      </c>
+      <c r="E79" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G79" s="1">
         <v>2</v>
@@ -3049,292 +3124,316 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>209</v>
+        <v>149</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C80" s="1">
-        <v>1970</v>
+        <v>150</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E80" t="b">
-        <v>1</v>
+        <v>153</v>
+      </c>
+      <c r="E80" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G80" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>438</v>
+        <v>209</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>439</v>
+        <v>210</v>
+      </c>
+      <c r="C81" s="1">
+        <v>1970</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E81" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G81" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>316</v>
+        <v>438</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="E82" t="b">
-        <v>1</v>
+        <v>439</v>
+      </c>
+      <c r="E82" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>442</v>
+        <v>316</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>443</v>
+        <v>317</v>
+      </c>
+      <c r="E83" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>495</v>
+        <v>442</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>496</v>
+        <v>443</v>
+      </c>
+      <c r="E84" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>294</v>
+        <v>495</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E85" t="b">
-        <v>1</v>
+        <v>496</v>
+      </c>
+      <c r="E85" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>336</v>
+        <v>294</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>337</v>
+        <v>295</v>
+      </c>
+      <c r="E86" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>429</v>
+        <v>336</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>430</v>
+        <v>337</v>
+      </c>
+      <c r="E87" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>318</v>
+        <v>429</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="E88" t="b">
-        <v>1</v>
+        <v>430</v>
+      </c>
+      <c r="E88" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>64</v>
+        <v>318</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C89" s="1">
-        <v>1993</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E89" t="b">
-        <v>1</v>
-      </c>
-      <c r="G89" s="1">
-        <v>2</v>
+        <v>319</v>
+      </c>
+      <c r="E89" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>281</v>
+        <v>64</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="E90" t="b">
-        <v>1</v>
+        <v>65</v>
+      </c>
+      <c r="C90" s="1">
+        <v>1993</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E90" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G90" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C91" s="1">
-        <v>1970</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E91" t="b">
-        <v>1</v>
-      </c>
-      <c r="F91" t="b">
-        <v>1</v>
-      </c>
-      <c r="G91" s="1">
-        <v>1</v>
+        <v>282</v>
+      </c>
+      <c r="E91" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>497</v>
+        <v>165</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>498</v>
+        <v>166</v>
+      </c>
+      <c r="C92" s="1">
+        <v>1970</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E92" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F92" t="b">
+        <v>1</v>
+      </c>
+      <c r="G92" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>475</v>
+        <v>497</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>476</v>
+        <v>498</v>
+      </c>
+      <c r="E93" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>221</v>
+        <v>475</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C94" s="1">
-        <v>1998</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E94" t="b">
-        <v>1</v>
+        <v>476</v>
+      </c>
+      <c r="E94" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="E95" t="b">
-        <v>1</v>
+        <v>222</v>
+      </c>
+      <c r="C95" s="1">
+        <v>1998</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E95" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>18</v>
+        <v>251</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C96" s="1">
-        <v>1972</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E96" t="b">
-        <v>1</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>217</v>
+        <v>252</v>
+      </c>
+      <c r="E96" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>491</v>
+        <v>18</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>492</v>
+        <v>88</v>
+      </c>
+      <c r="C97" s="1">
+        <v>1972</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E97" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>163</v>
+        <v>491</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C98" s="1">
-        <v>2004</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E98" t="b">
-        <v>1</v>
-      </c>
-      <c r="F98" t="b">
-        <v>1</v>
-      </c>
-      <c r="G98" s="1">
-        <v>1</v>
+        <v>492</v>
+      </c>
+      <c r="E98" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>320</v>
+        <v>163</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="E99" t="b">
+        <v>164</v>
+      </c>
+      <c r="C99" s="1">
+        <v>2004</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E99" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F99" t="b">
+        <v>1</v>
+      </c>
+      <c r="G99" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>191</v>
+        <v>320</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C100" s="1">
-        <v>1996</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E100" t="b">
-        <v>1</v>
-      </c>
-      <c r="G100" s="1">
-        <v>2</v>
+        <v>321</v>
+      </c>
+      <c r="E100" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>114</v>
+        <v>191</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>115</v>
+        <v>192</v>
       </c>
       <c r="C101" s="1">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E101" t="b">
-        <v>1</v>
+      <c r="E101" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G101" s="1">
         <v>2</v>
@@ -3342,725 +3441,800 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>456</v>
+        <v>114</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>84</v>
+        <v>115</v>
+      </c>
+      <c r="C102" s="1">
+        <v>1995</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E102" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G102" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>365</v>
+        <v>456</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>366</v>
+        <v>84</v>
+      </c>
+      <c r="E103" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>463</v>
+        <v>365</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>464</v>
+        <v>366</v>
+      </c>
+      <c r="E104" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>486</v>
+        <v>464</v>
+      </c>
+      <c r="E105" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>371</v>
+        <v>485</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>372</v>
+        <v>486</v>
+      </c>
+      <c r="E106" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>59</v>
+        <v>371</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C107" s="1">
-        <v>1979</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E107" t="b">
-        <v>1</v>
+        <v>372</v>
+      </c>
+      <c r="E107" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>306</v>
+        <v>59</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="E108" t="b">
-        <v>1</v>
+        <v>60</v>
+      </c>
+      <c r="C108" s="1">
+        <v>1979</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E108" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>391</v>
+        <v>306</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>392</v>
+        <v>307</v>
+      </c>
+      <c r="E109" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>342</v>
+        <v>391</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>343</v>
+        <v>392</v>
+      </c>
+      <c r="E110" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="E111" t="b">
-        <v>1</v>
+        <v>343</v>
+      </c>
+      <c r="E111" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>356</v>
+        <v>308</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="E112" t="b">
-        <v>1</v>
+        <v>309</v>
+      </c>
+      <c r="E112" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E113" t="b">
-        <v>1</v>
+        <v>289</v>
+      </c>
+      <c r="E113" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>19</v>
-      </c>
-      <c r="B114" t="s">
-        <v>89</v>
-      </c>
-      <c r="C114" s="1">
-        <v>1979</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E114" t="b">
-        <v>1</v>
-      </c>
-      <c r="G114" s="1">
-        <v>2</v>
+        <v>310</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E114" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>235</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>236</v>
+        <v>19</v>
+      </c>
+      <c r="B115" t="s">
+        <v>89</v>
       </c>
       <c r="C115" s="1">
-        <v>1989</v>
+        <v>1979</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E115" t="b">
-        <v>1</v>
+        <v>129</v>
+      </c>
+      <c r="E115" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G115" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>75</v>
+        <v>235</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>76</v>
+        <v>236</v>
       </c>
       <c r="C116" s="1">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E116" t="b">
-        <v>1</v>
-      </c>
-      <c r="G116" s="1">
-        <v>1</v>
+      <c r="E116" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="C117" s="1">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E117" t="b">
+        <v>133</v>
+      </c>
+      <c r="E117" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G117" s="1">
         <v>1</v>
-      </c>
-      <c r="G117" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>435</v>
+        <v>108</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
+      </c>
+      <c r="C118" s="1">
+        <v>1982</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E118" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G118" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>271</v>
+        <v>435</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="E119" t="b">
-        <v>1</v>
+        <v>89</v>
+      </c>
+      <c r="E119" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>126</v>
+        <v>271</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C120" s="1">
-        <v>1994</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E120" t="b">
-        <v>1</v>
-      </c>
-      <c r="G120" s="1">
-        <v>2</v>
+        <v>272</v>
+      </c>
+      <c r="E120" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>395</v>
+        <v>126</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>396</v>
+        <v>127</v>
+      </c>
+      <c r="C121" s="1">
+        <v>1994</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E121" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G121" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>352</v>
+        <v>395</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>353</v>
+        <v>396</v>
+      </c>
+      <c r="E122" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>24</v>
+        <v>352</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C123" s="1">
-        <v>1982</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E123" t="b">
-        <v>1</v>
-      </c>
-      <c r="G123" s="1">
-        <v>2</v>
+        <v>353</v>
+      </c>
+      <c r="E123" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="C124" s="1">
-        <v>2008</v>
+        <v>1982</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E124" t="b">
-        <v>1</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>217</v>
+        <v>129</v>
+      </c>
+      <c r="E124" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G124" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>153</v>
+        <v>123</v>
+      </c>
+      <c r="C125" s="1">
+        <v>2008</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E125" t="b">
-        <v>1</v>
+        <v>134</v>
+      </c>
+      <c r="E125" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>469</v>
+        <v>68</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>470</v>
+        <v>69</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E126" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>263</v>
+        <v>469</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="E127" t="b">
-        <v>1</v>
+        <v>470</v>
+      </c>
+      <c r="E127" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>407</v>
+        <v>263</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>408</v>
+        <v>264</v>
+      </c>
+      <c r="E128" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>354</v>
+        <v>407</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>355</v>
+        <v>408</v>
+      </c>
+      <c r="E129" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>454</v>
+        <v>354</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>455</v>
+        <v>355</v>
+      </c>
+      <c r="E130" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>2</v>
-      </c>
-      <c r="B131" t="s">
-        <v>91</v>
-      </c>
-      <c r="C131" s="1">
-        <v>1987</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E131" t="b">
-        <v>1</v>
-      </c>
-      <c r="G131" s="1">
-        <v>2</v>
+        <v>454</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="E131" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>431</v>
+        <v>2</v>
       </c>
       <c r="B132" t="s">
-        <v>432</v>
+        <v>91</v>
+      </c>
+      <c r="C132" s="1">
+        <v>1987</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E132" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G132" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="B133" t="s">
-        <v>288</v>
-      </c>
-      <c r="E133" t="b">
-        <v>1</v>
+        <v>432</v>
+      </c>
+      <c r="E133" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>70</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C134" s="1">
-        <v>1981</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E134" t="b">
-        <v>1</v>
-      </c>
-      <c r="G134" s="1">
-        <v>2</v>
+        <v>287</v>
+      </c>
+      <c r="B134" t="s">
+        <v>288</v>
+      </c>
+      <c r="E134" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>332</v>
+        <v>70</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>333</v>
+        <v>71</v>
+      </c>
+      <c r="C135" s="1">
+        <v>1981</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E135" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G135" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
+      </c>
+      <c r="E136" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>151</v>
+        <v>340</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C137" s="1">
-        <v>1973</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E137" t="b">
-        <v>1</v>
-      </c>
-      <c r="G137" s="1">
-        <v>2</v>
+        <v>341</v>
+      </c>
+      <c r="E137" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>448</v>
+        <v>151</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>449</v>
+        <v>152</v>
+      </c>
+      <c r="C138" s="1">
+        <v>1973</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E138" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G138" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>441</v>
+        <v>449</v>
+      </c>
+      <c r="E139" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>409</v>
+        <v>440</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>410</v>
+        <v>441</v>
+      </c>
+      <c r="E140" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>154</v>
+        <v>409</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C141" s="1">
-        <v>1978</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E141" t="b">
-        <v>1</v>
-      </c>
-      <c r="G141" s="1">
-        <v>2</v>
+        <v>410</v>
+      </c>
+      <c r="E141" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>249</v>
+        <v>154</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E142" t="b">
-        <v>1</v>
+        <v>155</v>
+      </c>
+      <c r="C142" s="1">
+        <v>1978</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E142" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G142" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>326</v>
+        <v>249</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="E143" t="b">
-        <v>1</v>
+        <v>250</v>
+      </c>
+      <c r="E143" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>120</v>
+        <v>326</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C144" s="1">
-        <v>1989</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E144" t="b">
-        <v>1</v>
-      </c>
-      <c r="G144" s="1">
-        <v>1</v>
+        <v>327</v>
+      </c>
+      <c r="E144" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>273</v>
+        <v>120</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="E145" t="b">
+        <v>121</v>
+      </c>
+      <c r="C145" s="1">
+        <v>1989</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E145" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G145" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>94</v>
+        <v>273</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C146" s="1">
-        <v>1981</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E146" t="b">
-        <v>1</v>
-      </c>
-      <c r="G146" s="1">
-        <v>2</v>
+        <v>274</v>
+      </c>
+      <c r="E146" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>22</v>
-      </c>
-      <c r="B147" t="s">
-        <v>92</v>
+        <v>94</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="C147" s="1">
-        <v>1986</v>
+        <v>1981</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E147" t="b">
-        <v>1</v>
+        <v>129</v>
+      </c>
+      <c r="E147" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G147" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>425</v>
+        <v>22</v>
       </c>
       <c r="B148" t="s">
-        <v>426</v>
+        <v>92</v>
+      </c>
+      <c r="C148" s="1">
+        <v>1986</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E148" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G148" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>43</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C149" s="1">
-        <v>1966</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E149" t="b">
-        <v>1</v>
-      </c>
-      <c r="G149" s="1">
-        <v>2</v>
+        <v>425</v>
+      </c>
+      <c r="B149" t="s">
+        <v>426</v>
+      </c>
+      <c r="E149" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>239</v>
+        <v>43</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>240</v>
+        <v>44</v>
       </c>
       <c r="C150" s="1">
-        <v>1992</v>
+        <v>1966</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E150" t="b">
-        <v>1</v>
+        <v>132</v>
+      </c>
+      <c r="E150" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G150" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>350</v>
+        <v>239</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>351</v>
+        <v>240</v>
+      </c>
+      <c r="C151" s="1">
+        <v>1992</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E151" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>102</v>
+        <v>350</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C152" s="1">
-        <v>1992</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E152" t="b">
-        <v>1</v>
-      </c>
-      <c r="G152" s="1">
-        <v>2</v>
+        <v>351</v>
+      </c>
+      <c r="E152" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>389</v>
+        <v>102</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>390</v>
+        <v>103</v>
+      </c>
+      <c r="C153" s="1">
+        <v>1992</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E153" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G153" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>411</v>
+        <v>389</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>412</v>
+        <v>390</v>
+      </c>
+      <c r="E154" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>81</v>
+        <v>411</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C155" s="1">
-        <v>1984</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E155" t="b">
-        <v>1</v>
+        <v>412</v>
+      </c>
+      <c r="E155" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>479</v>
+        <v>81</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>480</v>
+        <v>82</v>
+      </c>
+      <c r="C156" s="1">
+        <v>1984</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E156" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>62</v>
+        <v>479</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C157" s="1">
-        <v>1979</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E157" t="b">
-        <v>1</v>
-      </c>
-      <c r="G157" s="1">
-        <v>2</v>
+        <v>480</v>
+      </c>
+      <c r="E157" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="C158" s="1">
         <v>1979</v>
@@ -4068,39 +4242,39 @@
       <c r="D158" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E158" t="b">
-        <v>1</v>
+      <c r="E158" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G158" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E159" t="b">
-        <v>1</v>
-      </c>
-      <c r="G159" s="1">
-        <v>2</v>
+        <v>93</v>
+      </c>
+      <c r="C159" s="1">
+        <v>1979</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E159" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>1</v>
-      </c>
-      <c r="B160" t="s">
-        <v>96</v>
-      </c>
-      <c r="C160" s="1">
-        <v>1970</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E160" t="b">
-        <v>1</v>
+        <v>156</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E160" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G160" s="1">
         <v>2</v>
@@ -4108,19 +4282,19 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B161" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C161" s="1">
-        <v>2015</v>
+        <v>1970</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E161" t="b">
-        <v>1</v>
+        <v>132</v>
+      </c>
+      <c r="E161" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G161" s="1">
         <v>2</v>
@@ -4128,179 +4302,203 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>216</v>
-      </c>
-      <c r="B162" s="3" t="s">
-        <v>61</v>
+        <v>3</v>
+      </c>
+      <c r="B162" t="s">
+        <v>97</v>
       </c>
       <c r="C162" s="1">
-        <v>1978</v>
+        <v>2015</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E162" t="b">
-        <v>1</v>
+        <v>137</v>
+      </c>
+      <c r="E162" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G162" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>413</v>
+        <v>216</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>414</v>
+        <v>61</v>
+      </c>
+      <c r="C163" s="1">
+        <v>1978</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E163" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>357</v>
+        <v>413</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>358</v>
+        <v>414</v>
+      </c>
+      <c r="E164" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>419</v>
+        <v>357</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>420</v>
+        <v>358</v>
+      </c>
+      <c r="E165" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>447</v>
+        <v>420</v>
+      </c>
+      <c r="E166" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>344</v>
+        <v>446</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>345</v>
+        <v>447</v>
+      </c>
+      <c r="E167" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>245</v>
+        <v>344</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E168" t="b">
-        <v>1</v>
+        <v>345</v>
+      </c>
+      <c r="E168" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>169</v>
+        <v>245</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C169" s="1">
-        <v>1976</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E169" t="b">
-        <v>1</v>
-      </c>
-      <c r="G169" s="1">
-        <v>2</v>
+        <v>246</v>
+      </c>
+      <c r="E169" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>116</v>
+        <v>169</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>117</v>
+        <v>170</v>
       </c>
       <c r="C170" s="1">
-        <v>1980</v>
+        <v>1976</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E170" t="b">
-        <v>1</v>
+        <v>130</v>
+      </c>
+      <c r="E170" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G170" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>247</v>
+        <v>116</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E171" t="b">
-        <v>1</v>
+        <v>117</v>
+      </c>
+      <c r="C171" s="1">
+        <v>1980</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E171" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>346</v>
+        <v>247</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>347</v>
+        <v>248</v>
+      </c>
+      <c r="E172" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>373</v>
+        <v>346</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>374</v>
+        <v>347</v>
+      </c>
+      <c r="E173" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>362</v>
+        <v>374</v>
+      </c>
+      <c r="E174" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>6</v>
-      </c>
-      <c r="B175" t="s">
-        <v>98</v>
-      </c>
-      <c r="C175" s="1">
-        <v>1969</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E175" t="b">
-        <v>1</v>
-      </c>
-      <c r="G175" s="1">
-        <v>2</v>
+        <v>361</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="E175" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>33</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>153</v>
+        <v>6</v>
+      </c>
+      <c r="B176" t="s">
+        <v>98</v>
+      </c>
+      <c r="C176" s="1">
+        <v>1969</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E176" t="b">
-        <v>1</v>
+        <v>132</v>
+      </c>
+      <c r="E176" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G176" s="1">
         <v>2</v>
@@ -4308,67 +4506,67 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>167</v>
+        <v>33</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C177" s="1">
-        <v>2004</v>
+        <v>34</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E177" t="b">
-        <v>1</v>
+        <v>153</v>
+      </c>
+      <c r="E177" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G177" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>324</v>
+        <v>167</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="E178" t="b">
-        <v>1</v>
+        <v>168</v>
+      </c>
+      <c r="C178" s="1">
+        <v>2004</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E178" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>74</v>
+        <v>324</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C179" s="1">
-        <v>1968</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E179" t="b">
-        <v>1</v>
-      </c>
-      <c r="G179" s="1">
-        <v>2</v>
+        <v>325</v>
+      </c>
+      <c r="E179" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="C180" s="1">
-        <v>1971</v>
+        <v>1968</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E180" t="b">
-        <v>1</v>
+        <v>132</v>
+      </c>
+      <c r="E180" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G180" s="1">
         <v>2</v>
@@ -4376,19 +4574,19 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="C181" s="1">
-        <v>1985</v>
+        <v>1971</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E181" t="b">
-        <v>1</v>
+        <v>131</v>
+      </c>
+      <c r="E181" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G181" s="1">
         <v>2</v>
@@ -4396,127 +4594,142 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>421</v>
+        <v>11</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>422</v>
+        <v>99</v>
+      </c>
+      <c r="C182" s="1">
+        <v>1985</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E182" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G182" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>231</v>
+        <v>421</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C183" s="1">
-        <v>1977</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E183" t="b">
-        <v>1</v>
+        <v>422</v>
+      </c>
+      <c r="E183" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>487</v>
+        <v>231</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>488</v>
+        <v>232</v>
+      </c>
+      <c r="C184" s="1">
+        <v>1977</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E184" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>474</v>
+        <v>488</v>
+      </c>
+      <c r="E185" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>460</v>
+        <v>474</v>
+      </c>
+      <c r="E186" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>35</v>
+        <v>459</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C187" s="1">
-        <v>1975</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E187" t="b">
-        <v>1</v>
-      </c>
-      <c r="G187" s="1">
-        <v>2</v>
+        <v>460</v>
+      </c>
+      <c r="E187" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>397</v>
+        <v>35</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>398</v>
+        <v>36</v>
+      </c>
+      <c r="C188" s="1">
+        <v>1975</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E188" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G188" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>300</v>
+        <v>397</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="E189" t="b">
-        <v>1</v>
+        <v>398</v>
+      </c>
+      <c r="E189" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>12</v>
-      </c>
-      <c r="B190" t="s">
-        <v>100</v>
-      </c>
-      <c r="C190" s="1">
-        <v>1970</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E190" t="b">
-        <v>1</v>
-      </c>
-      <c r="G190" s="1">
-        <v>2</v>
+        <v>300</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E190" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>182</v>
-      </c>
-      <c r="B191" s="3" t="s">
-        <v>183</v>
+        <v>12</v>
+      </c>
+      <c r="B191" t="s">
+        <v>100</v>
       </c>
       <c r="C191" s="1">
-        <v>1995</v>
+        <v>1970</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E191" t="b">
-        <v>1</v>
+        <v>132</v>
+      </c>
+      <c r="E191" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G191" s="1">
         <v>2</v>
@@ -4524,128 +4737,131 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>302</v>
+        <v>182</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="E192" t="b">
-        <v>1</v>
+        <v>183</v>
+      </c>
+      <c r="C192" s="1">
+        <v>1995</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E192" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G192" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="E193" t="b">
-        <v>1</v>
+        <v>303</v>
+      </c>
+      <c r="E193" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>381</v>
+        <v>275</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>382</v>
+        <v>276</v>
+      </c>
+      <c r="E194" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="E195" t="b">
-        <v>1</v>
+        <v>382</v>
+      </c>
+      <c r="E195" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>20</v>
+        <v>322</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C196" s="1">
-        <v>1975</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E196" t="b">
-        <v>1</v>
-      </c>
-      <c r="G196" s="1">
-        <v>2</v>
+        <v>323</v>
+      </c>
+      <c r="E196" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>304</v>
+        <v>20</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="E197" t="b">
-        <v>1</v>
+        <v>58</v>
+      </c>
+      <c r="C197" s="1">
+        <v>1975</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E197" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G197" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>229</v>
+        <v>304</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C198" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E198" t="b">
-        <v>1</v>
+        <v>305</v>
+      </c>
+      <c r="E198" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>175</v>
+        <v>229</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>176</v>
+        <v>230</v>
       </c>
       <c r="C199" s="1">
-        <v>1963</v>
+        <v>2017</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="E199" t="b">
-        <v>1</v>
-      </c>
-      <c r="G199" s="1">
-        <v>2</v>
+        <v>134</v>
+      </c>
+      <c r="E199" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>37</v>
+        <v>175</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>153</v>
+        <v>176</v>
+      </c>
+      <c r="C200" s="1">
+        <v>1963</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E200" t="b">
-        <v>1</v>
+        <v>198</v>
+      </c>
+      <c r="E200" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G200" s="1">
         <v>2</v>
@@ -4653,19 +4869,19 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C201" s="1">
-        <v>1976</v>
+        <v>38</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E201" t="b">
-        <v>1</v>
+        <v>153</v>
+      </c>
+      <c r="E201" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G201" s="1">
         <v>2</v>
@@ -4673,99 +4889,114 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>467</v>
+        <v>112</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>468</v>
+        <v>113</v>
+      </c>
+      <c r="C202" s="1">
+        <v>1976</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E202" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G202" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>375</v>
+        <v>467</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>376</v>
+        <v>468</v>
+      </c>
+      <c r="E203" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>283</v>
+        <v>375</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="E204" t="b">
-        <v>1</v>
+        <v>376</v>
+      </c>
+      <c r="E204" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>158</v>
+        <v>283</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C205" s="1">
-        <v>1967</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E205" t="b">
-        <v>1</v>
-      </c>
-      <c r="G205" s="1">
-        <v>2</v>
+        <v>284</v>
+      </c>
+      <c r="E205" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>401</v>
+        <v>158</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>402</v>
+        <v>159</v>
+      </c>
+      <c r="C206" s="1">
+        <v>1967</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E206" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G206" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>255</v>
+        <v>401</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E207" t="b">
-        <v>1</v>
+        <v>402</v>
+      </c>
+      <c r="E207" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>118</v>
+        <v>255</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C208" s="1">
-        <v>1993</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E208" t="b">
-        <v>1</v>
-      </c>
-      <c r="G208" s="1">
-        <v>2</v>
+        <v>256</v>
+      </c>
+      <c r="E208" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>218</v>
+        <v>118</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="E209" t="b">
-        <v>1</v>
+        <v>119</v>
+      </c>
+      <c r="C209" s="1">
+        <v>1993</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E209" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G209" s="1">
         <v>2</v>
@@ -4773,422 +5004,446 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>259</v>
+        <v>218</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="E210" t="b">
-        <v>1</v>
+        <v>219</v>
+      </c>
+      <c r="E210" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G210" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>124</v>
+        <v>259</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C211" s="1">
-        <v>2004</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E211" t="b">
-        <v>1</v>
-      </c>
-      <c r="G211" s="1">
-        <v>4</v>
+        <v>260</v>
+      </c>
+      <c r="E211" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="C212" s="1">
-        <v>1976</v>
+        <v>2004</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E212" t="b">
-        <v>1</v>
+        <v>134</v>
+      </c>
+      <c r="E212" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G212" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>292</v>
+        <v>160</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="E213" t="b">
-        <v>1</v>
+        <v>161</v>
+      </c>
+      <c r="C213" s="1">
+        <v>1976</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E213" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G213" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>359</v>
+        <v>292</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>360</v>
+        <v>293</v>
+      </c>
+      <c r="E214" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>481</v>
+        <v>359</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>482</v>
+        <v>360</v>
+      </c>
+      <c r="E215" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>385</v>
+        <v>481</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>386</v>
+        <v>482</v>
+      </c>
+      <c r="E216" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>40</v>
+        <v>385</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C217" s="1">
-        <v>1970</v>
-      </c>
-      <c r="D217" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E217" t="b">
-        <v>1</v>
-      </c>
-      <c r="G217" s="1" t="s">
-        <v>217</v>
+        <v>386</v>
+      </c>
+      <c r="E217" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>193</v>
+        <v>40</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E218" t="b">
-        <v>1</v>
-      </c>
-      <c r="G218" s="1">
-        <v>2</v>
+        <v>41</v>
+      </c>
+      <c r="C218" s="1">
+        <v>1970</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E218" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G218" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C219" s="1">
-        <v>1970</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E219" t="b">
-        <v>1</v>
-      </c>
-      <c r="G219" s="1" t="s">
-        <v>217</v>
+        <v>194</v>
+      </c>
+      <c r="E219" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G219" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>383</v>
+        <v>205</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>384</v>
+        <v>206</v>
+      </c>
+      <c r="C220" s="1">
+        <v>1970</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E220" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G220" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>457</v>
+        <v>383</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>458</v>
+        <v>384</v>
+      </c>
+      <c r="E221" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>478</v>
+        <v>458</v>
+      </c>
+      <c r="E222" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>110</v>
+        <v>477</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C223" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E223" t="b">
-        <v>1</v>
-      </c>
-      <c r="G223" s="1">
-        <v>2</v>
+        <v>478</v>
+      </c>
+      <c r="E223" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>277</v>
+        <v>110</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="E224" t="b">
-        <v>1</v>
+        <v>111</v>
+      </c>
+      <c r="C224" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E224" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G224" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>184</v>
+        <v>277</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C225" s="1">
-        <v>2000</v>
-      </c>
-      <c r="D225" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E225" t="b">
-        <v>1</v>
-      </c>
-      <c r="G225" s="1" t="s">
-        <v>217</v>
+        <v>278</v>
+      </c>
+      <c r="E225" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>16</v>
-      </c>
-      <c r="B226" t="s">
-        <v>101</v>
+        <v>184</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="C226" s="1">
-        <v>1969</v>
+        <v>2000</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E226" t="b">
-        <v>1</v>
-      </c>
-      <c r="G226" s="1">
-        <v>2</v>
+        <v>134</v>
+      </c>
+      <c r="E226" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G226" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>66</v>
-      </c>
-      <c r="B227" s="3" t="s">
-        <v>67</v>
+        <v>16</v>
+      </c>
+      <c r="B227" t="s">
+        <v>101</v>
       </c>
       <c r="C227" s="1">
-        <v>1975</v>
+        <v>1969</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E227" t="b">
-        <v>1</v>
+        <v>132</v>
+      </c>
+      <c r="E227" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G227" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>433</v>
+        <v>66</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>434</v>
+        <v>67</v>
+      </c>
+      <c r="C228" s="1">
+        <v>1975</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E228" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>424</v>
+        <v>434</v>
+      </c>
+      <c r="E229" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>388</v>
+        <v>424</v>
+      </c>
+      <c r="E230" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>285</v>
+        <v>387</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="E231" t="b">
-        <v>1</v>
+        <v>388</v>
+      </c>
+      <c r="E231" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>8</v>
+        <v>285</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C232" s="1">
-        <v>1989</v>
-      </c>
-      <c r="D232" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E232" t="b">
-        <v>1</v>
-      </c>
-      <c r="G232" s="1">
-        <v>2</v>
+        <v>286</v>
+      </c>
+      <c r="E232" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>241</v>
+        <v>8</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>242</v>
+        <v>72</v>
       </c>
       <c r="C233" s="1">
-        <v>2002</v>
+        <v>1989</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E233" t="b">
-        <v>1</v>
+        <v>133</v>
+      </c>
+      <c r="E233" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G233" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>399</v>
-      </c>
-      <c r="B234" t="s">
-        <v>400</v>
+        <v>241</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C234" s="1">
+        <v>2002</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E234" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>52</v>
-      </c>
-      <c r="B235" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C235" s="1">
-        <v>2006</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E235" t="b">
-        <v>1</v>
-      </c>
-      <c r="G235" s="1">
-        <v>5</v>
+        <v>399</v>
+      </c>
+      <c r="B235" t="s">
+        <v>400</v>
+      </c>
+      <c r="E235" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>195</v>
+        <v>52</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>196</v>
+        <v>53</v>
       </c>
       <c r="C236" s="1">
-        <v>2019</v>
+        <v>2006</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E236" t="b">
-        <v>1</v>
+      <c r="E236" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G236" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>279</v>
+        <v>195</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="E237" t="b">
-        <v>1</v>
+        <v>196</v>
+      </c>
+      <c r="C237" s="1">
+        <v>2019</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E237" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G237" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>202</v>
+        <v>279</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C238" s="1">
-        <v>1998</v>
-      </c>
-      <c r="D238" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E238" t="b">
-        <v>1</v>
-      </c>
-      <c r="G238" s="1">
-        <v>2</v>
+        <v>280</v>
+      </c>
+      <c r="E238" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>49</v>
+        <v>197</v>
       </c>
       <c r="C239" s="1">
-        <v>1975</v>
+        <v>1998</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E239" t="b">
-        <v>1</v>
+        <v>136</v>
+      </c>
+      <c r="E239" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G239" s="1">
         <v>2</v>
@@ -5196,40 +5451,63 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>267</v>
+        <v>48</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="E240" t="b">
-        <v>1</v>
+        <v>49</v>
+      </c>
+      <c r="C240" s="1">
+        <v>1975</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E240" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G240" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>450</v>
+        <v>267</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>451</v>
+        <v>268</v>
+      </c>
+      <c r="E241" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
+        <v>450</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E242" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
         <v>203</v>
       </c>
-      <c r="B242" s="3" t="s">
+      <c r="B243" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C242" s="1">
+      <c r="C243" s="1">
         <v>1970</v>
       </c>
-      <c r="D242" s="1" t="s">
+      <c r="D243" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E242" t="b">
-        <v>1</v>
-      </c>
-      <c r="G242" s="1" t="s">
+      <c r="E243" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G243" s="1" t="s">
         <v>217</v>
       </c>
     </row>
@@ -5237,110 +5515,111 @@
   <hyperlinks>
     <hyperlink ref="B9" r:id="rId1" xr:uid="{8227A597-9225-4357-B8B6-9F19CC6D2D47}"/>
     <hyperlink ref="B28" r:id="rId2" xr:uid="{C440EE30-529A-4080-AE83-A4A978C3E02B}"/>
-    <hyperlink ref="B176" r:id="rId3" xr:uid="{C5FAAB38-5F1C-4A08-8709-401E7E23E0D1}"/>
-    <hyperlink ref="B187" r:id="rId4" xr:uid="{109EA93A-660A-4099-B212-FD77BC4B5297}"/>
-    <hyperlink ref="B200" r:id="rId5" xr:uid="{4FC29F3F-346D-4C86-81DD-BA31CA08B134}"/>
-    <hyperlink ref="B70" r:id="rId6" xr:uid="{98703E9F-F4A5-4829-8BBF-B9F807C63E68}"/>
-    <hyperlink ref="B217" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
+    <hyperlink ref="B177" r:id="rId3" xr:uid="{C5FAAB38-5F1C-4A08-8709-401E7E23E0D1}"/>
+    <hyperlink ref="B188" r:id="rId4" xr:uid="{109EA93A-660A-4099-B212-FD77BC4B5297}"/>
+    <hyperlink ref="B201" r:id="rId5" xr:uid="{4FC29F3F-346D-4C86-81DD-BA31CA08B134}"/>
+    <hyperlink ref="B71" r:id="rId6" xr:uid="{98703E9F-F4A5-4829-8BBF-B9F807C63E68}"/>
+    <hyperlink ref="B218" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
     <hyperlink ref="B45" r:id="rId8" xr:uid="{804D2DB9-BDF1-463B-9BD3-ACBFC15F041A}"/>
-    <hyperlink ref="B149" r:id="rId9" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
-    <hyperlink ref="B180" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
+    <hyperlink ref="B150" r:id="rId9" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
+    <hyperlink ref="B181" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
     <hyperlink ref="B38" r:id="rId11" xr:uid="{DF6F8079-E647-4079-9719-72DC2FF3791C}"/>
-    <hyperlink ref="B239" r:id="rId12" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
-    <hyperlink ref="B235" r:id="rId13" xr:uid="{ECCFE763-5E69-4122-B27B-DA1C21FADA86}"/>
+    <hyperlink ref="B240" r:id="rId12" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
+    <hyperlink ref="B236" r:id="rId13" xr:uid="{ECCFE763-5E69-4122-B27B-DA1C21FADA86}"/>
     <hyperlink ref="B2" r:id="rId14" xr:uid="{8869974B-11E2-4A99-8438-9F9B8ABEB9F6}"/>
     <hyperlink ref="B40" r:id="rId15" display="mailto:elizabeth.casarella@gmail.com" xr:uid="{C150E814-8C96-4E50-8A55-5EB3344749B1}"/>
-    <hyperlink ref="B196" r:id="rId16" display="mailto:paul@levelbreaker.com" xr:uid="{9746CC3F-863E-4E18-931A-FADD4ED10BF2}"/>
-    <hyperlink ref="B107" r:id="rId17" xr:uid="{316BCF75-05DF-4572-9F46-9F76127C0677}"/>
-    <hyperlink ref="B162" r:id="rId18" xr:uid="{57197F8F-1C51-4977-936A-74B15D239DF7}"/>
-    <hyperlink ref="B157" r:id="rId19" display="mailto:hef714@aol.com" xr:uid="{A4825BC7-F2DD-43E9-A39B-48544C54E403}"/>
-    <hyperlink ref="B89" r:id="rId20" xr:uid="{A871275A-577B-4F01-A590-B30FBADA40A1}"/>
-    <hyperlink ref="B227" r:id="rId21" xr:uid="{7E7AC9EC-4484-43DC-8B81-7AA0BCCFA407}"/>
-    <hyperlink ref="B134" r:id="rId22" display="mailto:Gjhusky52@yahoo.com" xr:uid="{1F5D9E16-5BA9-4F8F-B8CF-14485F325E5D}"/>
-    <hyperlink ref="B232" r:id="rId23" display="mailto:s.vibberts@yahoo.com" xr:uid="{CD95CA65-C8C5-44B3-8AFC-2E088AEC194C}"/>
-    <hyperlink ref="B179" r:id="rId24" display="mailto:oldparsonage3@gmail.com" xr:uid="{DC8DA8C9-CCEA-4FC3-AA05-1EF34B65B0C1}"/>
-    <hyperlink ref="B116" r:id="rId25" xr:uid="{C2395B48-B35E-4045-A136-C8B31BE4A5FC}"/>
+    <hyperlink ref="B197" r:id="rId16" display="mailto:paul@levelbreaker.com" xr:uid="{9746CC3F-863E-4E18-931A-FADD4ED10BF2}"/>
+    <hyperlink ref="B108" r:id="rId17" xr:uid="{316BCF75-05DF-4572-9F46-9F76127C0677}"/>
+    <hyperlink ref="B163" r:id="rId18" xr:uid="{57197F8F-1C51-4977-936A-74B15D239DF7}"/>
+    <hyperlink ref="B158" r:id="rId19" display="mailto:hef714@aol.com" xr:uid="{A4825BC7-F2DD-43E9-A39B-48544C54E403}"/>
+    <hyperlink ref="B90" r:id="rId20" xr:uid="{A871275A-577B-4F01-A590-B30FBADA40A1}"/>
+    <hyperlink ref="B228" r:id="rId21" xr:uid="{7E7AC9EC-4484-43DC-8B81-7AA0BCCFA407}"/>
+    <hyperlink ref="B135" r:id="rId22" display="mailto:Gjhusky52@yahoo.com" xr:uid="{1F5D9E16-5BA9-4F8F-B8CF-14485F325E5D}"/>
+    <hyperlink ref="B233" r:id="rId23" display="mailto:s.vibberts@yahoo.com" xr:uid="{CD95CA65-C8C5-44B3-8AFC-2E088AEC194C}"/>
+    <hyperlink ref="B180" r:id="rId24" display="mailto:oldparsonage3@gmail.com" xr:uid="{DC8DA8C9-CCEA-4FC3-AA05-1EF34B65B0C1}"/>
+    <hyperlink ref="B117" r:id="rId25" xr:uid="{C2395B48-B35E-4045-A136-C8B31BE4A5FC}"/>
     <hyperlink ref="B11" r:id="rId26" xr:uid="{37F7977A-EC68-4733-8738-6C53C959B816}"/>
     <hyperlink ref="B20" r:id="rId27" xr:uid="{A209B655-7CEF-4F8D-BFEE-DFB49C33870B}"/>
-    <hyperlink ref="B155" r:id="rId28" xr:uid="{46F1EE8C-941D-4D6B-A27A-3BDDA65A15CE}"/>
+    <hyperlink ref="B156" r:id="rId28" xr:uid="{46F1EE8C-941D-4D6B-A27A-3BDDA65A15CE}"/>
     <hyperlink ref="B13" r:id="rId29" xr:uid="{647703FF-1796-4612-923D-2A3CF89F5A46}"/>
     <hyperlink ref="B60" r:id="rId30" xr:uid="{D4F421DD-A322-4F00-A209-B464A28664A6}"/>
-    <hyperlink ref="B123" r:id="rId31" xr:uid="{5FF15619-CFAB-48CB-8BF0-78013919701C}"/>
-    <hyperlink ref="B146" r:id="rId32" display="mailto:Kmills8080@gmail.com" xr:uid="{6653A4F2-00C8-4ACF-A9B2-950ABB23037C}"/>
-    <hyperlink ref="B125" r:id="rId33" xr:uid="{0F8932AA-3F92-4F04-A82F-C839649C3558}"/>
-    <hyperlink ref="B181" r:id="rId34" xr:uid="{74573551-A238-45F0-95FA-078470676D33}"/>
-    <hyperlink ref="B152" r:id="rId35" xr:uid="{F093A50A-9255-43F2-873A-E61FB97B7B6E}"/>
-    <hyperlink ref="B68" r:id="rId36" display="mailto:lostdogs@charter.net" xr:uid="{95D046AE-D83E-4029-8E4D-F457CDD3F23E}"/>
+    <hyperlink ref="B124" r:id="rId31" xr:uid="{5FF15619-CFAB-48CB-8BF0-78013919701C}"/>
+    <hyperlink ref="B147" r:id="rId32" display="mailto:Kmills8080@gmail.com" xr:uid="{6653A4F2-00C8-4ACF-A9B2-950ABB23037C}"/>
+    <hyperlink ref="B126" r:id="rId33" xr:uid="{0F8932AA-3F92-4F04-A82F-C839649C3558}"/>
+    <hyperlink ref="B182" r:id="rId34" xr:uid="{74573551-A238-45F0-95FA-078470676D33}"/>
+    <hyperlink ref="B153" r:id="rId35" xr:uid="{F093A50A-9255-43F2-873A-E61FB97B7B6E}"/>
+    <hyperlink ref="B69" r:id="rId36" display="mailto:lostdogs@charter.net" xr:uid="{95D046AE-D83E-4029-8E4D-F457CDD3F23E}"/>
     <hyperlink ref="B57" r:id="rId37" xr:uid="{93D1D532-1D29-4735-B6C3-7B9B46F15302}"/>
-    <hyperlink ref="B117" r:id="rId38" display="mailto:langer0125@gmail.com" xr:uid="{EF3BA7C4-32BE-431A-9979-8B42711B0D73}"/>
-    <hyperlink ref="B223" r:id="rId39" display="mailto:Ntjr05@gmail.com" xr:uid="{38DDEC56-F2AD-4C66-8377-3BFC9B7BDDB9}"/>
-    <hyperlink ref="B201" r:id="rId40" display="mailto:gregsinay3@gmail.com" xr:uid="{004C878C-63EB-40FC-B549-87CFABDE66E1}"/>
-    <hyperlink ref="B101" r:id="rId41" display="mailto:Suj9283@yahoo.com" xr:uid="{E8FF833B-A9E0-4AED-A7DB-065ED67E2244}"/>
-    <hyperlink ref="B170" r:id="rId42" xr:uid="{FAF882CB-F959-4D5E-B4E0-3608ADC9DA13}"/>
-    <hyperlink ref="B208" r:id="rId43" display="mailto:sosikiii@msn.com" xr:uid="{218E6BB5-6D46-4A2B-BD2C-6CF05A021B3C}"/>
-    <hyperlink ref="B124" r:id="rId44" xr:uid="{33551D8E-478C-410F-9E21-46488F70F42D}"/>
-    <hyperlink ref="B211" r:id="rId45" display="mailto:brisparks@gmail.com" xr:uid="{E8A49946-13F1-4C59-AD3D-A3E5B9D77EFF}"/>
-    <hyperlink ref="B120" r:id="rId46" display="mailto:Dlew44@gmail.com" xr:uid="{25AC56D9-918C-4162-BE04-DAA69217239F}"/>
+    <hyperlink ref="B118" r:id="rId38" display="mailto:langer0125@gmail.com" xr:uid="{EF3BA7C4-32BE-431A-9979-8B42711B0D73}"/>
+    <hyperlink ref="B224" r:id="rId39" display="mailto:Ntjr05@gmail.com" xr:uid="{38DDEC56-F2AD-4C66-8377-3BFC9B7BDDB9}"/>
+    <hyperlink ref="B202" r:id="rId40" display="mailto:gregsinay3@gmail.com" xr:uid="{004C878C-63EB-40FC-B549-87CFABDE66E1}"/>
+    <hyperlink ref="B102" r:id="rId41" display="mailto:Suj9283@yahoo.com" xr:uid="{E8FF833B-A9E0-4AED-A7DB-065ED67E2244}"/>
+    <hyperlink ref="B171" r:id="rId42" xr:uid="{FAF882CB-F959-4D5E-B4E0-3608ADC9DA13}"/>
+    <hyperlink ref="B209" r:id="rId43" display="mailto:sosikiii@msn.com" xr:uid="{218E6BB5-6D46-4A2B-BD2C-6CF05A021B3C}"/>
+    <hyperlink ref="B125" r:id="rId44" xr:uid="{33551D8E-478C-410F-9E21-46488F70F42D}"/>
+    <hyperlink ref="B212" r:id="rId45" display="mailto:brisparks@gmail.com" xr:uid="{E8A49946-13F1-4C59-AD3D-A3E5B9D77EFF}"/>
+    <hyperlink ref="B121" r:id="rId46" display="mailto:Dlew44@gmail.com" xr:uid="{25AC56D9-918C-4162-BE04-DAA69217239F}"/>
     <hyperlink ref="B12" r:id="rId47" xr:uid="{02619D1B-E12D-411C-8267-1EA72D337FA4}"/>
     <hyperlink ref="B26" r:id="rId48" xr:uid="{297F912D-F1B3-4511-B9FB-7F6A5151679A}"/>
     <hyperlink ref="B34" r:id="rId49" xr:uid="{23A72ED8-42A8-4AD2-AED4-16447BAE4A08}"/>
     <hyperlink ref="B36" r:id="rId50" xr:uid="{5484D007-8240-489C-A613-B2C0F0F2AC56}"/>
     <hyperlink ref="B42" r:id="rId51" xr:uid="{D01BE816-0B5A-4446-924C-46E6BAD18108}"/>
-    <hyperlink ref="B79" r:id="rId52" xr:uid="{276C5002-FCF1-4B64-9438-E4287F3F2787}"/>
-    <hyperlink ref="B137" r:id="rId53" xr:uid="{05B37D53-659E-462F-9D42-00105B550079}"/>
-    <hyperlink ref="B141" r:id="rId54" xr:uid="{F7EC428E-8409-4830-9429-9C5E7ABB09A4}"/>
-    <hyperlink ref="B159" r:id="rId55" xr:uid="{EE1C2C4D-03AE-46ED-A073-46B29C8D3689}"/>
-    <hyperlink ref="B205" r:id="rId56" xr:uid="{4C733EB2-A8CB-4A19-80B4-31601DA15BF2}"/>
-    <hyperlink ref="B212" r:id="rId57" xr:uid="{77C5CEA7-AAB7-4C0E-8FED-A2F21F462250}"/>
-    <hyperlink ref="B225" r:id="rId58" xr:uid="{D3F25966-9FE3-42C3-94BB-54469D722B9E}"/>
-    <hyperlink ref="B98" r:id="rId59" display="mailto:bill.irwin58@gmail.com" xr:uid="{21398664-274B-466E-AEF3-003790919F40}"/>
-    <hyperlink ref="B91" r:id="rId60" display="mailto:Hogan6523@Yahoo.com" xr:uid="{8F033920-5D36-4035-9970-BF7A906D9337}"/>
-    <hyperlink ref="B177" r:id="rId61" xr:uid="{3915D652-1507-4F3C-AEB3-935E95D07A08}"/>
-    <hyperlink ref="B169" r:id="rId62" display="mailto:bernard.e.palmer@gmail.com" xr:uid="{4E7DEDEB-BA72-4331-A716-378C6A511DCC}"/>
-    <hyperlink ref="B78" r:id="rId63" display="mailto:fogs14@yahoo.com" xr:uid="{E734B4DB-161E-4386-9BE4-4D2A768C19C0}"/>
+    <hyperlink ref="B80" r:id="rId52" xr:uid="{276C5002-FCF1-4B64-9438-E4287F3F2787}"/>
+    <hyperlink ref="B138" r:id="rId53" xr:uid="{05B37D53-659E-462F-9D42-00105B550079}"/>
+    <hyperlink ref="B142" r:id="rId54" xr:uid="{F7EC428E-8409-4830-9429-9C5E7ABB09A4}"/>
+    <hyperlink ref="B160" r:id="rId55" xr:uid="{EE1C2C4D-03AE-46ED-A073-46B29C8D3689}"/>
+    <hyperlink ref="B206" r:id="rId56" xr:uid="{4C733EB2-A8CB-4A19-80B4-31601DA15BF2}"/>
+    <hyperlink ref="B213" r:id="rId57" xr:uid="{77C5CEA7-AAB7-4C0E-8FED-A2F21F462250}"/>
+    <hyperlink ref="B226" r:id="rId58" xr:uid="{D3F25966-9FE3-42C3-94BB-54469D722B9E}"/>
+    <hyperlink ref="B99" r:id="rId59" display="mailto:bill.irwin58@gmail.com" xr:uid="{21398664-274B-466E-AEF3-003790919F40}"/>
+    <hyperlink ref="B92" r:id="rId60" display="mailto:Hogan6523@Yahoo.com" xr:uid="{8F033920-5D36-4035-9970-BF7A906D9337}"/>
+    <hyperlink ref="B178" r:id="rId61" xr:uid="{3915D652-1507-4F3C-AEB3-935E95D07A08}"/>
+    <hyperlink ref="B170" r:id="rId62" display="mailto:bernard.e.palmer@gmail.com" xr:uid="{4E7DEDEB-BA72-4331-A716-378C6A511DCC}"/>
+    <hyperlink ref="B79" r:id="rId63" display="mailto:fogs14@yahoo.com" xr:uid="{E734B4DB-161E-4386-9BE4-4D2A768C19C0}"/>
     <hyperlink ref="B6" r:id="rId64" xr:uid="{94ECE3FB-34A8-40D2-A511-C6F49E1F79C8}"/>
-    <hyperlink ref="B199" r:id="rId65" xr:uid="{8042AEE0-2132-486D-AFC6-008B86CDABF9}"/>
+    <hyperlink ref="B200" r:id="rId65" xr:uid="{8042AEE0-2132-486D-AFC6-008B86CDABF9}"/>
     <hyperlink ref="B56" r:id="rId66" display="mailto:rmdecambre@gmail.com" xr:uid="{61906EF9-7178-4E37-9EF5-F697B7AF8714}"/>
-    <hyperlink ref="B191" r:id="rId67" xr:uid="{C73311BF-B167-4642-BFA3-507299A38EFE}"/>
+    <hyperlink ref="B192" r:id="rId67" xr:uid="{C73311BF-B167-4642-BFA3-507299A38EFE}"/>
     <hyperlink ref="B44" r:id="rId68" xr:uid="{A7D0DDDF-0E1D-4EAA-BC8A-6B20E1097E98}"/>
-    <hyperlink ref="B75" r:id="rId69" display="mailto:tfink9@juno.com" xr:uid="{34A73A04-8440-48B2-9348-0E4A6602D420}"/>
-    <hyperlink ref="B74" r:id="rId70" xr:uid="{0BB6B871-9927-4DD2-B508-224D22FD6229}"/>
-    <hyperlink ref="B218" r:id="rId71" xr:uid="{6DBAAB43-CE57-45EC-BCA9-CB408BBC84B6}"/>
-    <hyperlink ref="B236" r:id="rId72" xr:uid="{DB8385C7-8934-4CD0-B87E-4D74991BD43E}"/>
-    <hyperlink ref="B242" r:id="rId73" xr:uid="{CEB5326F-2589-4355-9CCD-6A3D6FC84E4A}"/>
-    <hyperlink ref="B219" r:id="rId74" xr:uid="{4A20E15A-8219-4697-83CE-53E329D1A594}"/>
-    <hyperlink ref="B67" r:id="rId75" xr:uid="{CB15C81B-047D-40F8-BDE8-B1539A6E2F0B}"/>
-    <hyperlink ref="B80" r:id="rId76" xr:uid="{B485936F-7DCD-4862-9E33-EEA8B063A75F}"/>
+    <hyperlink ref="B76" r:id="rId69" display="mailto:tfink9@juno.com" xr:uid="{34A73A04-8440-48B2-9348-0E4A6602D420}"/>
+    <hyperlink ref="B75" r:id="rId70" xr:uid="{0BB6B871-9927-4DD2-B508-224D22FD6229}"/>
+    <hyperlink ref="B219" r:id="rId71" xr:uid="{6DBAAB43-CE57-45EC-BCA9-CB408BBC84B6}"/>
+    <hyperlink ref="B237" r:id="rId72" xr:uid="{DB8385C7-8934-4CD0-B87E-4D74991BD43E}"/>
+    <hyperlink ref="B243" r:id="rId73" xr:uid="{CEB5326F-2589-4355-9CCD-6A3D6FC84E4A}"/>
+    <hyperlink ref="B220" r:id="rId74" xr:uid="{4A20E15A-8219-4697-83CE-53E329D1A594}"/>
+    <hyperlink ref="B68" r:id="rId75" xr:uid="{CB15C81B-047D-40F8-BDE8-B1539A6E2F0B}"/>
+    <hyperlink ref="B81" r:id="rId76" xr:uid="{B485936F-7DCD-4862-9E33-EEA8B063A75F}"/>
     <hyperlink ref="B15" r:id="rId77" xr:uid="{74BFC159-A59B-4245-BC6C-B882819624B3}"/>
-    <hyperlink ref="B69" r:id="rId78" xr:uid="{F3187CCB-7830-43D4-9E21-FF900FE7F868}"/>
-    <hyperlink ref="B209" r:id="rId79" display="mailto:Sowell47@gmail.com" xr:uid="{03411C75-D37D-4435-805E-31377118488D}"/>
+    <hyperlink ref="B70" r:id="rId78" xr:uid="{F3187CCB-7830-43D4-9E21-FF900FE7F868}"/>
+    <hyperlink ref="B210" r:id="rId79" display="mailto:Sowell47@gmail.com" xr:uid="{03411C75-D37D-4435-805E-31377118488D}"/>
     <hyperlink ref="B17" r:id="rId80" xr:uid="{6DB4A5CC-5D1F-4EF9-932C-678F4FC22DA9}"/>
     <hyperlink ref="B27" r:id="rId81" xr:uid="{CF88E969-EAAC-46AC-8516-43C895BD47AD}"/>
-    <hyperlink ref="B96" r:id="rId82" xr:uid="{FC781576-FE15-492B-950C-DC624C8FF2B0}"/>
-    <hyperlink ref="B158" r:id="rId83" xr:uid="{0486C015-E59C-4C68-91D3-4ACAD00E12CD}"/>
-    <hyperlink ref="B94" r:id="rId84" display="mailto:Phuntone9@gmail.com" xr:uid="{97AD22F5-2C24-4F75-816F-70DD5E10F7E3}"/>
+    <hyperlink ref="B97" r:id="rId82" xr:uid="{FC781576-FE15-492B-950C-DC624C8FF2B0}"/>
+    <hyperlink ref="B159" r:id="rId83" xr:uid="{0486C015-E59C-4C68-91D3-4ACAD00E12CD}"/>
+    <hyperlink ref="B95" r:id="rId84" display="mailto:Phuntone9@gmail.com" xr:uid="{97AD22F5-2C24-4F75-816F-70DD5E10F7E3}"/>
     <hyperlink ref="B4" r:id="rId85" display="mailto:rasool@icgglobal.com" xr:uid="{8CC08D82-DC80-4069-A607-F03D467D475C}"/>
     <hyperlink ref="B31" r:id="rId86" display="mailto:Steven.brouse@gmail.com" xr:uid="{0E704A9F-B2C5-4BBF-8D88-3BAC495E147F}"/>
     <hyperlink ref="B16" r:id="rId87" display="mailto:j.b.internationalcellars@gmail.com" xr:uid="{839EF4EB-A6F8-43A3-B660-F7D49F2E61D4}"/>
-    <hyperlink ref="B198" r:id="rId88" display="mailto:Bryant.shirreffs@yahoo.com" xr:uid="{BA1A9DD0-A412-4686-BC81-5FFC622C25A9}"/>
-    <hyperlink ref="B183" r:id="rId89" display="mailto:jcpurl@aol.com" xr:uid="{E4621CD0-F8C1-458A-9567-BDCA1089D95C}"/>
+    <hyperlink ref="B199" r:id="rId88" display="mailto:Bryant.shirreffs@yahoo.com" xr:uid="{BA1A9DD0-A412-4686-BC81-5FFC622C25A9}"/>
+    <hyperlink ref="B184" r:id="rId89" display="mailto:jcpurl@aol.com" xr:uid="{E4621CD0-F8C1-458A-9567-BDCA1089D95C}"/>
     <hyperlink ref="B47" r:id="rId90" display="mailto:jeremyclaflin6@gmail.com" xr:uid="{7538A4E0-FA80-4082-AB29-64F526F8CC24}"/>
-    <hyperlink ref="B115" r:id="rId91" display="mailto:landolfimark285@gmail.com" xr:uid="{20BF721A-932E-4360-ABD6-6884414072C6}"/>
-    <hyperlink ref="B150" r:id="rId92" display="mailto:moynihanjr@gmail.com" xr:uid="{09EAB6B8-1CC0-499B-A77D-568323DE9156}"/>
-    <hyperlink ref="B233" r:id="rId93" display="mailto:Razulwallace@gmail.com" xr:uid="{9C945E29-299D-45FA-BA11-7A092AE0F910}"/>
+    <hyperlink ref="B116" r:id="rId91" display="mailto:landolfimark285@gmail.com" xr:uid="{20BF721A-932E-4360-ABD6-6884414072C6}"/>
+    <hyperlink ref="B151" r:id="rId92" display="mailto:moynihanjr@gmail.com" xr:uid="{09EAB6B8-1CC0-499B-A77D-568323DE9156}"/>
+    <hyperlink ref="B234" r:id="rId93" display="mailto:Razulwallace@gmail.com" xr:uid="{9C945E29-299D-45FA-BA11-7A092AE0F910}"/>
     <hyperlink ref="B21" r:id="rId94" xr:uid="{6C755390-FCE5-44E8-BA6D-9E526EFB3191}"/>
-    <hyperlink ref="B168" r:id="rId95" xr:uid="{9BE879F8-944D-49CA-BDF0-CCE8169FD5BB}"/>
-    <hyperlink ref="B171" r:id="rId96" xr:uid="{540A47A4-EBFF-400C-8A2A-34A2B8B77B2D}"/>
-    <hyperlink ref="B142" r:id="rId97" xr:uid="{E13A9C92-7D31-49D1-BE2B-F27CA13491B5}"/>
-    <hyperlink ref="B95" r:id="rId98" xr:uid="{81BDB679-61B9-4944-986C-D6792DE6A5DB}"/>
+    <hyperlink ref="B169" r:id="rId95" xr:uid="{9BE879F8-944D-49CA-BDF0-CCE8169FD5BB}"/>
+    <hyperlink ref="B172" r:id="rId96" xr:uid="{540A47A4-EBFF-400C-8A2A-34A2B8B77B2D}"/>
+    <hyperlink ref="B143" r:id="rId97" xr:uid="{E13A9C92-7D31-49D1-BE2B-F27CA13491B5}"/>
+    <hyperlink ref="B96" r:id="rId98" xr:uid="{81BDB679-61B9-4944-986C-D6792DE6A5DB}"/>
     <hyperlink ref="B41" r:id="rId99" xr:uid="{9B66D431-5F64-437B-9ED8-E1AA1BFEF87C}"/>
-    <hyperlink ref="B207" r:id="rId100" xr:uid="{2A6177C8-A0ED-4F54-8722-887534A734D3}"/>
+    <hyperlink ref="B208" r:id="rId100" xr:uid="{2A6177C8-A0ED-4F54-8722-887534A734D3}"/>
     <hyperlink ref="B55" r:id="rId101" xr:uid="{D91E0C62-76BF-46FA-9851-1CA99AA007AE}"/>
-    <hyperlink ref="B210" r:id="rId102" xr:uid="{7D0062DB-B731-433D-A351-DC4851587C48}"/>
+    <hyperlink ref="B211" r:id="rId102" xr:uid="{7D0062DB-B731-433D-A351-DC4851587C48}"/>
     <hyperlink ref="B54" r:id="rId103" xr:uid="{4CA45CB5-781C-4C0B-ADA3-5C566420DAE0}"/>
-    <hyperlink ref="B220" r:id="rId104" display="mailto:DaniaSweeney@aol.com" xr:uid="{14EDA941-F642-4041-9501-FBEC3A51835C}"/>
+    <hyperlink ref="B221" r:id="rId104" display="mailto:DaniaSweeney@aol.com" xr:uid="{14EDA941-F642-4041-9501-FBEC3A51835C}"/>
+    <hyperlink ref="B66" r:id="rId105" xr:uid="{96814C29-3A86-4144-AFD3-C82B183A5390}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId105"/>
+  <pageSetup orientation="portrait" r:id="rId106"/>
 </worksheet>
 </file>
--- a/UConnBleedBlue/wwwroot/Data/Players.xlsx
+++ b/UConnBleedBlue/wwwroot/Data/Players.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\UConnBleedBlue\UConnBleedBlue\wwwroot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F07D21F-5AA9-4F6E-A47D-0574327ED22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73753A9-04D0-44F6-84A7-6A232694D0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32655" yWindow="-1185" windowWidth="28800" windowHeight="15345" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
   </bookViews>
@@ -2269,6 +2269,9 @@
       <c r="E3" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="F3" s="7">
+        <v>100</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -2299,7 +2302,7 @@
       </c>
       <c r="J5" s="7">
         <f>SUM(F2:F285)</f>
-        <v>800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -2317,6 +2320,9 @@
       </c>
       <c r="E6" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="F6" s="7">
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">

--- a/UConnBleedBlue/wwwroot/Data/Players.xlsx
+++ b/UConnBleedBlue/wwwroot/Data/Players.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\UConnBleedBlue\UConnBleedBlue\wwwroot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA8C0F6-576F-40D8-9E2E-5EFFAB5CC538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42277B30-3352-4A19-946C-EEDE87FBB192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-2325" windowWidth="38640" windowHeight="21120" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="673">
   <si>
     <t>Demers, Kenny</t>
   </si>
@@ -1517,9 +1517,6 @@
     <t>Total Donations</t>
   </si>
   <si>
-    <t>Extra Tickets Needed</t>
-  </si>
-  <si>
     <t>Silva,John</t>
   </si>
   <si>
@@ -2055,6 +2052,9 @@
   </si>
   <si>
     <t>Horvath,Howard</t>
+  </si>
+  <si>
+    <t>To ME Cash App</t>
   </si>
 </sst>
 </file>
@@ -2153,7 +2153,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2211,6 +2211,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2609,9 +2612,12 @@
       <c r="E4" s="11" t="b">
         <v>1</v>
       </c>
+      <c r="F4" s="23">
+        <v>100</v>
+      </c>
       <c r="J4" s="6">
         <f>SUM(F2:F329)</f>
-        <v>12050</v>
+        <v>12150</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2650,9 +2656,6 @@
       <c r="E6" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>493</v>
-      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -2667,10 +2670,6 @@
       <c r="E7" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="J7" s="1">
-        <f>SUM(G2:G329)</f>
-        <v>3</v>
-      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -2683,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -2706,7 +2705,7 @@
         <v>100</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -2720,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -2743,7 +2742,7 @@
         <v>250</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -2762,13 +2761,16 @@
       <c r="E12" s="11" t="b">
         <v>1</v>
       </c>
+      <c r="J12" s="14" t="s">
+        <v>672</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>531</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>532</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>533</v>
       </c>
       <c r="C13" s="1">
         <v>1987</v>
@@ -2782,7 +2784,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>485</v>
@@ -2822,10 +2824,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>647</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>648</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>649</v>
       </c>
       <c r="C16" s="1">
         <v>1996</v>
@@ -2890,10 +2892,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>655</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>656</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>657</v>
       </c>
       <c r="C20" s="1">
         <v>1995</v>
@@ -2935,10 +2937,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>642</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>643</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>644</v>
       </c>
       <c r="C23" s="1">
         <v>1982</v>
@@ -2949,7 +2951,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>341</v>
@@ -2963,10 +2965,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>498</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>499</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>500</v>
       </c>
       <c r="C25" s="1">
         <v>1977</v>
@@ -2977,10 +2979,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>585</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>586</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>587</v>
       </c>
       <c r="C26" s="1">
         <v>2004</v>
@@ -3053,10 +3055,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C31" s="1">
         <v>2017</v>
@@ -3081,10 +3083,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>504</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>505</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>506</v>
       </c>
       <c r="C33" s="1">
         <v>1998</v>
@@ -3106,10 +3108,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>547</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>548</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>549</v>
       </c>
       <c r="C35" s="1">
         <v>1993</v>
@@ -3182,10 +3184,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>630</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>631</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>632</v>
       </c>
       <c r="E40" s="1" t="b">
         <v>0</v>
@@ -3213,10 +3215,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E42" s="14" t="b">
         <v>1</v>
@@ -3224,7 +3226,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>293</v>
@@ -3241,10 +3243,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>541</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>542</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>543</v>
       </c>
       <c r="C44" s="1">
         <v>1973</v>
@@ -3255,10 +3257,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>502</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>503</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>504</v>
       </c>
       <c r="C45" s="1">
         <v>1981</v>
@@ -3407,14 +3409,14 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="1">
         <v>2025</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E55" s="1" t="b">
         <v>0</v>
@@ -3560,10 +3562,10 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>523</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>524</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>525</v>
       </c>
       <c r="E65" s="1" t="b">
         <v>0</v>
@@ -3602,7 +3604,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B68" s="15"/>
       <c r="E68" s="14" t="b">
@@ -3628,10 +3630,10 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>650</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>651</v>
       </c>
       <c r="C70" s="1">
         <v>2002</v>
@@ -3656,10 +3658,10 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>528</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>529</v>
       </c>
       <c r="C72" s="1">
         <v>1994</v>
@@ -3670,10 +3672,10 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>582</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>583</v>
       </c>
       <c r="C73" s="1">
         <v>2000</v>
@@ -3718,13 +3720,13 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="D76" s="8" t="s">
         <v>512</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>513</v>
       </c>
       <c r="E76" s="1" t="b">
         <v>0</v>
@@ -3749,10 +3751,10 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>591</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>592</v>
       </c>
       <c r="C78" s="1">
         <v>2015</v>
@@ -3831,10 +3833,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>561</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>562</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>563</v>
       </c>
       <c r="C83" s="1">
         <v>1983</v>
@@ -3856,10 +3858,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>587</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>588</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>589</v>
       </c>
       <c r="C85" s="1">
         <v>2009</v>
@@ -3887,10 +3889,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>559</v>
+      </c>
+      <c r="B87" s="7" t="s">
         <v>560</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>561</v>
       </c>
       <c r="C87" s="1">
         <v>1985</v>
@@ -3912,7 +3914,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>415</v>
@@ -3929,10 +3931,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C90" s="1">
         <v>1981</v>
@@ -4011,10 +4013,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>557</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>558</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>559</v>
       </c>
       <c r="C95" s="1">
         <v>2003</v>
@@ -4025,10 +4027,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>640</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>641</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>642</v>
       </c>
       <c r="C96" s="1">
         <v>1980</v>
@@ -4087,10 +4089,10 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>644</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>645</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>646</v>
       </c>
       <c r="C100" s="1">
         <v>1990</v>
@@ -4129,10 +4131,10 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>623</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>624</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>625</v>
       </c>
       <c r="C103" s="1">
         <v>1978</v>
@@ -4141,7 +4143,7 @@
         <v>1</v>
       </c>
       <c r="J103" s="8" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -4158,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="J104" s="11" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -4166,7 +4168,7 @@
         <v>197</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C105" s="1">
         <v>1982</v>
@@ -4178,7 +4180,7 @@
         <v>1</v>
       </c>
       <c r="J105" s="12" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -4198,12 +4200,12 @@
         <v>500</v>
       </c>
       <c r="J106" s="13" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B107" s="3"/>
       <c r="F107" s="18">
@@ -4227,6 +4229,9 @@
       <c r="F108" s="17">
         <v>50</v>
       </c>
+      <c r="J108" s="14" t="s">
+        <v>672</v>
+      </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
@@ -4247,10 +4252,10 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>533</v>
+      </c>
+      <c r="B110" s="3" t="s">
         <v>534</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>535</v>
       </c>
       <c r="C110" s="1">
         <v>2021</v>
@@ -4298,10 +4303,10 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>549</v>
+      </c>
+      <c r="B113" s="3" t="s">
         <v>550</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>551</v>
       </c>
       <c r="C113" s="1">
         <v>1988</v>
@@ -4340,10 +4345,10 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>506</v>
+      </c>
+      <c r="B116" s="3" t="s">
         <v>507</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>508</v>
       </c>
       <c r="C116" s="1">
         <v>1988</v>
@@ -4354,10 +4359,10 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>595</v>
+      </c>
+      <c r="B117" s="3" t="s">
         <v>596</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>597</v>
       </c>
       <c r="C117" s="1">
         <v>2004</v>
@@ -4368,10 +4373,10 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>597</v>
+      </c>
+      <c r="B118" s="3" t="s">
         <v>598</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>599</v>
       </c>
       <c r="C118" s="1">
         <v>2008</v>
@@ -4382,10 +4387,10 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>579</v>
+      </c>
+      <c r="B119" s="3" t="s">
         <v>580</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>581</v>
       </c>
       <c r="C119" s="1">
         <v>1963</v>
@@ -4402,10 +4407,10 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>519</v>
+      </c>
+      <c r="B120" s="3" t="s">
         <v>520</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>521</v>
       </c>
       <c r="C120" s="1">
         <v>1976</v>
@@ -4475,10 +4480,10 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>551</v>
+      </c>
+      <c r="B125" s="3" t="s">
         <v>552</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>553</v>
       </c>
       <c r="C125" s="1">
         <v>1979</v>
@@ -4534,10 +4539,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>545</v>
+      </c>
+      <c r="B129" s="3" t="s">
         <v>546</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>547</v>
       </c>
       <c r="C129" s="1">
         <v>1970</v>
@@ -4548,10 +4553,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>515</v>
+      </c>
+      <c r="B130" s="3" t="s">
         <v>516</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>517</v>
       </c>
       <c r="C130" s="1">
         <v>2009</v>
@@ -4607,7 +4612,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B134" s="3"/>
       <c r="E134" s="1" t="b">
@@ -4658,10 +4663,10 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>563</v>
+      </c>
+      <c r="B138" s="3" t="s">
         <v>564</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>565</v>
       </c>
       <c r="E138" s="1" t="b">
         <v>0</v>
@@ -4686,7 +4691,7 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>476</v>
@@ -4720,10 +4725,10 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>638</v>
+      </c>
+      <c r="B142" s="3" t="s">
         <v>639</v>
-      </c>
-      <c r="B142" s="3" t="s">
-        <v>640</v>
       </c>
       <c r="C142" s="1">
         <v>1987</v>
@@ -4745,10 +4750,10 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>599</v>
+      </c>
+      <c r="B144" s="3" t="s">
         <v>600</v>
-      </c>
-      <c r="B144" s="3" t="s">
-        <v>601</v>
       </c>
       <c r="C144" s="1">
         <v>1988</v>
@@ -4759,10 +4764,10 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>625</v>
+      </c>
+      <c r="B145" s="3" t="s">
         <v>626</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>627</v>
       </c>
       <c r="C145" s="1">
         <v>1980</v>
@@ -4807,10 +4812,10 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>592</v>
+      </c>
+      <c r="B148" s="7" t="s">
         <v>593</v>
-      </c>
-      <c r="B148" s="7" t="s">
-        <v>594</v>
       </c>
       <c r="C148" s="1">
         <v>2021</v>
@@ -4936,7 +4941,7 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>336</v>
@@ -4964,10 +4969,10 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>508</v>
+      </c>
+      <c r="B159" s="3" t="s">
         <v>509</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>510</v>
       </c>
       <c r="C159" s="1">
         <v>1968</v>
@@ -4984,7 +4989,7 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B160" s="3"/>
       <c r="C160" s="1">
@@ -5171,10 +5176,10 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
+        <v>611</v>
+      </c>
+      <c r="B172" s="3" t="s">
         <v>612</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>613</v>
       </c>
       <c r="C172" s="1">
         <v>1998</v>
@@ -5202,10 +5207,10 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>574</v>
+      </c>
+      <c r="B174" s="3" t="s">
         <v>575</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>576</v>
       </c>
       <c r="C174" s="1">
         <v>2002</v>
@@ -5264,10 +5269,10 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>555</v>
+      </c>
+      <c r="B178" s="3" t="s">
         <v>556</v>
-      </c>
-      <c r="B178" s="3" t="s">
-        <v>557</v>
       </c>
       <c r="C178" s="1">
         <v>1975</v>
@@ -5402,10 +5407,10 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C187" s="1">
         <v>1976</v>
@@ -5462,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="J190" s="8" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
@@ -5479,7 +5484,7 @@
         <v>0</v>
       </c>
       <c r="J191" s="11" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
@@ -5499,7 +5504,7 @@
         <v>50</v>
       </c>
       <c r="J192" s="12" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
@@ -5516,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="J193" s="13" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
@@ -5535,13 +5540,16 @@
       <c r="E194" s="11" t="b">
         <v>1</v>
       </c>
+      <c r="J194" s="14" t="s">
+        <v>672</v>
+      </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
+        <v>583</v>
+      </c>
+      <c r="B195" s="3" t="s">
         <v>584</v>
-      </c>
-      <c r="B195" s="3" t="s">
-        <v>585</v>
       </c>
       <c r="C195" s="1">
         <v>1996</v>
@@ -5563,10 +5571,10 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>571</v>
+      </c>
+      <c r="B197" s="3" t="s">
         <v>572</v>
-      </c>
-      <c r="B197" s="3" t="s">
-        <v>573</v>
       </c>
       <c r="C197" s="1">
         <v>1985</v>
@@ -5659,10 +5667,10 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
+        <v>577</v>
+      </c>
+      <c r="B203" s="3" t="s">
         <v>578</v>
-      </c>
-      <c r="B203" s="3" t="s">
-        <v>579</v>
       </c>
       <c r="E203" s="11" t="b">
         <v>1</v>
@@ -5715,7 +5723,7 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>342</v>
@@ -5822,10 +5830,10 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
+        <v>613</v>
+      </c>
+      <c r="B214" s="3" t="s">
         <v>614</v>
-      </c>
-      <c r="B214" s="3" t="s">
-        <v>615</v>
       </c>
       <c r="C214" s="1">
         <v>1973</v>
@@ -5890,10 +5898,10 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
+        <v>636</v>
+      </c>
+      <c r="B218" s="3" t="s">
         <v>637</v>
-      </c>
-      <c r="B218" s="3" t="s">
-        <v>638</v>
       </c>
       <c r="C218" s="1">
         <v>1995</v>
@@ -5938,10 +5946,10 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
+        <v>653</v>
+      </c>
+      <c r="B221" s="3" t="s">
         <v>654</v>
-      </c>
-      <c r="B221" s="3" t="s">
-        <v>655</v>
       </c>
       <c r="C221" s="1">
         <v>1978</v>
@@ -5983,10 +5991,10 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C224" s="1">
         <v>2010</v>
@@ -5997,10 +6005,10 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
+        <v>513</v>
+      </c>
+      <c r="B225" s="3" t="s">
         <v>514</v>
-      </c>
-      <c r="B225" s="3" t="s">
-        <v>515</v>
       </c>
       <c r="C225" s="1">
         <v>2004</v>
@@ -6028,10 +6036,10 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C227" s="1">
         <v>2003</v>
@@ -6101,10 +6109,10 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>569</v>
+      </c>
+      <c r="B232" s="3" t="s">
         <v>570</v>
-      </c>
-      <c r="B232" s="3" t="s">
-        <v>571</v>
       </c>
       <c r="E232" s="1" t="b">
         <v>0</v>
@@ -6287,10 +6295,10 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
+        <v>609</v>
+      </c>
+      <c r="B244" s="3" t="s">
         <v>610</v>
-      </c>
-      <c r="B244" s="3" t="s">
-        <v>611</v>
       </c>
       <c r="C244" s="1">
         <v>1985</v>
@@ -6332,10 +6340,10 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
+        <v>535</v>
+      </c>
+      <c r="B247" s="3" t="s">
         <v>536</v>
-      </c>
-      <c r="B247" s="3" t="s">
-        <v>537</v>
       </c>
       <c r="E247" s="1" t="b">
         <v>0</v>
@@ -6377,10 +6385,10 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
+        <v>539</v>
+      </c>
+      <c r="B250" s="3" t="s">
         <v>540</v>
-      </c>
-      <c r="B250" s="3" t="s">
-        <v>541</v>
       </c>
       <c r="C250" s="1">
         <v>1981</v>
@@ -6436,10 +6444,10 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
+        <v>601</v>
+      </c>
+      <c r="B254" s="3" t="s">
         <v>602</v>
-      </c>
-      <c r="B254" s="3" t="s">
-        <v>603</v>
       </c>
       <c r="C254" s="1">
         <v>1990</v>
@@ -6450,10 +6458,10 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
+        <v>496</v>
+      </c>
+      <c r="B255" s="3" t="s">
         <v>497</v>
-      </c>
-      <c r="B255" s="3" t="s">
-        <v>498</v>
       </c>
       <c r="C255" s="1">
         <v>1993</v>
@@ -6478,10 +6486,10 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
+        <v>628</v>
+      </c>
+      <c r="B257" s="3" t="s">
         <v>629</v>
-      </c>
-      <c r="B257" s="3" t="s">
-        <v>630</v>
       </c>
       <c r="C257" s="1">
         <v>1962</v>
@@ -6574,10 +6582,10 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
+        <v>616</v>
+      </c>
+      <c r="B263" s="3" t="s">
         <v>617</v>
-      </c>
-      <c r="B263" s="3" t="s">
-        <v>618</v>
       </c>
       <c r="C263" s="1">
         <v>1998</v>
@@ -6616,7 +6624,7 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B266" s="3"/>
       <c r="C266" s="1">
@@ -6648,10 +6656,10 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
+        <v>657</v>
+      </c>
+      <c r="B268" s="3" t="s">
         <v>658</v>
-      </c>
-      <c r="B268" s="3" t="s">
-        <v>659</v>
       </c>
       <c r="C268" s="1">
         <v>1995</v>
@@ -6662,10 +6670,10 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
+        <v>659</v>
+      </c>
+      <c r="B269" s="3" t="s">
         <v>660</v>
-      </c>
-      <c r="B269" s="3" t="s">
-        <v>661</v>
       </c>
       <c r="C269" s="1">
         <v>1995</v>
@@ -6707,10 +6715,10 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
+        <v>565</v>
+      </c>
+      <c r="B272" s="3" t="s">
         <v>566</v>
-      </c>
-      <c r="B272" s="3" t="s">
-        <v>567</v>
       </c>
       <c r="C272" s="1">
         <v>2020</v>
@@ -6721,10 +6729,10 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
+        <v>493</v>
+      </c>
+      <c r="B273" s="3" t="s">
         <v>494</v>
-      </c>
-      <c r="B273" s="3" t="s">
-        <v>495</v>
       </c>
       <c r="E273" s="1" t="b">
         <v>0</v>
@@ -6783,10 +6791,10 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
+        <v>634</v>
+      </c>
+      <c r="B277" s="3" t="s">
         <v>635</v>
-      </c>
-      <c r="B277" s="3" t="s">
-        <v>636</v>
       </c>
       <c r="C277" s="1">
         <v>1971</v>
@@ -6884,10 +6892,10 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
+        <v>517</v>
+      </c>
+      <c r="B284" s="3" t="s">
         <v>518</v>
-      </c>
-      <c r="B284" s="3" t="s">
-        <v>519</v>
       </c>
       <c r="C284" s="1">
         <v>1973</v>
@@ -6994,10 +7002,10 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
+        <v>521</v>
+      </c>
+      <c r="B291" s="3" t="s">
         <v>522</v>
-      </c>
-      <c r="B291" s="3" t="s">
-        <v>523</v>
       </c>
       <c r="C291" s="1">
         <v>1974</v>
@@ -7068,7 +7076,7 @@
         <v>50</v>
       </c>
       <c r="J295" s="8" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.25">
@@ -7085,7 +7093,7 @@
         <v>1</v>
       </c>
       <c r="J296" s="11" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.25">
@@ -7105,15 +7113,15 @@
         <v>1</v>
       </c>
       <c r="J297" s="12" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
+        <v>537</v>
+      </c>
+      <c r="B298" s="3" t="s">
         <v>538</v>
-      </c>
-      <c r="B298" s="3" t="s">
-        <v>539</v>
       </c>
       <c r="C298" s="1">
         <v>1971</v>
@@ -7122,7 +7130,7 @@
         <v>0</v>
       </c>
       <c r="J298" s="13" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
@@ -7138,6 +7146,9 @@
       <c r="E299" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="J299" s="14" t="s">
+        <v>672</v>
+      </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
@@ -7169,10 +7180,10 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
+        <v>553</v>
+      </c>
+      <c r="B302" s="3" t="s">
         <v>554</v>
-      </c>
-      <c r="B302" s="3" t="s">
-        <v>555</v>
       </c>
       <c r="C302" s="1">
         <v>1977</v>
@@ -7183,10 +7194,10 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
+        <v>567</v>
+      </c>
+      <c r="B303" s="3" t="s">
         <v>568</v>
-      </c>
-      <c r="B303" s="3" t="s">
-        <v>569</v>
       </c>
       <c r="C303" s="1">
         <v>2005</v>
@@ -7197,10 +7208,10 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
+        <v>661</v>
+      </c>
+      <c r="B304" s="3" t="s">
         <v>662</v>
-      </c>
-      <c r="B304" s="3" t="s">
-        <v>663</v>
       </c>
       <c r="C304" s="1">
         <v>1998</v>
@@ -7228,10 +7239,10 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
+        <v>632</v>
+      </c>
+      <c r="B306" s="3" t="s">
         <v>633</v>
-      </c>
-      <c r="B306" s="3" t="s">
-        <v>634</v>
       </c>
       <c r="C306" s="1">
         <v>1995</v>
@@ -7380,10 +7391,10 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
+        <v>663</v>
+      </c>
+      <c r="B316" s="3" t="s">
         <v>664</v>
-      </c>
-      <c r="B316" s="3" t="s">
-        <v>665</v>
       </c>
       <c r="C316" s="1">
         <v>1995</v>
@@ -7394,10 +7405,10 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
+        <v>500</v>
+      </c>
+      <c r="B317" s="3" t="s">
         <v>501</v>
-      </c>
-      <c r="B317" s="3" t="s">
-        <v>502</v>
       </c>
       <c r="C317" s="1">
         <v>1994</v>
@@ -7425,10 +7436,10 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
+        <v>525</v>
+      </c>
+      <c r="B319" s="3" t="s">
         <v>526</v>
-      </c>
-      <c r="B319" s="3" t="s">
-        <v>527</v>
       </c>
       <c r="C319" s="1">
         <v>1995</v>
@@ -7515,10 +7526,10 @@
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
+        <v>665</v>
+      </c>
+      <c r="B325" s="3" t="s">
         <v>666</v>
-      </c>
-      <c r="B325" s="3" t="s">
-        <v>667</v>
       </c>
       <c r="C325" s="1">
         <v>2017</v>
@@ -7591,11 +7602,14 @@
       <c r="E329" s="11" t="b">
         <v>1</v>
       </c>
+      <c r="J329" s="1" t="s">
+        <v>492</v>
+      </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.25">
       <c r="J330" s="10">
         <f>SUM(F2:F330)</f>
-        <v>12050</v>
+        <v>12150</v>
       </c>
     </row>
   </sheetData>
